--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2CCEE1-9304-4227-9DB8-E92FE13CD950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11F32D7-9D41-4AE4-AC61-9359E3DBF28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="305">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -935,6 +935,24 @@
   <si>
     <t>AKINDURO GABRIELLA</t>
   </si>
+  <si>
+    <t>NIP:EZEKIEL ADEDAYO OJO</t>
+  </si>
+  <si>
+    <t>NIP:AYOBAMI KASALI</t>
+  </si>
+  <si>
+    <t>OLABISI OLAYIWOLA</t>
+  </si>
+  <si>
+    <t>AYODELE SANDRA</t>
+  </si>
+  <si>
+    <t>ADENIYI HERITAGE</t>
+  </si>
+  <si>
+    <t>ABDULAZEEZ FAMILY</t>
+  </si>
 </sst>
 </file>
 
@@ -1070,7 +1088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1178,6 +1196,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1588,23 +1609,23 @@
         <v>0</v>
       </c>
       <c r="J2" s="24">
-        <f>(1-$D2)*E2</f>
+        <f t="shared" ref="J2:J33" si="0">(1-$D2)*E2</f>
         <v>0</v>
       </c>
       <c r="K2" s="24">
-        <f>(1-$D2)*F2</f>
+        <f t="shared" ref="K2:K33" si="1">(1-$D2)*F2</f>
         <v>19500</v>
       </c>
       <c r="L2" s="24">
-        <f>G2</f>
+        <f t="shared" ref="L2:L33" si="2">G2</f>
         <v>4000</v>
       </c>
       <c r="M2" s="24">
-        <f>(1-$D2)*H2</f>
+        <f t="shared" ref="M2:M33" si="3">(1-$D2)*H2</f>
         <v>0</v>
       </c>
       <c r="N2" s="24">
-        <f>(1-$D2)*I2</f>
+        <f t="shared" ref="N2:N33" si="4">(1-$D2)*I2</f>
         <v>0</v>
       </c>
       <c r="O2" s="24">
@@ -1641,26 +1662,26 @@
         <v>750</v>
       </c>
       <c r="Z2" s="24">
-        <f>SUM(J2:Y2)</f>
+        <f t="shared" ref="Z2:Z33" si="5">SUM(J2:Y2)</f>
         <v>51180</v>
       </c>
       <c r="AA2" s="24">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AB2" s="20">
-        <f>Z2-AA2</f>
-        <v>51180</v>
+        <f t="shared" ref="AB2:AB33" si="6">Z2-AA2</f>
+        <v>21180</v>
       </c>
       <c r="AC2" s="24" t="str">
-        <f>IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
+        <f t="shared" ref="AC2:AC33" si="7">IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
         <v/>
       </c>
       <c r="AD2" s="24" t="str">
-        <f>IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
+        <f t="shared" ref="AD2:AD33" si="8">IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
         <v/>
       </c>
       <c r="AE2" s="24" t="str">
-        <f>IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
+        <f t="shared" ref="AE2:AE33" si="9">IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
         <v/>
       </c>
       <c r="AF2" s="25" t="str">
@@ -1697,23 +1718,23 @@
         <v>5000</v>
       </c>
       <c r="J3" s="24">
-        <f>(1-$D3)*E3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K3" s="24">
-        <f>(1-$D3)*F3</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L3" s="24">
-        <f>G3</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M3" s="24">
-        <f>(1-$D3)*H3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N3" s="24">
-        <f>(1-$D3)*I3</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O3" s="24">
@@ -1750,30 +1771,30 @@
         <v>125</v>
       </c>
       <c r="Z3" s="24">
-        <f>SUM(J3:Y3)</f>
+        <f t="shared" si="5"/>
         <v>72355</v>
       </c>
       <c r="AA3" s="24">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AB3" s="20">
-        <f>Z3-AA3</f>
-        <v>72355</v>
+        <f t="shared" si="6"/>
+        <v>42355</v>
       </c>
       <c r="AC3" s="24" t="str">
-        <f>IF(AND($T3=6000, ($T3+$W3-$AB3)&gt;=6000),T3,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD3" s="24" t="str">
-        <f>IF(AND($T3=8000, ($T3+$W3-$AB3)&gt;=8000),T3,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE3" s="24" t="str">
-        <f>IF(($T3+$W3-$AB3)&gt;=$T3+8000,W3,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF3" s="25" t="str">
-        <f>IF(AB3&lt;=0,"BONUS","")</f>
+        <f t="shared" ref="AF3:AF66" si="10">IF(AB3&lt;=0,"BONUS","")</f>
         <v/>
       </c>
     </row>
@@ -1806,23 +1827,23 @@
         <v>8000</v>
       </c>
       <c r="J4" s="24">
-        <f>(1-$D4)*E4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4" s="24">
-        <f>(1-$D4)*F4</f>
+        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="L4" s="24">
-        <f>G4</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M4" s="24">
-        <f>(1-$D4)*H4</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N4" s="24">
-        <f>(1-$D4)*I4</f>
+        <f t="shared" si="4"/>
         <v>8000</v>
       </c>
       <c r="O4" s="24">
@@ -1859,30 +1880,30 @@
         <v>0</v>
       </c>
       <c r="Z4" s="24">
-        <f>SUM(J4:Y4)</f>
+        <f t="shared" si="5"/>
         <v>81210</v>
       </c>
       <c r="AA4" s="24">
         <v>0</v>
       </c>
       <c r="AB4" s="20">
-        <f>Z4-AA4</f>
+        <f t="shared" si="6"/>
         <v>81210</v>
       </c>
       <c r="AC4" s="24" t="str">
-        <f>IF(AND($T4=6000, ($T4+$W4-$AB4)&gt;=6000),T4,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD4" s="24" t="str">
-        <f>IF(AND($T4=8000, ($T4+$W4-$AB4)&gt;=8000),T4,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE4" s="24" t="str">
-        <f>IF(($T4+$W4-$AB4)&gt;=$T4+8000,W4,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF4" s="25" t="str">
-        <f>IF(AB4&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -1915,23 +1936,23 @@
         <v>0</v>
       </c>
       <c r="J5" s="24">
-        <f>(1-$D5)*E5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K5" s="24">
-        <f>(1-$D5)*F5</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L5" s="24">
-        <f>G5</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M5" s="24">
-        <f>(1-$D5)*H5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N5" s="24">
-        <f>(1-$D5)*I5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O5" s="24">
@@ -1968,30 +1989,30 @@
         <v>0</v>
       </c>
       <c r="Z5" s="24">
-        <f>SUM(J5:Y5)</f>
+        <f t="shared" si="5"/>
         <v>59160</v>
       </c>
       <c r="AA5" s="24">
         <v>0</v>
       </c>
       <c r="AB5" s="20">
-        <f>Z5-AA5</f>
+        <f t="shared" si="6"/>
         <v>59160</v>
       </c>
       <c r="AC5" s="24" t="str">
-        <f>IF(AND($T5=6000, ($T5+$W5-$AB5)&gt;=6000),T5,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD5" s="24" t="str">
-        <f>IF(AND($T5=8000, ($T5+$W5-$AB5)&gt;=8000),T5,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE5" s="24" t="str">
-        <f>IF(($T5+$W5-$AB5)&gt;=$T5+8000,W5,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF5" s="25" t="str">
-        <f>IF(AB5&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2024,23 +2045,23 @@
         <v>0</v>
       </c>
       <c r="J6" s="24">
-        <f>(1-$D6)*E6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="24">
-        <f>(1-$D6)*F6</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L6" s="24">
-        <f>G6</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M6" s="24">
-        <f>(1-$D6)*H6</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N6" s="24">
-        <f>(1-$D6)*I6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O6" s="24">
@@ -2077,30 +2098,30 @@
         <v>0</v>
       </c>
       <c r="Z6" s="24">
-        <f>SUM(J6:Y6)</f>
+        <f t="shared" si="5"/>
         <v>44280</v>
       </c>
       <c r="AA6" s="24">
         <v>0</v>
       </c>
       <c r="AB6" s="20">
-        <f>Z6-AA6</f>
+        <f t="shared" si="6"/>
         <v>44280</v>
       </c>
       <c r="AC6" s="24" t="str">
-        <f>IF(AND($T6=6000, ($T6+$W6-$AB6)&gt;=6000),T6,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD6" s="24" t="str">
-        <f>IF(AND($T6=8000, ($T6+$W6-$AB6)&gt;=8000),T6,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE6" s="24" t="str">
-        <f>IF(($T6+$W6-$AB6)&gt;=$T6+8000,W6,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF6" s="25" t="str">
-        <f>IF(AB6&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2133,23 +2154,23 @@
         <v>0</v>
       </c>
       <c r="J7" s="24">
-        <f>(1-$D7)*E7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7" s="24">
-        <f>(1-$D7)*F7</f>
+        <f t="shared" si="1"/>
         <v>18200</v>
       </c>
       <c r="L7" s="24">
-        <f>G7</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M7" s="24">
-        <f>(1-$D7)*H7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N7" s="24">
-        <f>(1-$D7)*I7</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O7" s="24">
@@ -2186,30 +2207,30 @@
         <v>0</v>
       </c>
       <c r="Z7" s="24">
-        <f>SUM(J7:Y7)</f>
+        <f t="shared" si="5"/>
         <v>43130</v>
       </c>
       <c r="AA7" s="24">
         <v>43130</v>
       </c>
       <c r="AB7" s="20">
-        <f>Z7-AA7</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC7" s="24" t="str">
-        <f>IF(AND($T7=6000, ($T7+$W7-$AB7)&gt;=6000),T7,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD7" s="24" t="str">
-        <f>IF(AND($T7=8000, ($T7+$W7-$AB7)&gt;=8000),T7,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE7" s="24" t="str">
-        <f>IF(($T7+$W7-$AB7)&gt;=$T7+8000,W7,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF7" s="25" t="str">
-        <f>IF(AB7&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -2242,23 +2263,23 @@
         <v>0</v>
       </c>
       <c r="J8" s="24">
-        <f>(1-$D8)*E8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="24">
-        <f>(1-$D8)*F8</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L8" s="24">
-        <f>G8</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M8" s="24">
-        <f>(1-$D8)*H8</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N8" s="24">
-        <f>(1-$D8)*I8</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O8" s="24">
@@ -2295,30 +2316,30 @@
         <v>-90</v>
       </c>
       <c r="Z8" s="24">
-        <f>SUM(J8:Y8)</f>
+        <f t="shared" si="5"/>
         <v>50190</v>
       </c>
       <c r="AA8" s="24">
         <v>30000</v>
       </c>
       <c r="AB8" s="20">
-        <f>Z8-AA8</f>
+        <f t="shared" si="6"/>
         <v>20190</v>
       </c>
       <c r="AC8" s="24" t="str">
-        <f>IF(AND($T8=6000, ($T8+$W8-$AB8)&gt;=6000),T8,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD8" s="24" t="str">
-        <f>IF(AND($T8=8000, ($T8+$W8-$AB8)&gt;=8000),T8,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE8" s="24" t="str">
-        <f>IF(($T8+$W8-$AB8)&gt;=$T8+8000,W8,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF8" s="25" t="str">
-        <f>IF(AB8&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2351,23 +2372,23 @@
         <v>0</v>
       </c>
       <c r="J9" s="24">
-        <f>(1-$D9)*E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="24">
-        <f>(1-$D9)*F9</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L9" s="24">
-        <f>G9</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M9" s="24">
-        <f>(1-$D9)*H9</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N9" s="24">
-        <f>(1-$D9)*I9</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O9" s="24">
@@ -2404,30 +2425,30 @@
         <v>0</v>
       </c>
       <c r="Z9" s="24">
-        <f>SUM(J9:Y9)</f>
+        <f t="shared" si="5"/>
         <v>44280</v>
       </c>
       <c r="AA9" s="24">
         <v>16870</v>
       </c>
       <c r="AB9" s="20">
-        <f>Z9-AA9</f>
+        <f t="shared" si="6"/>
         <v>27410</v>
       </c>
       <c r="AC9" s="24" t="str">
-        <f>IF(AND($T9=6000, ($T9+$W9-$AB9)&gt;=6000),T9,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD9" s="24" t="str">
-        <f>IF(AND($T9=8000, ($T9+$W9-$AB9)&gt;=8000),T9,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE9" s="24" t="str">
-        <f>IF(($T9+$W9-$AB9)&gt;=$T9+8000,W9,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF9" s="25" t="str">
-        <f>IF(AB9&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2460,23 +2481,23 @@
         <v>5000</v>
       </c>
       <c r="J10" s="24">
-        <f>(1-$D10)*E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="24">
-        <f>(1-$D10)*F10</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L10" s="24">
-        <f>G10</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M10" s="24">
-        <f>(1-$D10)*H10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N10" s="24">
-        <f>(1-$D10)*I10</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O10" s="24">
@@ -2513,30 +2534,30 @@
         <v>0</v>
       </c>
       <c r="Z10" s="24">
-        <f>SUM(J10:Y10)</f>
+        <f t="shared" si="5"/>
         <v>69290</v>
       </c>
       <c r="AA10" s="24">
         <v>0</v>
       </c>
       <c r="AB10" s="20">
-        <f>Z10-AA10</f>
+        <f t="shared" si="6"/>
         <v>69290</v>
       </c>
       <c r="AC10" s="24" t="str">
-        <f>IF(AND($T10=6000, ($T10+$W10-$AB10)&gt;=6000),T10,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD10" s="24" t="str">
-        <f>IF(AND($T10=8000, ($T10+$W10-$AB10)&gt;=8000),T10,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE10" s="24" t="str">
-        <f>IF(($T10+$W10-$AB10)&gt;=$T10+8000,W10,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF10" s="25" t="str">
-        <f>IF(AB10&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2569,23 +2590,23 @@
         <v>6000</v>
       </c>
       <c r="J11" s="24">
-        <f>(1-$D11)*E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="24">
-        <f>(1-$D11)*F11</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L11" s="24">
-        <f>G11</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M11" s="24">
-        <f>(1-$D11)*H11</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N11" s="24">
-        <f>(1-$D11)*I11</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O11" s="24">
@@ -2622,30 +2643,30 @@
         <v>750</v>
       </c>
       <c r="Z11" s="24">
-        <f>SUM(J11:Y11)</f>
+        <f t="shared" si="5"/>
         <v>78330</v>
       </c>
       <c r="AA11" s="24">
         <v>0</v>
       </c>
       <c r="AB11" s="20">
-        <f>Z11-AA11</f>
+        <f t="shared" si="6"/>
         <v>78330</v>
       </c>
       <c r="AC11" s="24" t="str">
-        <f>IF(AND($T11=6000, ($T11+$W11-$AB11)&gt;=6000),T11,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD11" s="24" t="str">
-        <f>IF(AND($T11=8000, ($T11+$W11-$AB11)&gt;=8000),T11,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE11" s="24" t="str">
-        <f>IF(($T11+$W11-$AB11)&gt;=$T11+8000,W11,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF11" s="25" t="str">
-        <f>IF(AB11&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2678,23 +2699,23 @@
         <v>8000</v>
       </c>
       <c r="J12" s="24">
-        <f>(1-$D12)*E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="24">
-        <f>(1-$D12)*F12</f>
+        <f t="shared" si="1"/>
         <v>30000</v>
       </c>
       <c r="L12" s="24">
-        <f>G12</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M12" s="24">
-        <f>(1-$D12)*H12</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N12" s="24">
-        <f>(1-$D12)*I12</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O12" s="24">
@@ -2731,30 +2752,30 @@
         <v>540</v>
       </c>
       <c r="Z12" s="24">
-        <f>SUM(J12:Y12)</f>
+        <f t="shared" si="5"/>
         <v>97250</v>
       </c>
       <c r="AA12" s="24">
         <v>0</v>
       </c>
       <c r="AB12" s="20">
-        <f>Z12-AA12</f>
+        <f t="shared" si="6"/>
         <v>97250</v>
       </c>
       <c r="AC12" s="24" t="str">
-        <f>IF(AND($T12=6000, ($T12+$W12-$AB12)&gt;=6000),T12,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD12" s="24" t="str">
-        <f>IF(AND($T12=8000, ($T12+$W12-$AB12)&gt;=8000),T12,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE12" s="24" t="str">
-        <f>IF(($T12+$W12-$AB12)&gt;=$T12+8000,W12,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF12" s="25" t="str">
-        <f>IF(AB12&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2787,23 +2808,23 @@
         <v>0</v>
       </c>
       <c r="J13" s="24">
-        <f>(1-$D13)*E13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="24">
-        <f>(1-$D13)*F13</f>
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
       <c r="L13" s="24">
-        <f>G13</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M13" s="24">
-        <f>(1-$D13)*H13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N13" s="24">
-        <f>(1-$D13)*I13</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O13" s="24">
@@ -2840,30 +2861,30 @@
         <v>0</v>
       </c>
       <c r="Z13" s="24">
-        <f>SUM(J13:Y13)</f>
+        <f t="shared" si="5"/>
         <v>52660</v>
       </c>
       <c r="AA13" s="24">
         <v>0</v>
       </c>
       <c r="AB13" s="20">
-        <f>Z13-AA13</f>
+        <f t="shared" si="6"/>
         <v>52660</v>
       </c>
       <c r="AC13" s="24" t="str">
-        <f>IF(AND($T13=6000, ($T13+$W13-$AB13)&gt;=6000),T13,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD13" s="24" t="str">
-        <f>IF(AND($T13=8000, ($T13+$W13-$AB13)&gt;=8000),T13,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE13" s="24" t="str">
-        <f>IF(($T13+$W13-$AB13)&gt;=$T13+8000,W13,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF13" s="25" t="str">
-        <f>IF(AB13&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2896,23 +2917,23 @@
         <v>5000</v>
       </c>
       <c r="J14" s="24">
-        <f>(1-$D14)*E14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="24">
-        <f>(1-$D14)*F14</f>
+        <f t="shared" si="1"/>
         <v>14000</v>
       </c>
       <c r="L14" s="24">
-        <f>G14</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M14" s="24">
-        <f>(1-$D14)*H14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="24">
-        <f>(1-$D14)*I14</f>
+        <f t="shared" si="4"/>
         <v>2500</v>
       </c>
       <c r="O14" s="24">
@@ -2949,30 +2970,30 @@
         <v>-530</v>
       </c>
       <c r="Z14" s="24">
-        <f>SUM(J14:Y14)</f>
+        <f t="shared" si="5"/>
         <v>60510</v>
       </c>
       <c r="AA14" s="24">
         <v>0</v>
       </c>
       <c r="AB14" s="20">
-        <f>Z14-AA14</f>
+        <f t="shared" si="6"/>
         <v>60510</v>
       </c>
       <c r="AC14" s="24" t="str">
-        <f>IF(AND($T14=6000, ($T14+$W14-$AB14)&gt;=6000),T14,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD14" s="24" t="str">
-        <f>IF(AND($T14=8000, ($T14+$W14-$AB14)&gt;=8000),T14,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE14" s="24" t="str">
-        <f>IF(($T14+$W14-$AB14)&gt;=$T14+8000,W14,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF14" s="25" t="str">
-        <f>IF(AB14&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3005,23 +3026,23 @@
         <v>0</v>
       </c>
       <c r="J15" s="24">
-        <f>(1-$D15)*E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15" s="24">
-        <f>(1-$D15)*F15</f>
+        <f t="shared" si="1"/>
         <v>24700</v>
       </c>
       <c r="L15" s="24">
-        <f>G15</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M15" s="24">
-        <f>(1-$D15)*H15</f>
+        <f t="shared" si="3"/>
         <v>950</v>
       </c>
       <c r="N15" s="24">
-        <f>(1-$D15)*I15</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O15" s="24">
@@ -3058,30 +3079,30 @@
         <v>-1000</v>
       </c>
       <c r="Z15" s="24">
-        <f>SUM(J15:Y15)</f>
+        <f t="shared" si="5"/>
         <v>40790</v>
       </c>
       <c r="AA15" s="24">
         <v>42140</v>
       </c>
       <c r="AB15" s="20">
-        <f>Z15-AA15</f>
+        <f t="shared" si="6"/>
         <v>-1350</v>
       </c>
       <c r="AC15" s="24" t="str">
-        <f>IF(AND($T15=6000, ($T15+$W15-$AB15)&gt;=6000),T15,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD15" s="24" t="str">
-        <f>IF(AND($T15=8000, ($T15+$W15-$AB15)&gt;=8000),T15,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE15" s="24" t="str">
-        <f>IF(($T15+$W15-$AB15)&gt;=$T15+8000,W15,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF15" s="25" t="str">
-        <f>IF(AB15&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -3114,23 +3135,23 @@
         <v>0</v>
       </c>
       <c r="J16" s="24">
-        <f>(1-$D16)*E16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="24">
-        <f>(1-$D16)*F16</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L16" s="24">
-        <f>G16</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M16" s="24">
-        <f>(1-$D16)*H16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N16" s="24">
-        <f>(1-$D16)*I16</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16" s="24">
@@ -3167,30 +3188,30 @@
         <v>0</v>
       </c>
       <c r="Z16" s="24">
-        <f>SUM(J16:Y16)</f>
+        <f t="shared" si="5"/>
         <v>59160</v>
       </c>
       <c r="AA16" s="24">
         <v>0</v>
       </c>
       <c r="AB16" s="20">
-        <f>Z16-AA16</f>
+        <f t="shared" si="6"/>
         <v>59160</v>
       </c>
       <c r="AC16" s="24" t="str">
-        <f>IF(AND($T16=6000, ($T16+$W16-$AB16)&gt;=6000),T16,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD16" s="24" t="str">
-        <f>IF(AND($T16=8000, ($T16+$W16-$AB16)&gt;=8000),T16,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE16" s="24" t="str">
-        <f>IF(($T16+$W16-$AB16)&gt;=$T16+8000,W16,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF16" s="25" t="str">
-        <f>IF(AB16&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3223,23 +3244,23 @@
         <v>5000</v>
       </c>
       <c r="J17" s="24">
-        <f>(1-$D17)*E17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K17" s="24">
-        <f>(1-$D17)*F17</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L17" s="24">
-        <f>G17</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M17" s="24">
-        <f>(1-$D17)*H17</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N17" s="24">
-        <f>(1-$D17)*I17</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O17" s="24">
@@ -3276,30 +3297,30 @@
         <v>0</v>
       </c>
       <c r="Z17" s="24">
-        <f>SUM(J17:Y17)</f>
+        <f t="shared" si="5"/>
         <v>69290</v>
       </c>
       <c r="AA17" s="24">
         <v>0</v>
       </c>
       <c r="AB17" s="20">
-        <f>Z17-AA17</f>
+        <f t="shared" si="6"/>
         <v>69290</v>
       </c>
       <c r="AC17" s="24" t="str">
-        <f>IF(AND($T17=6000, ($T17+$W17-$AB17)&gt;=6000),T17,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD17" s="24" t="str">
-        <f>IF(AND($T17=8000, ($T17+$W17-$AB17)&gt;=8000),T17,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE17" s="24" t="str">
-        <f>IF(($T17+$W17-$AB17)&gt;=$T17+8000,W17,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF17" s="25" t="str">
-        <f>IF(AB17&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3332,23 +3353,23 @@
         <v>0</v>
       </c>
       <c r="J18" s="24">
-        <f>(1-$D18)*E18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K18" s="24">
-        <f>(1-$D18)*F18</f>
+        <f t="shared" si="1"/>
         <v>18200</v>
       </c>
       <c r="L18" s="24">
-        <f>G18</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M18" s="24">
-        <f>(1-$D18)*H18</f>
+        <f t="shared" si="3"/>
         <v>700</v>
       </c>
       <c r="N18" s="24">
-        <f>(1-$D18)*I18</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O18" s="24">
@@ -3385,30 +3406,30 @@
         <v>0</v>
       </c>
       <c r="Z18" s="24">
-        <f>SUM(J18:Y18)</f>
+        <f t="shared" si="5"/>
         <v>42930</v>
       </c>
       <c r="AA18" s="24">
         <v>42930</v>
       </c>
       <c r="AB18" s="20">
-        <f>Z18-AA18</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC18" s="24" t="str">
-        <f>IF(AND($T18=6000, ($T18+$W18-$AB18)&gt;=6000),T18,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD18" s="24" t="str">
-        <f>IF(AND($T18=8000, ($T18+$W18-$AB18)&gt;=8000),T18,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE18" s="24" t="str">
-        <f>IF(($T18+$W18-$AB18)&gt;=$T18+8000,W18,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF18" s="25" t="str">
-        <f>IF(AB18&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -3441,23 +3462,23 @@
         <v>5000</v>
       </c>
       <c r="J19" s="24">
-        <f>(1-$D19)*E19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19" s="24">
-        <f>(1-$D19)*F19</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L19" s="24">
-        <f>G19</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M19" s="24">
-        <f>(1-$D19)*H19</f>
+        <f t="shared" si="3"/>
         <v>1875</v>
       </c>
       <c r="N19" s="24">
-        <f>(1-$D19)*I19</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O19" s="24">
@@ -3494,30 +3515,30 @@
         <v>0</v>
       </c>
       <c r="Z19" s="24">
-        <f>SUM(J19:Y19)</f>
+        <f t="shared" si="5"/>
         <v>73925</v>
       </c>
       <c r="AA19" s="24">
         <v>51685</v>
       </c>
       <c r="AB19" s="20">
-        <f>Z19-AA19</f>
+        <f t="shared" si="6"/>
         <v>22240</v>
       </c>
       <c r="AC19" s="24" t="str">
-        <f>IF(AND($T19=6000, ($T19+$W19-$AB19)&gt;=6000),T19,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD19" s="24" t="str">
-        <f>IF(AND($T19=8000, ($T19+$W19-$AB19)&gt;=8000),T19,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE19" s="24" t="str">
-        <f>IF(($T19+$W19-$AB19)&gt;=$T19+8000,W19,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF19" s="25" t="str">
-        <f>IF(AB19&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3550,23 +3571,23 @@
         <v>5000</v>
       </c>
       <c r="J20" s="24">
-        <f>(1-$D20)*E20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20" s="24">
-        <f>(1-$D20)*F20</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L20" s="24">
-        <f>G20</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M20" s="24">
-        <f>(1-$D20)*H20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N20" s="24">
-        <f>(1-$D20)*I20</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O20" s="24">
@@ -3603,30 +3624,30 @@
         <v>0</v>
       </c>
       <c r="Z20" s="24">
-        <f>SUM(J20:Y20)</f>
+        <f t="shared" si="5"/>
         <v>76770</v>
       </c>
       <c r="AA20" s="24">
         <v>0</v>
       </c>
       <c r="AB20" s="20">
-        <f>Z20-AA20</f>
+        <f t="shared" si="6"/>
         <v>76770</v>
       </c>
       <c r="AC20" s="24" t="str">
-        <f>IF(AND($T20=6000, ($T20+$W20-$AB20)&gt;=6000),T20,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD20" s="24" t="str">
-        <f>IF(AND($T20=8000, ($T20+$W20-$AB20)&gt;=8000),T20,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE20" s="24" t="str">
-        <f>IF(($T20+$W20-$AB20)&gt;=$T20+8000,W20,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF20" s="25" t="str">
-        <f>IF(AB20&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3659,23 +3680,23 @@
         <v>6000</v>
       </c>
       <c r="J21" s="24">
-        <f>(1-$D21)*E21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K21" s="24">
-        <f>(1-$D21)*F21</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L21" s="24">
-        <f>G21</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M21" s="24">
-        <f>(1-$D21)*H21</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N21" s="24">
-        <f>(1-$D21)*I21</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O21" s="24">
@@ -3712,30 +3733,30 @@
         <v>0</v>
       </c>
       <c r="Z21" s="24">
-        <f>SUM(J21:Y21)</f>
+        <f t="shared" si="5"/>
         <v>62230</v>
       </c>
       <c r="AA21" s="24">
         <v>0</v>
       </c>
       <c r="AB21" s="20">
-        <f>Z21-AA21</f>
+        <f t="shared" si="6"/>
         <v>62230</v>
       </c>
       <c r="AC21" s="24" t="str">
-        <f>IF(AND($T21=6000, ($T21+$W21-$AB21)&gt;=6000),T21,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD21" s="24" t="str">
-        <f>IF(AND($T21=8000, ($T21+$W21-$AB21)&gt;=8000),T21,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE21" s="24" t="str">
-        <f>IF(($T21+$W21-$AB21)&gt;=$T21+8000,W21,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF21" s="25" t="str">
-        <f>IF(AB21&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3768,23 +3789,23 @@
         <v>6000</v>
       </c>
       <c r="J22" s="24">
-        <f>(1-$D22)*E22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K22" s="24">
-        <f>(1-$D22)*F22</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L22" s="24">
-        <f>G22</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M22" s="24">
-        <f>(1-$D22)*H22</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N22" s="24">
-        <f>(1-$D22)*I22</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O22" s="24">
@@ -3821,30 +3842,30 @@
         <v>0</v>
       </c>
       <c r="Z22" s="24">
-        <f>SUM(J22:Y22)</f>
+        <f t="shared" si="5"/>
         <v>67530</v>
       </c>
       <c r="AA22" s="24">
         <v>0</v>
       </c>
       <c r="AB22" s="20">
-        <f>Z22-AA22</f>
+        <f t="shared" si="6"/>
         <v>67530</v>
       </c>
       <c r="AC22" s="24" t="str">
-        <f>IF(AND($T22=6000, ($T22+$W22-$AB22)&gt;=6000),T22,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD22" s="24" t="str">
-        <f>IF(AND($T22=8000, ($T22+$W22-$AB22)&gt;=8000),T22,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE22" s="24" t="str">
-        <f>IF(($T22+$W22-$AB22)&gt;=$T22+8000,W22,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF22" s="25" t="str">
-        <f>IF(AB22&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3877,23 +3898,23 @@
         <v>5000</v>
       </c>
       <c r="J23" s="24">
-        <f>(1-$D23)*E23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K23" s="24">
-        <f>(1-$D23)*F23</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L23" s="24">
-        <f>G23</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M23" s="24">
-        <f>(1-$D23)*H23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N23" s="24">
-        <f>(1-$D23)*I23</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O23" s="24">
@@ -3930,30 +3951,30 @@
         <v>0</v>
       </c>
       <c r="Z23" s="24">
-        <f>SUM(J23:Y23)</f>
+        <f t="shared" si="5"/>
         <v>66230</v>
       </c>
       <c r="AA23" s="24">
         <v>0</v>
       </c>
       <c r="AB23" s="20">
-        <f>Z23-AA23</f>
+        <f t="shared" si="6"/>
         <v>66230</v>
       </c>
       <c r="AC23" s="24" t="str">
-        <f>IF(AND($T23=6000, ($T23+$W23-$AB23)&gt;=6000),T23,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD23" s="24" t="str">
-        <f>IF(AND($T23=8000, ($T23+$W23-$AB23)&gt;=8000),T23,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE23" s="24" t="str">
-        <f>IF(($T23+$W23-$AB23)&gt;=$T23+8000,W23,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF23" s="25" t="str">
-        <f>IF(AB23&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3986,23 +4007,23 @@
         <v>5000</v>
       </c>
       <c r="J24" s="24">
-        <f>(1-$D24)*E24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K24" s="24">
-        <f>(1-$D24)*F24</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L24" s="24">
-        <f>G24</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M24" s="24">
-        <f>(1-$D24)*H24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N24" s="24">
-        <f>(1-$D24)*I24</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O24" s="24">
@@ -4039,30 +4060,30 @@
         <v>0</v>
       </c>
       <c r="Z24" s="24">
-        <f>SUM(J24:Y24)</f>
+        <f t="shared" si="5"/>
         <v>66230</v>
       </c>
       <c r="AA24" s="24">
         <v>0</v>
       </c>
       <c r="AB24" s="20">
-        <f>Z24-AA24</f>
+        <f t="shared" si="6"/>
         <v>66230</v>
       </c>
       <c r="AC24" s="24" t="str">
-        <f>IF(AND($T24=6000, ($T24+$W24-$AB24)&gt;=6000),T24,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD24" s="24" t="str">
-        <f>IF(AND($T24=8000, ($T24+$W24-$AB24)&gt;=8000),T24,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE24" s="24" t="str">
-        <f>IF(($T24+$W24-$AB24)&gt;=$T24+8000,W24,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF24" s="25" t="str">
-        <f>IF(AB24&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4095,23 +4116,23 @@
         <v>6000</v>
       </c>
       <c r="J25" s="24">
-        <f>(1-$D25)*E25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K25" s="24">
-        <f>(1-$D25)*F25</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L25" s="24">
-        <f>G25</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M25" s="24">
-        <f>(1-$D25)*H25</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N25" s="24">
-        <f>(1-$D25)*I25</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O25" s="24">
@@ -4148,30 +4169,30 @@
         <v>0</v>
       </c>
       <c r="Z25" s="24">
-        <f>SUM(J25:Y25)</f>
+        <f t="shared" si="5"/>
         <v>79830</v>
       </c>
       <c r="AA25" s="24">
         <v>60000</v>
       </c>
       <c r="AB25" s="20">
-        <f>Z25-AA25</f>
+        <f t="shared" si="6"/>
         <v>19830</v>
       </c>
       <c r="AC25" s="24" t="str">
-        <f>IF(AND($T25=6000, ($T25+$W25-$AB25)&gt;=6000),T25,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD25" s="24" t="str">
-        <f>IF(AND($T25=8000, ($T25+$W25-$AB25)&gt;=8000),T25,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE25" s="24" t="str">
-        <f>IF(($T25+$W25-$AB25)&gt;=$T25+8000,W25,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF25" s="25" t="str">
-        <f>IF(AB25&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4186,7 +4207,7 @@
         <v>67</v>
       </c>
       <c r="D26" s="23">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E26" s="24">
         <v>0</v>
@@ -4204,24 +4225,24 @@
         <v>6000</v>
       </c>
       <c r="J26" s="24">
-        <f>(1-$D26)*E26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26" s="24">
-        <f>(1-$D26)*F26</f>
-        <v>16500</v>
+        <f t="shared" si="1"/>
+        <v>14849.999999999998</v>
       </c>
       <c r="L26" s="24">
-        <f>G26</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M26" s="24">
-        <f>(1-$D26)*H26</f>
-        <v>1000</v>
+        <f t="shared" si="3"/>
+        <v>899.99999999999989</v>
       </c>
       <c r="N26" s="24">
-        <f>(1-$D26)*I26</f>
-        <v>3000</v>
+        <f t="shared" si="4"/>
+        <v>2699.9999999999995</v>
       </c>
       <c r="O26" s="24">
         <v>22400</v>
@@ -4257,31 +4278,31 @@
         <v>0</v>
       </c>
       <c r="Z26" s="24">
-        <f>SUM(J26:Y26)</f>
+        <f t="shared" si="5"/>
+        <v>60180</v>
+      </c>
+      <c r="AA26" s="24">
         <v>62230</v>
       </c>
-      <c r="AA26" s="24">
-        <v>0</v>
-      </c>
       <c r="AB26" s="20">
-        <f>Z26-AA26</f>
-        <v>62230</v>
+        <f t="shared" si="6"/>
+        <v>-2050</v>
       </c>
       <c r="AC26" s="24" t="str">
-        <f>IF(AND($T26=6000, ($T26+$W26-$AB26)&gt;=6000),T26,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD26" s="24" t="str">
-        <f>IF(AND($T26=8000, ($T26+$W26-$AB26)&gt;=8000),T26,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE26" s="24" t="str">
-        <f>IF(($T26+$W26-$AB26)&gt;=$T26+8000,W26,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF26" s="25" t="str">
-        <f>IF(AB26&lt;=0,"BONUS","")</f>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
@@ -4313,23 +4334,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="24">
-        <f>(1-$D27)*E27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K27" s="24">
-        <f>(1-$D27)*F27</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L27" s="24">
-        <f>G27</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M27" s="24">
-        <f>(1-$D27)*H27</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N27" s="24">
-        <f>(1-$D27)*I27</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O27" s="24">
@@ -4366,30 +4387,30 @@
         <v>-400</v>
       </c>
       <c r="Z27" s="24">
-        <f>SUM(J27:Y27)</f>
+        <f t="shared" si="5"/>
         <v>56630</v>
       </c>
       <c r="AA27" s="24">
         <v>0</v>
       </c>
       <c r="AB27" s="20">
-        <f>Z27-AA27</f>
+        <f t="shared" si="6"/>
         <v>56630</v>
       </c>
       <c r="AC27" s="24" t="str">
-        <f>IF(AND($T27=6000, ($T27+$W27-$AB27)&gt;=6000),T27,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD27" s="24" t="str">
-        <f>IF(AND($T27=8000, ($T27+$W27-$AB27)&gt;=8000),T27,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE27" s="24" t="str">
-        <f>IF(($T27+$W27-$AB27)&gt;=$T27+8000,W27,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF27" s="25" t="str">
-        <f>IF(AB27&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4422,23 +4443,23 @@
         <v>0</v>
       </c>
       <c r="J28" s="24">
-        <f>(1-$D28)*E28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28" s="24">
-        <f>(1-$D28)*F28</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L28" s="24">
-        <f>G28</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M28" s="24">
-        <f>(1-$D28)*H28</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N28" s="24">
-        <f>(1-$D28)*I28</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="24">
@@ -4475,30 +4496,30 @@
         <v>0</v>
       </c>
       <c r="Z28" s="24">
-        <f>SUM(J28:Y28)</f>
+        <f t="shared" si="5"/>
         <v>43140</v>
       </c>
       <c r="AA28" s="24">
         <v>0</v>
       </c>
       <c r="AB28" s="20">
-        <f>Z28-AA28</f>
+        <f t="shared" si="6"/>
         <v>43140</v>
       </c>
       <c r="AC28" s="24" t="str">
-        <f>IF(AND($T28=6000, ($T28+$W28-$AB28)&gt;=6000),T28,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD28" s="24" t="str">
-        <f>IF(AND($T28=8000, ($T28+$W28-$AB28)&gt;=8000),T28,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE28" s="24" t="str">
-        <f>IF(($T28+$W28-$AB28)&gt;=$T28+8000,W28,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF28" s="25" t="str">
-        <f>IF(AB28&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4531,23 +4552,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="24">
-        <f>(1-$D29)*E29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K29" s="24">
-        <f>(1-$D29)*F29</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L29" s="24">
-        <f>G29</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M29" s="24">
-        <f>(1-$D29)*H29</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N29" s="24">
-        <f>(1-$D29)*I29</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="24">
@@ -4584,30 +4605,30 @@
         <v>11000</v>
       </c>
       <c r="Z29" s="24">
-        <f>SUM(J29:Y29)</f>
+        <f t="shared" si="5"/>
         <v>62030</v>
       </c>
       <c r="AA29" s="24">
         <v>0</v>
       </c>
       <c r="AB29" s="20">
-        <f>Z29-AA29</f>
+        <f t="shared" si="6"/>
         <v>62030</v>
       </c>
       <c r="AC29" s="24" t="str">
-        <f>IF(AND($T29=6000, ($T29+$W29-$AB29)&gt;=6000),T29,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD29" s="24" t="str">
-        <f>IF(AND($T29=8000, ($T29+$W29-$AB29)&gt;=8000),T29,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE29" s="24" t="str">
-        <f>IF(($T29+$W29-$AB29)&gt;=$T29+8000,W29,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF29" s="25" t="str">
-        <f>IF(AB29&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4640,23 +4661,23 @@
         <v>8000</v>
       </c>
       <c r="J30" s="24">
-        <f>(1-$D30)*E30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K30" s="24">
-        <f>(1-$D30)*F30</f>
+        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="L30" s="24">
-        <f>G30</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M30" s="24">
-        <f>(1-$D30)*H30</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N30" s="24">
-        <f>(1-$D30)*I30</f>
+        <f t="shared" si="4"/>
         <v>8000</v>
       </c>
       <c r="O30" s="24">
@@ -4693,30 +4714,30 @@
         <v>0</v>
       </c>
       <c r="Z30" s="24">
-        <f>SUM(J30:Y30)</f>
+        <f t="shared" si="5"/>
         <v>81210</v>
       </c>
       <c r="AA30" s="24">
         <v>0</v>
       </c>
       <c r="AB30" s="20">
-        <f>Z30-AA30</f>
+        <f t="shared" si="6"/>
         <v>81210</v>
       </c>
       <c r="AC30" s="24" t="str">
-        <f>IF(AND($T30=6000, ($T30+$W30-$AB30)&gt;=6000),T30,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD30" s="24" t="str">
-        <f>IF(AND($T30=8000, ($T30+$W30-$AB30)&gt;=8000),T30,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE30" s="24" t="str">
-        <f>IF(($T30+$W30-$AB30)&gt;=$T30+8000,W30,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF30" s="25" t="str">
-        <f>IF(AB30&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4749,23 +4770,23 @@
         <v>0</v>
       </c>
       <c r="J31" s="24">
-        <f>(1-$D31)*E31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K31" s="24">
-        <f>(1-$D31)*F31</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L31" s="24">
-        <f>G31</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M31" s="24">
-        <f>(1-$D31)*H31</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N31" s="24">
-        <f>(1-$D31)*I31</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O31" s="24">
@@ -4802,30 +4823,30 @@
         <v>0</v>
       </c>
       <c r="Z31" s="24">
-        <f>SUM(J31:Y31)</f>
+        <f t="shared" si="5"/>
         <v>43140</v>
       </c>
       <c r="AA31" s="24">
         <v>0</v>
       </c>
       <c r="AB31" s="20">
-        <f>Z31-AA31</f>
+        <f t="shared" si="6"/>
         <v>43140</v>
       </c>
       <c r="AC31" s="24" t="str">
-        <f>IF(AND($T31=6000, ($T31+$W31-$AB31)&gt;=6000),T31,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD31" s="24" t="str">
-        <f>IF(AND($T31=8000, ($T31+$W31-$AB31)&gt;=8000),T31,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE31" s="24" t="str">
-        <f>IF(($T31+$W31-$AB31)&gt;=$T31+8000,W31,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF31" s="25" t="str">
-        <f>IF(AB31&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4858,23 +4879,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="24">
-        <f>(1-$D32)*E32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K32" s="24">
-        <f>(1-$D32)*F32</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L32" s="24">
-        <f>G32</f>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="M32" s="24">
-        <f>(1-$D32)*H32</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32" s="24">
-        <f>(1-$D32)*I32</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="24">
@@ -4911,30 +4932,30 @@
         <v>0</v>
       </c>
       <c r="Z32" s="24">
-        <f>SUM(J32:Y32)</f>
+        <f t="shared" si="5"/>
         <v>24550</v>
       </c>
       <c r="AA32" s="24">
         <v>1300</v>
       </c>
       <c r="AB32" s="20">
-        <f>Z32-AA32</f>
+        <f t="shared" si="6"/>
         <v>23250</v>
       </c>
       <c r="AC32" s="24" t="str">
-        <f>IF(AND($T32=6000, ($T32+$W32-$AB32)&gt;=6000),T32,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD32" s="24" t="str">
-        <f>IF(AND($T32=8000, ($T32+$W32-$AB32)&gt;=8000),T32,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE32" s="24" t="str">
-        <f>IF(($T32+$W32-$AB32)&gt;=$T32+8000,W32,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF32" s="25" t="str">
-        <f>IF(AB32&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4967,23 +4988,23 @@
         <v>0</v>
       </c>
       <c r="J33" s="24">
-        <f>(1-$D33)*E33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K33" s="24">
-        <f>(1-$D33)*F33</f>
+        <f t="shared" si="1"/>
         <v>18200</v>
       </c>
       <c r="L33" s="24">
-        <f>G33</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M33" s="24">
-        <f>(1-$D33)*H33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N33" s="24">
-        <f>(1-$D33)*I33</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O33" s="24">
@@ -5020,30 +5041,30 @@
         <v>0</v>
       </c>
       <c r="Z33" s="24">
-        <f>SUM(J33:Y33)</f>
+        <f t="shared" si="5"/>
         <v>49130</v>
       </c>
       <c r="AA33" s="24">
         <v>49130</v>
       </c>
       <c r="AB33" s="20">
-        <f>Z33-AA33</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC33" s="24">
-        <f>IF(AND($T33=6000, ($T33+$W33-$AB33)&gt;=6000),T33,"")</f>
+        <f t="shared" si="7"/>
         <v>6000</v>
       </c>
       <c r="AD33" s="24" t="str">
-        <f>IF(AND($T33=8000, ($T33+$W33-$AB33)&gt;=8000),T33,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE33" s="24" t="str">
-        <f>IF(($T33+$W33-$AB33)&gt;=$T33+8000,W33,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF33" s="25" t="str">
-        <f>IF(AB33&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -5076,23 +5097,23 @@
         <v>0</v>
       </c>
       <c r="J34" s="24">
-        <f>(1-$D34)*E34</f>
+        <f t="shared" ref="J34:J65" si="11">(1-$D34)*E34</f>
         <v>0</v>
       </c>
       <c r="K34" s="24">
-        <f>(1-$D34)*F34</f>
+        <f t="shared" ref="K34:K65" si="12">(1-$D34)*F34</f>
         <v>19500</v>
       </c>
       <c r="L34" s="24">
-        <f>G34</f>
+        <f t="shared" ref="L34:L65" si="13">G34</f>
         <v>4000</v>
       </c>
       <c r="M34" s="24">
-        <f>(1-$D34)*H34</f>
+        <f t="shared" ref="M34:M65" si="14">(1-$D34)*H34</f>
         <v>0</v>
       </c>
       <c r="N34" s="24">
-        <f>(1-$D34)*I34</f>
+        <f t="shared" ref="N34:N65" si="15">(1-$D34)*I34</f>
         <v>0</v>
       </c>
       <c r="O34" s="24">
@@ -5129,30 +5150,30 @@
         <v>0</v>
       </c>
       <c r="Z34" s="24">
-        <f>SUM(J34:Y34)</f>
+        <f t="shared" ref="Z34:Z65" si="16">SUM(J34:Y34)</f>
         <v>65160</v>
       </c>
       <c r="AA34" s="24">
         <v>0</v>
       </c>
       <c r="AB34" s="20">
-        <f>Z34-AA34</f>
+        <f t="shared" ref="AB34:AB65" si="17">Z34-AA34</f>
         <v>65160</v>
       </c>
       <c r="AC34" s="24" t="str">
-        <f>IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
+        <f t="shared" ref="AC34:AC65" si="18">IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
         <v/>
       </c>
       <c r="AD34" s="24" t="str">
-        <f>IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
+        <f t="shared" ref="AD34:AD65" si="19">IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="24" t="str">
-        <f>IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
+        <f t="shared" ref="AE34:AE65" si="20">IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
         <v/>
       </c>
       <c r="AF34" s="25" t="str">
-        <f>IF(AB34&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5185,23 +5206,23 @@
         <v>5000</v>
       </c>
       <c r="J35" s="24">
-        <f>(1-$D35)*E35</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K35" s="24">
-        <f>(1-$D35)*F35</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L35" s="24">
-        <f>G35</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M35" s="24">
-        <f>(1-$D35)*H35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N35" s="24">
-        <f>(1-$D35)*I35</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O35" s="24">
@@ -5238,30 +5259,30 @@
         <v>250</v>
       </c>
       <c r="Z35" s="24">
-        <f>SUM(J35:Y35)</f>
+        <f t="shared" si="16"/>
         <v>72480</v>
       </c>
       <c r="AA35" s="24">
         <v>0</v>
       </c>
       <c r="AB35" s="20">
-        <f>Z35-AA35</f>
+        <f t="shared" si="17"/>
         <v>72480</v>
       </c>
       <c r="AC35" s="24" t="str">
-        <f>IF(AND($T35=6000, ($T35+$W35-$AB35)&gt;=6000),T35,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD35" s="24" t="str">
-        <f>IF(AND($T35=8000, ($T35+$W35-$AB35)&gt;=8000),T35,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE35" s="24" t="str">
-        <f>IF(($T35+$W35-$AB35)&gt;=$T35+8000,W35,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF35" s="25" t="str">
-        <f>IF(AB35&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5294,23 +5315,23 @@
         <v>0</v>
       </c>
       <c r="J36" s="24">
-        <f>(1-$D36)*E36</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K36" s="24">
-        <f>(1-$D36)*F36</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L36" s="24">
-        <f>G36</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M36" s="24">
-        <f>(1-$D36)*H36</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N36" s="24">
-        <f>(1-$D36)*I36</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O36" s="24">
@@ -5347,30 +5368,30 @@
         <v>0</v>
       </c>
       <c r="Z36" s="24">
-        <f>SUM(J36:Y36)</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AA36" s="24">
         <v>28000</v>
       </c>
       <c r="AB36" s="20">
-        <f>Z36-AA36</f>
+        <f t="shared" si="17"/>
         <v>15140</v>
       </c>
       <c r="AC36" s="24" t="str">
-        <f>IF(AND($T36=6000, ($T36+$W36-$AB36)&gt;=6000),T36,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD36" s="24" t="str">
-        <f>IF(AND($T36=8000, ($T36+$W36-$AB36)&gt;=8000),T36,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE36" s="24" t="str">
-        <f>IF(($T36+$W36-$AB36)&gt;=$T36+8000,W36,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF36" s="25" t="str">
-        <f>IF(AB36&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5403,23 +5424,23 @@
         <v>0</v>
       </c>
       <c r="J37" s="24">
-        <f>(1-$D37)*E37</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K37" s="24">
-        <f>(1-$D37)*F37</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L37" s="24">
-        <f>G37</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M37" s="24">
-        <f>(1-$D37)*H37</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N37" s="24">
-        <f>(1-$D37)*I37</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O37" s="24">
@@ -5456,30 +5477,30 @@
         <v>0</v>
       </c>
       <c r="Z37" s="24">
-        <f>SUM(J37:Y37)</f>
+        <f t="shared" si="16"/>
         <v>56930</v>
       </c>
       <c r="AA37" s="24">
         <v>0</v>
       </c>
       <c r="AB37" s="20">
-        <f>Z37-AA37</f>
+        <f t="shared" si="17"/>
         <v>56930</v>
       </c>
       <c r="AC37" s="24" t="str">
-        <f>IF(AND($T37=6000, ($T37+$W37-$AB37)&gt;=6000),T37,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD37" s="24" t="str">
-        <f>IF(AND($T37=8000, ($T37+$W37-$AB37)&gt;=8000),T37,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE37" s="24" t="str">
-        <f>IF(($T37+$W37-$AB37)&gt;=$T37+8000,W37,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF37" s="25" t="str">
-        <f>IF(AB37&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5512,23 +5533,23 @@
         <v>0</v>
       </c>
       <c r="J38" s="24">
-        <f>(1-$D38)*E38</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K38" s="24">
-        <f>(1-$D38)*F38</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L38" s="24">
-        <f>G38</f>
+        <f t="shared" si="13"/>
         <v>2000</v>
       </c>
       <c r="M38" s="24">
-        <f>(1-$D38)*H38</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N38" s="24">
-        <f>(1-$D38)*I38</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O38" s="24">
@@ -5565,30 +5586,30 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <f>SUM(J38:Y38)</f>
+        <f t="shared" si="16"/>
         <v>31050</v>
       </c>
       <c r="AA38" s="24">
         <v>0</v>
       </c>
       <c r="AB38" s="20">
-        <f>Z38-AA38</f>
+        <f t="shared" si="17"/>
         <v>31050</v>
       </c>
       <c r="AC38" s="24" t="str">
-        <f>IF(AND($T38=6000, ($T38+$W38-$AB38)&gt;=6000),T38,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD38" s="24" t="str">
-        <f>IF(AND($T38=8000, ($T38+$W38-$AB38)&gt;=8000),T38,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE38" s="24" t="str">
-        <f>IF(($T38+$W38-$AB38)&gt;=$T38+8000,W38,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF38" s="25" t="str">
-        <f>IF(AB38&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5621,23 +5642,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="24">
-        <f>(1-$D39)*E39</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K39" s="24">
-        <f>(1-$D39)*F39</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L39" s="24">
-        <f>G39</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M39" s="24">
-        <f>(1-$D39)*H39</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N39" s="24">
-        <f>(1-$D39)*I39</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O39" s="24">
@@ -5674,30 +5695,30 @@
         <v>0</v>
       </c>
       <c r="Z39" s="24">
-        <f>SUM(J39:Y39)</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AA39" s="24">
         <v>0</v>
       </c>
       <c r="AB39" s="20">
-        <f>Z39-AA39</f>
+        <f t="shared" si="17"/>
         <v>43140</v>
       </c>
       <c r="AC39" s="24" t="str">
-        <f>IF(AND($T39=6000, ($T39+$W39-$AB39)&gt;=6000),T39,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD39" s="24" t="str">
-        <f>IF(AND($T39=8000, ($T39+$W39-$AB39)&gt;=8000),T39,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE39" s="24" t="str">
-        <f>IF(($T39+$W39-$AB39)&gt;=$T39+8000,W39,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF39" s="25" t="str">
-        <f>IF(AB39&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5730,23 +5751,23 @@
         <v>6000</v>
       </c>
       <c r="J40" s="24">
-        <f>(1-$D40)*E40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K40" s="24">
-        <f>(1-$D40)*F40</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L40" s="24">
-        <f>G40</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M40" s="24">
-        <f>(1-$D40)*H40</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N40" s="24">
-        <f>(1-$D40)*I40</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O40" s="24">
@@ -5783,30 +5804,30 @@
         <v>-30</v>
       </c>
       <c r="Z40" s="24">
-        <f>SUM(J40:Y40)</f>
+        <f t="shared" si="16"/>
         <v>70200</v>
       </c>
       <c r="AA40" s="24">
         <v>0</v>
       </c>
       <c r="AB40" s="20">
-        <f>Z40-AA40</f>
+        <f t="shared" si="17"/>
         <v>70200</v>
       </c>
       <c r="AC40" s="24" t="str">
-        <f>IF(AND($T40=6000, ($T40+$W40-$AB40)&gt;=6000),T40,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD40" s="24" t="str">
-        <f>IF(AND($T40=8000, ($T40+$W40-$AB40)&gt;=8000),T40,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE40" s="24" t="str">
-        <f>IF(($T40+$W40-$AB40)&gt;=$T40+8000,W40,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF40" s="25" t="str">
-        <f>IF(AB40&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5839,23 +5860,23 @@
         <v>6000</v>
       </c>
       <c r="J41" s="24">
-        <f>(1-$D41)*E41</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K41" s="24">
-        <f>(1-$D41)*F41</f>
+        <f t="shared" si="12"/>
         <v>33000</v>
       </c>
       <c r="L41" s="24">
-        <f>G41</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M41" s="24">
-        <f>(1-$D41)*H41</f>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N41" s="24">
-        <f>(1-$D41)*I41</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O41" s="24">
@@ -5892,30 +5913,30 @@
         <v>-8970</v>
       </c>
       <c r="Z41" s="24">
-        <f>SUM(J41:Y41)</f>
+        <f t="shared" si="16"/>
         <v>73760</v>
       </c>
       <c r="AA41" s="24">
         <v>0</v>
       </c>
       <c r="AB41" s="20">
-        <f>Z41-AA41</f>
+        <f t="shared" si="17"/>
         <v>73760</v>
       </c>
       <c r="AC41" s="24" t="str">
-        <f>IF(AND($T41=6000, ($T41+$W41-$AB41)&gt;=6000),T41,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD41" s="24" t="str">
-        <f>IF(AND($T41=8000, ($T41+$W41-$AB41)&gt;=8000),T41,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE41" s="24" t="str">
-        <f>IF(($T41+$W41-$AB41)&gt;=$T41+8000,W41,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF41" s="25" t="str">
-        <f>IF(AB41&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -5948,23 +5969,23 @@
         <v>8000</v>
       </c>
       <c r="J42" s="24">
-        <f>(1-$D42)*E42</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K42" s="24">
-        <f>(1-$D42)*F42</f>
+        <f t="shared" si="12"/>
         <v>40000</v>
       </c>
       <c r="L42" s="24">
-        <f>G42</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M42" s="24">
-        <f>(1-$D42)*H42</f>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N42" s="24">
-        <f>(1-$D42)*I42</f>
+        <f t="shared" si="15"/>
         <v>8000</v>
       </c>
       <c r="O42" s="24">
@@ -6001,30 +6022,30 @@
         <v>120</v>
       </c>
       <c r="Z42" s="24">
-        <f>SUM(J42:Y42)</f>
+        <f t="shared" si="16"/>
         <v>81330</v>
       </c>
       <c r="AA42" s="24">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AB42" s="20">
-        <f>Z42-AA42</f>
-        <v>81330</v>
+        <f t="shared" si="17"/>
+        <v>31330</v>
       </c>
       <c r="AC42" s="24" t="str">
-        <f>IF(AND($T42=6000, ($T42+$W42-$AB42)&gt;=6000),T42,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD42" s="24" t="str">
-        <f>IF(AND($T42=8000, ($T42+$W42-$AB42)&gt;=8000),T42,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE42" s="24" t="str">
-        <f>IF(($T42+$W42-$AB42)&gt;=$T42+8000,W42,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF42" s="25" t="str">
-        <f>IF(AB42&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6057,23 +6078,23 @@
         <v>6000</v>
       </c>
       <c r="J43" s="24">
-        <f>(1-$D43)*E43</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K43" s="24">
-        <f>(1-$D43)*F43</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L43" s="24">
-        <f>G43</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M43" s="24">
-        <f>(1-$D43)*H43</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N43" s="24">
-        <f>(1-$D43)*I43</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O43" s="24">
@@ -6110,30 +6131,30 @@
         <v>480</v>
       </c>
       <c r="Z43" s="24">
-        <f>SUM(J43:Y43)</f>
+        <f t="shared" si="16"/>
         <v>62710</v>
       </c>
       <c r="AA43" s="24">
         <v>0</v>
       </c>
       <c r="AB43" s="20">
-        <f>Z43-AA43</f>
+        <f t="shared" si="17"/>
         <v>62710</v>
       </c>
       <c r="AC43" s="24" t="str">
-        <f>IF(AND($T43=6000, ($T43+$W43-$AB43)&gt;=6000),T43,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD43" s="24" t="str">
-        <f>IF(AND($T43=8000, ($T43+$W43-$AB43)&gt;=8000),T43,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE43" s="24" t="str">
-        <f>IF(($T43+$W43-$AB43)&gt;=$T43+8000,W43,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF43" s="25" t="str">
-        <f>IF(AB43&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6166,23 +6187,23 @@
         <v>6000</v>
       </c>
       <c r="J44" s="24">
-        <f>(1-$D44)*E44</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K44" s="24">
-        <f>(1-$D44)*F44</f>
+        <f t="shared" si="12"/>
         <v>24750</v>
       </c>
       <c r="L44" s="24">
-        <f>G44</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M44" s="24">
-        <f>(1-$D44)*H44</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N44" s="24">
-        <f>(1-$D44)*I44</f>
+        <f t="shared" si="15"/>
         <v>4500</v>
       </c>
       <c r="O44" s="24">
@@ -6219,30 +6240,30 @@
         <v>0</v>
       </c>
       <c r="Z44" s="24">
-        <f>SUM(J44:Y44)</f>
+        <f t="shared" si="16"/>
         <v>72480</v>
       </c>
       <c r="AA44" s="24">
         <v>0</v>
       </c>
       <c r="AB44" s="20">
-        <f>Z44-AA44</f>
+        <f t="shared" si="17"/>
         <v>72480</v>
       </c>
       <c r="AC44" s="24" t="str">
-        <f>IF(AND($T44=6000, ($T44+$W44-$AB44)&gt;=6000),T44,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD44" s="24" t="str">
-        <f>IF(AND($T44=8000, ($T44+$W44-$AB44)&gt;=8000),T44,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE44" s="24" t="str">
-        <f>IF(($T44+$W44-$AB44)&gt;=$T44+8000,W44,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF44" s="25" t="str">
-        <f>IF(AB44&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6275,23 +6296,23 @@
         <v>8000</v>
       </c>
       <c r="J45" s="24">
-        <f>(1-$D45)*E45</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K45" s="24">
-        <f>(1-$D45)*F45</f>
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="L45" s="24">
-        <f>G45</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M45" s="24">
-        <f>(1-$D45)*H45</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N45" s="24">
-        <f>(1-$D45)*I45</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O45" s="24">
@@ -6328,30 +6349,30 @@
         <v>0</v>
       </c>
       <c r="Z45" s="24">
-        <f>SUM(J45:Y45)</f>
+        <f t="shared" si="16"/>
         <v>68710</v>
       </c>
       <c r="AA45" s="24">
         <v>0</v>
       </c>
       <c r="AB45" s="20">
-        <f>Z45-AA45</f>
+        <f t="shared" si="17"/>
         <v>68710</v>
       </c>
       <c r="AC45" s="24" t="str">
-        <f>IF(AND($T45=6000, ($T45+$W45-$AB45)&gt;=6000),T45,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD45" s="24" t="str">
-        <f>IF(AND($T45=8000, ($T45+$W45-$AB45)&gt;=8000),T45,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE45" s="24" t="str">
-        <f>IF(($T45+$W45-$AB45)&gt;=$T45+8000,W45,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF45" s="25" t="str">
-        <f>IF(AB45&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6384,23 +6405,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="24">
-        <f>(1-$D46)*E46</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K46" s="24">
-        <f>(1-$D46)*F46</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L46" s="24">
-        <f>G46</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M46" s="24">
-        <f>(1-$D46)*H46</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N46" s="24">
-        <f>(1-$D46)*I46</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O46" s="24">
@@ -6437,30 +6458,30 @@
         <v>0</v>
       </c>
       <c r="Z46" s="24">
-        <f>SUM(J46:Y46)</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AA46" s="24">
         <v>0</v>
       </c>
       <c r="AB46" s="20">
-        <f>Z46-AA46</f>
+        <f t="shared" si="17"/>
         <v>43140</v>
       </c>
       <c r="AC46" s="24" t="str">
-        <f>IF(AND($T46=6000, ($T46+$W46-$AB46)&gt;=6000),T46,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD46" s="24" t="str">
-        <f>IF(AND($T46=8000, ($T46+$W46-$AB46)&gt;=8000),T46,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE46" s="24" t="str">
-        <f>IF(($T46+$W46-$AB46)&gt;=$T46+8000,W46,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF46" s="25" t="str">
-        <f>IF(AB46&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6493,23 +6514,23 @@
         <v>0</v>
       </c>
       <c r="J47" s="24">
-        <f>(1-$D47)*E47</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K47" s="24">
-        <f>(1-$D47)*F47</f>
+        <f t="shared" si="12"/>
         <v>19500</v>
       </c>
       <c r="L47" s="24">
-        <f>G47</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M47" s="24">
-        <f>(1-$D47)*H47</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N47" s="24">
-        <f>(1-$D47)*I47</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O47" s="24">
@@ -6546,30 +6567,30 @@
         <v>18500</v>
       </c>
       <c r="Z47" s="24">
-        <f>SUM(J47:Y47)</f>
+        <f t="shared" si="16"/>
         <v>83660</v>
       </c>
       <c r="AA47" s="24">
         <v>48000</v>
       </c>
       <c r="AB47" s="20">
-        <f>Z47-AA47</f>
+        <f t="shared" si="17"/>
         <v>35660</v>
       </c>
       <c r="AC47" s="24" t="str">
-        <f>IF(AND($T47=6000, ($T47+$W47-$AB47)&gt;=6000),T47,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD47" s="24" t="str">
-        <f>IF(AND($T47=8000, ($T47+$W47-$AB47)&gt;=8000),T47,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE47" s="24" t="str">
-        <f>IF(($T47+$W47-$AB47)&gt;=$T47+8000,W47,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF47" s="25" t="str">
-        <f>IF(AB47&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6602,23 +6623,23 @@
         <v>5000</v>
       </c>
       <c r="J48" s="24">
-        <f>(1-$D48)*E48</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K48" s="24">
-        <f>(1-$D48)*F48</f>
+        <f t="shared" si="12"/>
         <v>26600</v>
       </c>
       <c r="L48" s="24">
-        <f>G48</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M48" s="24">
-        <f>(1-$D48)*H48</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N48" s="24">
-        <f>(1-$D48)*I48</f>
+        <f t="shared" si="15"/>
         <v>4750</v>
       </c>
       <c r="O48" s="24">
@@ -6655,30 +6676,30 @@
         <v>0</v>
       </c>
       <c r="Z48" s="24">
-        <f>SUM(J48:Y48)</f>
+        <f t="shared" si="16"/>
         <v>77370</v>
       </c>
       <c r="AA48" s="24">
         <v>79020</v>
       </c>
       <c r="AB48" s="20">
-        <f>Z48-AA48</f>
+        <f t="shared" si="17"/>
         <v>-1650</v>
       </c>
       <c r="AC48" s="24" t="str">
-        <f>IF(AND($T48=6000, ($T48+$W48-$AB48)&gt;=6000),T48,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD48" s="24" t="str">
-        <f>IF(AND($T48=8000, ($T48+$W48-$AB48)&gt;=8000),T48,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE48" s="24" t="str">
-        <f>IF(($T48+$W48-$AB48)&gt;=$T48+8000,W48,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF48" s="25" t="str">
-        <f>IF(AB48&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -6711,23 +6732,23 @@
         <v>5000</v>
       </c>
       <c r="J49" s="24">
-        <f>(1-$D49)*E49</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K49" s="24">
-        <f>(1-$D49)*F49</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L49" s="24">
-        <f>G49</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M49" s="24">
-        <f>(1-$D49)*H49</f>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N49" s="24">
-        <f>(1-$D49)*I49</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O49" s="24">
@@ -6764,30 +6785,30 @@
         <v>0</v>
       </c>
       <c r="Z49" s="24">
-        <f>SUM(J49:Y49)</f>
+        <f t="shared" si="16"/>
         <v>82800</v>
       </c>
       <c r="AA49" s="24">
         <v>42350</v>
       </c>
       <c r="AB49" s="20">
-        <f>Z49-AA49</f>
+        <f t="shared" si="17"/>
         <v>40450</v>
       </c>
       <c r="AC49" s="24" t="str">
-        <f>IF(AND($T49=6000, ($T49+$W49-$AB49)&gt;=6000),T49,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD49" s="24" t="str">
-        <f>IF(AND($T49=8000, ($T49+$W49-$AB49)&gt;=8000),T49,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE49" s="24" t="str">
-        <f>IF(($T49+$W49-$AB49)&gt;=$T49+8000,W49,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF49" s="25" t="str">
-        <f>IF(AB49&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6820,23 +6841,23 @@
         <v>6000</v>
       </c>
       <c r="J50" s="24">
-        <f>(1-$D50)*E50</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K50" s="24">
-        <f>(1-$D50)*F50</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L50" s="24">
-        <f>G50</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M50" s="24">
-        <f>(1-$D50)*H50</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N50" s="24">
-        <f>(1-$D50)*I50</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O50" s="24">
@@ -6873,30 +6894,30 @@
         <v>500</v>
       </c>
       <c r="Z50" s="24">
-        <f>SUM(J50:Y50)</f>
+        <f t="shared" si="16"/>
         <v>62730</v>
       </c>
       <c r="AA50" s="24">
         <v>0</v>
       </c>
       <c r="AB50" s="20">
-        <f>Z50-AA50</f>
+        <f t="shared" si="17"/>
         <v>62730</v>
       </c>
       <c r="AC50" s="24" t="str">
-        <f>IF(AND($T50=6000, ($T50+$W50-$AB50)&gt;=6000),T50,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD50" s="24" t="str">
-        <f>IF(AND($T50=8000, ($T50+$W50-$AB50)&gt;=8000),T50,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE50" s="24" t="str">
-        <f>IF(($T50+$W50-$AB50)&gt;=$T50+8000,W50,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF50" s="25" t="str">
-        <f>IF(AB50&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6929,23 +6950,23 @@
         <v>5000</v>
       </c>
       <c r="J51" s="24">
-        <f>(1-$D51)*E51</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K51" s="24">
-        <f>(1-$D51)*F51</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L51" s="24">
-        <f>G51</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M51" s="24">
-        <f>(1-$D51)*H51</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N51" s="24">
-        <f>(1-$D51)*I51</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O51" s="24">
@@ -6982,30 +7003,30 @@
         <v>22105</v>
       </c>
       <c r="Z51" s="24">
-        <f>SUM(J51:Y51)</f>
+        <f t="shared" si="16"/>
         <v>94335</v>
       </c>
       <c r="AA51" s="24">
         <v>0</v>
       </c>
       <c r="AB51" s="20">
-        <f>Z51-AA51</f>
+        <f t="shared" si="17"/>
         <v>94335</v>
       </c>
       <c r="AC51" s="24" t="str">
-        <f>IF(AND($T51=6000, ($T51+$W51-$AB51)&gt;=6000),T51,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD51" s="24" t="str">
-        <f>IF(AND($T51=8000, ($T51+$W51-$AB51)&gt;=8000),T51,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE51" s="24" t="str">
-        <f>IF(($T51+$W51-$AB51)&gt;=$T51+8000,W51,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF51" s="25" t="str">
-        <f>IF(AB51&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7038,23 +7059,23 @@
         <v>5000</v>
       </c>
       <c r="J52" s="24">
-        <f>(1-$D52)*E52</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K52" s="24">
-        <f>(1-$D52)*F52</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L52" s="24">
-        <f>G52</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M52" s="24">
-        <f>(1-$D52)*H52</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N52" s="24">
-        <f>(1-$D52)*I52</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O52" s="24">
@@ -7091,30 +7112,30 @@
         <v>24395</v>
       </c>
       <c r="Z52" s="24">
-        <f>SUM(J52:Y52)</f>
+        <f t="shared" si="16"/>
         <v>101165</v>
       </c>
       <c r="AA52" s="24">
         <v>0</v>
       </c>
       <c r="AB52" s="20">
-        <f>Z52-AA52</f>
+        <f t="shared" si="17"/>
         <v>101165</v>
       </c>
       <c r="AC52" s="24" t="str">
-        <f>IF(AND($T52=6000, ($T52+$W52-$AB52)&gt;=6000),T52,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD52" s="24" t="str">
-        <f>IF(AND($T52=8000, ($T52+$W52-$AB52)&gt;=8000),T52,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE52" s="24" t="str">
-        <f>IF(($T52+$W52-$AB52)&gt;=$T52+8000,W52,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF52" s="25" t="str">
-        <f>IF(AB52&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7147,23 +7168,23 @@
         <v>0</v>
       </c>
       <c r="J53" s="24">
-        <f>(1-$D53)*E53</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K53" s="24">
-        <f>(1-$D53)*F53</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L53" s="24">
-        <f>G53</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M53" s="24">
-        <f>(1-$D53)*H53</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N53" s="24">
-        <f>(1-$D53)*I53</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O53" s="24">
@@ -7200,30 +7221,30 @@
         <v>0</v>
       </c>
       <c r="Z53" s="24">
-        <f>SUM(J53:Y53)</f>
+        <f t="shared" si="16"/>
         <v>51030</v>
       </c>
       <c r="AA53" s="24">
         <v>0</v>
       </c>
       <c r="AB53" s="20">
-        <f>Z53-AA53</f>
+        <f t="shared" si="17"/>
         <v>51030</v>
       </c>
       <c r="AC53" s="24" t="str">
-        <f>IF(AND($T53=6000, ($T53+$W53-$AB53)&gt;=6000),T53,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD53" s="24" t="str">
-        <f>IF(AND($T53=8000, ($T53+$W53-$AB53)&gt;=8000),T53,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE53" s="24" t="str">
-        <f>IF(($T53+$W53-$AB53)&gt;=$T53+8000,W53,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF53" s="25" t="str">
-        <f>IF(AB53&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7256,23 +7277,23 @@
         <v>0</v>
       </c>
       <c r="J54" s="24">
-        <f>(1-$D54)*E54</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K54" s="24">
-        <f>(1-$D54)*F54</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L54" s="24">
-        <f>G54</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M54" s="24">
-        <f>(1-$D54)*H54</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N54" s="24">
-        <f>(1-$D54)*I54</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O54" s="24">
@@ -7309,30 +7330,30 @@
         <v>2000</v>
       </c>
       <c r="Z54" s="24">
-        <f>SUM(J54:Y54)</f>
+        <f t="shared" si="16"/>
         <v>45140</v>
       </c>
       <c r="AA54" s="24">
         <v>39840</v>
       </c>
       <c r="AB54" s="20">
-        <f>Z54-AA54</f>
+        <f t="shared" si="17"/>
         <v>5300</v>
       </c>
       <c r="AC54" s="24" t="str">
-        <f>IF(AND($T54=6000, ($T54+$W54-$AB54)&gt;=6000),T54,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD54" s="24" t="str">
-        <f>IF(AND($T54=8000, ($T54+$W54-$AB54)&gt;=8000),T54,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE54" s="24" t="str">
-        <f>IF(($T54+$W54-$AB54)&gt;=$T54+8000,W54,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF54" s="25" t="str">
-        <f>IF(AB54&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7363,23 +7384,23 @@
         <v>6000</v>
       </c>
       <c r="J55" s="24">
-        <f>(1-$D55)*E55</f>
+        <f t="shared" si="11"/>
         <v>2250</v>
       </c>
       <c r="K55" s="24">
-        <f>(1-$D55)*F55</f>
+        <f t="shared" si="12"/>
         <v>24750</v>
       </c>
       <c r="L55" s="24">
-        <f>G55</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M55" s="24">
-        <f>(1-$D55)*H55</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N55" s="24">
-        <f>(1-$D55)*I55</f>
+        <f t="shared" si="15"/>
         <v>4500</v>
       </c>
       <c r="O55" s="24">
@@ -7416,30 +7437,30 @@
         <v>0</v>
       </c>
       <c r="Z55" s="24">
-        <f>SUM(J55:Y55)</f>
+        <f t="shared" si="16"/>
         <v>102730</v>
       </c>
       <c r="AA55" s="24">
         <v>100000</v>
       </c>
       <c r="AB55" s="20">
-        <f>Z55-AA55</f>
+        <f t="shared" si="17"/>
         <v>2730</v>
       </c>
       <c r="AC55" s="24" t="str">
-        <f>IF(AND($T55=6000, ($T55+$W55-$AB55)&gt;=6000),T55,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD55" s="24" t="str">
-        <f>IF(AND($T55=8000, ($T55+$W55-$AB55)&gt;=8000),T55,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE55" s="24" t="str">
-        <f>IF(($T55+$W55-$AB55)&gt;=$T55+8000,W55,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF55" s="25" t="str">
-        <f>IF(AB55&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7470,23 +7491,23 @@
         <v>8000</v>
       </c>
       <c r="J56" s="24">
-        <f>(1-$D56)*E56</f>
+        <f t="shared" si="11"/>
         <v>2250</v>
       </c>
       <c r="K56" s="24">
-        <f>(1-$D56)*F56</f>
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="L56" s="24">
-        <f>G56</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M56" s="24">
-        <f>(1-$D56)*H56</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N56" s="24">
-        <f>(1-$D56)*I56</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O56" s="24">
@@ -7523,30 +7544,30 @@
         <v>0</v>
       </c>
       <c r="Z56" s="24">
-        <f>SUM(J56:Y56)</f>
+        <f t="shared" si="16"/>
         <v>106960</v>
       </c>
       <c r="AA56" s="24">
         <v>100000</v>
       </c>
       <c r="AB56" s="20">
-        <f>Z56-AA56</f>
+        <f t="shared" si="17"/>
         <v>6960</v>
       </c>
       <c r="AC56" s="24" t="str">
-        <f>IF(AND($T56=6000, ($T56+$W56-$AB56)&gt;=6000),T56,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD56" s="24" t="str">
-        <f>IF(AND($T56=8000, ($T56+$W56-$AB56)&gt;=8000),T56,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE56" s="24" t="str">
-        <f>IF(($T56+$W56-$AB56)&gt;=$T56+8000,W56,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF56" s="25" t="str">
-        <f>IF(AB56&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7579,23 +7600,23 @@
         <v>0</v>
       </c>
       <c r="J57" s="24">
-        <f>(1-$D57)*E57</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K57" s="24">
-        <f>(1-$D57)*F57</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L57" s="24">
-        <f>G57</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M57" s="24">
-        <f>(1-$D57)*H57</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N57" s="24">
-        <f>(1-$D57)*I57</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O57" s="24">
@@ -7632,30 +7653,30 @@
         <v>0</v>
       </c>
       <c r="Z57" s="24">
-        <f>SUM(J57:Y57)</f>
+        <f t="shared" si="16"/>
         <v>56930</v>
       </c>
       <c r="AA57" s="24">
         <v>0</v>
       </c>
       <c r="AB57" s="20">
-        <f>Z57-AA57</f>
+        <f t="shared" si="17"/>
         <v>56930</v>
       </c>
       <c r="AC57" s="24" t="str">
-        <f>IF(AND($T57=6000, ($T57+$W57-$AB57)&gt;=6000),T57,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD57" s="24" t="str">
-        <f>IF(AND($T57=8000, ($T57+$W57-$AB57)&gt;=8000),T57,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE57" s="24" t="str">
-        <f>IF(($T57+$W57-$AB57)&gt;=$T57+8000,W57,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF57" s="25" t="str">
-        <f>IF(AB57&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7688,23 +7709,23 @@
         <v>5000</v>
       </c>
       <c r="J58" s="24">
-        <f>(1-$D58)*E58</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K58" s="24">
-        <f>(1-$D58)*F58</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L58" s="24">
-        <f>G58</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M58" s="24">
-        <f>(1-$D58)*H58</f>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N58" s="24">
-        <f>(1-$D58)*I58</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O58" s="24">
@@ -7741,30 +7762,30 @@
         <v>0</v>
       </c>
       <c r="Z58" s="24">
-        <f>SUM(J58:Y58)</f>
+        <f t="shared" si="16"/>
         <v>76800</v>
       </c>
       <c r="AA58" s="24">
         <v>0</v>
       </c>
       <c r="AB58" s="20">
-        <f>Z58-AA58</f>
+        <f t="shared" si="17"/>
         <v>76800</v>
       </c>
       <c r="AC58" s="24" t="str">
-        <f>IF(AND($T58=6000, ($T58+$W58-$AB58)&gt;=6000),T58,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD58" s="24" t="str">
-        <f>IF(AND($T58=8000, ($T58+$W58-$AB58)&gt;=8000),T58,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE58" s="24" t="str">
-        <f>IF(($T58+$W58-$AB58)&gt;=$T58+8000,W58,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF58" s="25" t="str">
-        <f>IF(AB58&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7797,23 +7818,23 @@
         <v>0</v>
       </c>
       <c r="J59" s="24">
-        <f>(1-$D59)*E59</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K59" s="24">
-        <f>(1-$D59)*F59</f>
+        <f t="shared" si="12"/>
         <v>19500</v>
       </c>
       <c r="L59" s="24">
-        <f>G59</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M59" s="24">
-        <f>(1-$D59)*H59</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N59" s="24">
-        <f>(1-$D59)*I59</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O59" s="24">
@@ -7850,30 +7871,30 @@
         <v>0</v>
       </c>
       <c r="Z59" s="24">
-        <f>SUM(J59:Y59)</f>
+        <f t="shared" si="16"/>
         <v>44430</v>
       </c>
       <c r="AA59" s="24">
         <v>0</v>
       </c>
       <c r="AB59" s="20">
-        <f>Z59-AA59</f>
+        <f t="shared" si="17"/>
         <v>44430</v>
       </c>
       <c r="AC59" s="24" t="str">
-        <f>IF(AND($T59=6000, ($T59+$W59-$AB59)&gt;=6000),T59,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD59" s="24" t="str">
-        <f>IF(AND($T59=8000, ($T59+$W59-$AB59)&gt;=8000),T59,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE59" s="24" t="str">
-        <f>IF(($T59+$W59-$AB59)&gt;=$T59+8000,W59,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF59" s="25" t="str">
-        <f>IF(AB59&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7906,23 +7927,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="24">
-        <f>(1-$D60)*E60</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K60" s="24">
-        <f>(1-$D60)*F60</f>
+        <f t="shared" si="12"/>
         <v>24700</v>
       </c>
       <c r="L60" s="24">
-        <f>G60</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M60" s="24">
-        <f>(1-$D60)*H60</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N60" s="24">
-        <f>(1-$D60)*I60</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O60" s="24">
@@ -7959,30 +7980,30 @@
         <v>1000</v>
       </c>
       <c r="Z60" s="24">
-        <f>SUM(J60:Y60)</f>
+        <f t="shared" si="16"/>
         <v>50630</v>
       </c>
       <c r="AA60" s="24">
         <v>51930</v>
       </c>
       <c r="AB60" s="20">
-        <f>Z60-AA60</f>
+        <f t="shared" si="17"/>
         <v>-1300</v>
       </c>
       <c r="AC60" s="24" t="str">
-        <f>IF(AND($T60=6000, ($T60+$W60-$AB60)&gt;=6000),T60,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD60" s="24" t="str">
-        <f>IF(AND($T60=8000, ($T60+$W60-$AB60)&gt;=8000),T60,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE60" s="24" t="str">
-        <f>IF(($T60+$W60-$AB60)&gt;=$T60+8000,W60,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF60" s="25" t="str">
-        <f>IF(AB60&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -8015,23 +8036,23 @@
         <v>5000</v>
       </c>
       <c r="J61" s="24">
-        <f>(1-$D61)*E61</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K61" s="24">
-        <f>(1-$D61)*F61</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L61" s="24">
-        <f>G61</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M61" s="24">
-        <f>(1-$D61)*H61</f>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N61" s="24">
-        <f>(1-$D61)*I61</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O61" s="24">
@@ -8068,30 +8089,30 @@
         <v>550</v>
       </c>
       <c r="Z61" s="24">
-        <f>SUM(J61:Y61)</f>
+        <f t="shared" si="16"/>
         <v>77350</v>
       </c>
       <c r="AA61" s="24">
         <v>0</v>
       </c>
       <c r="AB61" s="20">
-        <f>Z61-AA61</f>
+        <f t="shared" si="17"/>
         <v>77350</v>
       </c>
       <c r="AC61" s="24" t="str">
-        <f>IF(AND($T61=6000, ($T61+$W61-$AB61)&gt;=6000),T61,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD61" s="24" t="str">
-        <f>IF(AND($T61=8000, ($T61+$W61-$AB61)&gt;=8000),T61,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE61" s="24" t="str">
-        <f>IF(($T61+$W61-$AB61)&gt;=$T61+8000,W61,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF61" s="25" t="str">
-        <f>IF(AB61&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8124,23 +8145,23 @@
         <v>5000</v>
       </c>
       <c r="J62" s="24">
-        <f>(1-$D62)*E62</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K62" s="24">
-        <f>(1-$D62)*F62</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L62" s="24">
-        <f>G62</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M62" s="24">
-        <f>(1-$D62)*H62</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N62" s="24">
-        <f>(1-$D62)*I62</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O62" s="24">
@@ -8177,30 +8198,30 @@
         <v>0</v>
       </c>
       <c r="Z62" s="24">
-        <f>SUM(J62:Y62)</f>
+        <f t="shared" si="16"/>
         <v>77540</v>
       </c>
       <c r="AA62" s="24">
         <v>0</v>
       </c>
       <c r="AB62" s="20">
-        <f>Z62-AA62</f>
+        <f t="shared" si="17"/>
         <v>77540</v>
       </c>
       <c r="AC62" s="24" t="str">
-        <f>IF(AND($T62=6000, ($T62+$W62-$AB62)&gt;=6000),T62,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD62" s="24" t="str">
-        <f>IF(AND($T62=8000, ($T62+$W62-$AB62)&gt;=8000),T62,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE62" s="24" t="str">
-        <f>IF(($T62+$W62-$AB62)&gt;=$T62+8000,W62,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF62" s="25" t="str">
-        <f>IF(AB62&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8233,23 +8254,23 @@
         <v>6000</v>
       </c>
       <c r="J63" s="24">
-        <f>(1-$D63)*E63</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K63" s="24">
-        <f>(1-$D63)*F63</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L63" s="24">
-        <f>G63</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M63" s="24">
-        <f>(1-$D63)*H63</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N63" s="24">
-        <f>(1-$D63)*I63</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O63" s="24">
@@ -8286,30 +8307,30 @@
         <v>0</v>
       </c>
       <c r="Z63" s="24">
-        <f>SUM(J63:Y63)</f>
+        <f t="shared" si="16"/>
         <v>62230</v>
       </c>
       <c r="AA63" s="24">
         <v>0</v>
       </c>
       <c r="AB63" s="20">
-        <f>Z63-AA63</f>
+        <f t="shared" si="17"/>
         <v>62230</v>
       </c>
       <c r="AC63" s="24" t="str">
-        <f>IF(AND($T63=6000, ($T63+$W63-$AB63)&gt;=6000),T63,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD63" s="24" t="str">
-        <f>IF(AND($T63=8000, ($T63+$W63-$AB63)&gt;=8000),T63,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE63" s="24" t="str">
-        <f>IF(($T63+$W63-$AB63)&gt;=$T63+8000,W63,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF63" s="25" t="str">
-        <f>IF(AB63&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8342,23 +8363,23 @@
         <v>5000</v>
       </c>
       <c r="J64" s="24">
-        <f>(1-$D64)*E64</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K64" s="24">
-        <f>(1-$D64)*F64</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L64" s="24">
-        <f>G64</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M64" s="24">
-        <f>(1-$D64)*H64</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N64" s="24">
-        <f>(1-$D64)*I64</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O64" s="24">
@@ -8395,30 +8416,30 @@
         <v>0</v>
       </c>
       <c r="Z64" s="24">
-        <f>SUM(J64:Y64)</f>
+        <f t="shared" si="16"/>
         <v>69310</v>
       </c>
       <c r="AA64" s="24">
         <v>0</v>
       </c>
       <c r="AB64" s="20">
-        <f>Z64-AA64</f>
+        <f t="shared" si="17"/>
         <v>69310</v>
       </c>
       <c r="AC64" s="24" t="str">
-        <f>IF(AND($T64=6000, ($T64+$W64-$AB64)&gt;=6000),T64,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD64" s="24" t="str">
-        <f>IF(AND($T64=8000, ($T64+$W64-$AB64)&gt;=8000),T64,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE64" s="24" t="str">
-        <f>IF(($T64+$W64-$AB64)&gt;=$T64+8000,W64,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF64" s="25" t="str">
-        <f>IF(AB64&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8451,23 +8472,23 @@
         <v>6000</v>
       </c>
       <c r="J65" s="24">
-        <f>(1-$D65)*E65</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K65" s="24">
-        <f>(1-$D65)*F65</f>
+        <f t="shared" si="12"/>
         <v>33000</v>
       </c>
       <c r="L65" s="24">
-        <f>G65</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M65" s="24">
-        <f>(1-$D65)*H65</f>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N65" s="24">
-        <f>(1-$D65)*I65</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O65" s="24">
@@ -8504,30 +8525,30 @@
         <v>0</v>
       </c>
       <c r="Z65" s="24">
-        <f>SUM(J65:Y65)</f>
+        <f t="shared" si="16"/>
         <v>79830</v>
       </c>
       <c r="AA65" s="24">
         <v>0</v>
       </c>
       <c r="AB65" s="20">
-        <f>Z65-AA65</f>
+        <f t="shared" si="17"/>
         <v>79830</v>
       </c>
       <c r="AC65" s="24" t="str">
-        <f>IF(AND($T65=6000, ($T65+$W65-$AB65)&gt;=6000),T65,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD65" s="24" t="str">
-        <f>IF(AND($T65=8000, ($T65+$W65-$AB65)&gt;=8000),T65,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE65" s="24" t="str">
-        <f>IF(($T65+$W65-$AB65)&gt;=$T65+8000,W65,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF65" s="25" t="str">
-        <f>IF(AB65&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8542,7 +8563,7 @@
         <v>49</v>
       </c>
       <c r="D66" s="23">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E66" s="24">
         <v>0</v>
@@ -8560,23 +8581,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="24">
-        <f>(1-$D66)*E66</f>
+        <f t="shared" ref="J66:J97" si="21">(1-$D66)*E66</f>
         <v>0</v>
       </c>
       <c r="K66" s="24">
-        <f>(1-$D66)*F66</f>
-        <v>13000</v>
+        <f t="shared" ref="K66:K97" si="22">(1-$D66)*F66</f>
+        <v>11699.999999999998</v>
       </c>
       <c r="L66" s="24">
-        <f>G66</f>
+        <f t="shared" ref="L66:L97" si="23">G66</f>
         <v>4000</v>
       </c>
       <c r="M66" s="24">
-        <f>(1-$D66)*H66</f>
-        <v>500</v>
+        <f t="shared" ref="M66:M97" si="24">(1-$D66)*H66</f>
+        <v>449.99999999999994</v>
       </c>
       <c r="N66" s="24">
-        <f>(1-$D66)*I66</f>
+        <f t="shared" ref="N66:N97" si="25">(1-$D66)*I66</f>
         <v>0</v>
       </c>
       <c r="O66" s="24">
@@ -8613,31 +8634,31 @@
         <v>0</v>
       </c>
       <c r="Z66" s="24">
-        <f>SUM(J66:Y66)</f>
+        <f t="shared" ref="Z66:Z97" si="26">SUM(J66:Y66)</f>
+        <v>28290</v>
+      </c>
+      <c r="AA66" s="24">
         <v>29640</v>
       </c>
-      <c r="AA66" s="24">
-        <v>20000</v>
-      </c>
       <c r="AB66" s="20">
-        <f>Z66-AA66</f>
-        <v>9640</v>
+        <f t="shared" ref="AB66:AB97" si="27">Z66-AA66</f>
+        <v>-1350</v>
       </c>
       <c r="AC66" s="24" t="str">
-        <f>IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
+        <f t="shared" ref="AC66:AC97" si="28">IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
         <v/>
       </c>
       <c r="AD66" s="24" t="str">
-        <f>IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
+        <f t="shared" ref="AD66:AD97" si="29">IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
         <v/>
       </c>
       <c r="AE66" s="24" t="str">
-        <f>IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
+        <f t="shared" ref="AE66:AE97" si="30">IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
         <v/>
       </c>
       <c r="AF66" s="25" t="str">
-        <f>IF(AB66&lt;=0,"BONUS","")</f>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
@@ -8669,23 +8690,23 @@
         <v>0</v>
       </c>
       <c r="J67" s="24">
-        <f>(1-$D67)*E67</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K67" s="24">
-        <f>(1-$D67)*F67</f>
+        <f t="shared" si="22"/>
         <v>13000</v>
       </c>
       <c r="L67" s="24">
-        <f>G67</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M67" s="24">
-        <f>(1-$D67)*H67</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N67" s="24">
-        <f>(1-$D67)*I67</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O67" s="24">
@@ -8722,30 +8743,30 @@
         <v>8000</v>
       </c>
       <c r="Z67" s="24">
-        <f>SUM(J67:Y67)</f>
+        <f t="shared" si="26"/>
         <v>45930</v>
       </c>
       <c r="AA67" s="24">
         <v>0</v>
       </c>
       <c r="AB67" s="20">
-        <f>Z67-AA67</f>
+        <f t="shared" si="27"/>
         <v>45930</v>
       </c>
       <c r="AC67" s="24" t="str">
-        <f>IF(AND($T67=6000, ($T67+$W67-$AB67)&gt;=6000),T67,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD67" s="24" t="str">
-        <f>IF(AND($T67=8000, ($T67+$W67-$AB67)&gt;=8000),T67,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE67" s="24" t="str">
-        <f>IF(($T67+$W67-$AB67)&gt;=$T67+8000,W67,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF67" s="25" t="str">
-        <f>IF(AB67&lt;=0,"BONUS","")</f>
+        <f t="shared" ref="AF67:AF125" si="31">IF(AB67&lt;=0,"BONUS","")</f>
         <v/>
       </c>
     </row>
@@ -8778,23 +8799,23 @@
         <v>0</v>
       </c>
       <c r="J68" s="24">
-        <f>(1-$D68)*E68</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K68" s="24">
-        <f>(1-$D68)*F68</f>
+        <f t="shared" si="22"/>
         <v>13000</v>
       </c>
       <c r="L68" s="24">
-        <f>G68</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M68" s="24">
-        <f>(1-$D68)*H68</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N68" s="24">
-        <f>(1-$D68)*I68</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O68" s="24">
@@ -8831,30 +8852,30 @@
         <v>8000</v>
       </c>
       <c r="Z68" s="24">
-        <f>SUM(J68:Y68)</f>
+        <f t="shared" si="26"/>
         <v>45930</v>
       </c>
       <c r="AA68" s="24">
         <v>0</v>
       </c>
       <c r="AB68" s="20">
-        <f>Z68-AA68</f>
+        <f t="shared" si="27"/>
         <v>45930</v>
       </c>
       <c r="AC68" s="24" t="str">
-        <f>IF(AND($T68=6000, ($T68+$W68-$AB68)&gt;=6000),T68,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD68" s="24" t="str">
-        <f>IF(AND($T68=8000, ($T68+$W68-$AB68)&gt;=8000),T68,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE68" s="24" t="str">
-        <f>IF(($T68+$W68-$AB68)&gt;=$T68+8000,W68,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF68" s="25" t="str">
-        <f>IF(AB68&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -8887,23 +8908,23 @@
         <v>5000</v>
       </c>
       <c r="J69" s="24">
-        <f>(1-$D69)*E69</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K69" s="24">
-        <f>(1-$D69)*F69</f>
+        <f t="shared" si="22"/>
         <v>14000</v>
       </c>
       <c r="L69" s="24">
-        <f>G69</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M69" s="24">
-        <f>(1-$D69)*H69</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N69" s="24">
-        <f>(1-$D69)*I69</f>
+        <f t="shared" si="25"/>
         <v>2500</v>
       </c>
       <c r="O69" s="24">
@@ -8940,30 +8961,30 @@
         <v>8080</v>
       </c>
       <c r="Z69" s="24">
-        <f>SUM(J69:Y69)</f>
+        <f t="shared" si="26"/>
         <v>69140</v>
       </c>
       <c r="AA69" s="24">
         <v>0</v>
       </c>
       <c r="AB69" s="20">
-        <f>Z69-AA69</f>
+        <f t="shared" si="27"/>
         <v>69140</v>
       </c>
       <c r="AC69" s="24" t="str">
-        <f>IF(AND($T69=6000, ($T69+$W69-$AB69)&gt;=6000),T69,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD69" s="24" t="str">
-        <f>IF(AND($T69=8000, ($T69+$W69-$AB69)&gt;=8000),T69,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE69" s="24" t="str">
-        <f>IF(($T69+$W69-$AB69)&gt;=$T69+8000,W69,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF69" s="25" t="str">
-        <f>IF(AB69&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -8996,23 +9017,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="24">
-        <f>(1-$D70)*E70</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K70" s="24">
-        <f>(1-$D70)*F70</f>
+        <f t="shared" si="22"/>
         <v>26000</v>
       </c>
       <c r="L70" s="24">
-        <f>G70</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M70" s="24">
-        <f>(1-$D70)*H70</f>
+        <f t="shared" si="24"/>
         <v>1000</v>
       </c>
       <c r="N70" s="24">
-        <f>(1-$D70)*I70</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O70" s="24">
@@ -9049,30 +9070,30 @@
         <v>0</v>
       </c>
       <c r="Z70" s="24">
-        <f>SUM(J70:Y70)</f>
+        <f t="shared" si="26"/>
         <v>43140</v>
       </c>
       <c r="AA70" s="24">
         <v>0</v>
       </c>
       <c r="AB70" s="20">
-        <f>Z70-AA70</f>
+        <f t="shared" si="27"/>
         <v>43140</v>
       </c>
       <c r="AC70" s="24" t="str">
-        <f>IF(AND($T70=6000, ($T70+$W70-$AB70)&gt;=6000),T70,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD70" s="24" t="str">
-        <f>IF(AND($T70=8000, ($T70+$W70-$AB70)&gt;=8000),T70,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE70" s="24" t="str">
-        <f>IF(($T70+$W70-$AB70)&gt;=$T70+8000,W70,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF70" s="25" t="str">
-        <f>IF(AB70&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9105,23 +9126,23 @@
         <v>0</v>
       </c>
       <c r="J71" s="24">
-        <f>(1-$D71)*E71</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K71" s="24">
-        <f>(1-$D71)*F71</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L71" s="24">
-        <f>G71</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M71" s="24">
-        <f>(1-$D71)*H71</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N71" s="24">
-        <f>(1-$D71)*I71</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O71" s="24">
@@ -9158,30 +9179,30 @@
         <v>0</v>
       </c>
       <c r="Z71" s="24">
-        <f>SUM(J71:Y71)</f>
+        <f t="shared" si="26"/>
         <v>65160</v>
       </c>
       <c r="AA71" s="24">
         <v>0</v>
       </c>
       <c r="AB71" s="20">
-        <f>Z71-AA71</f>
+        <f t="shared" si="27"/>
         <v>65160</v>
       </c>
       <c r="AC71" s="24" t="str">
-        <f>IF(AND($T71=6000, ($T71+$W71-$AB71)&gt;=6000),T71,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD71" s="24" t="str">
-        <f>IF(AND($T71=8000, ($T71+$W71-$AB71)&gt;=8000),T71,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE71" s="24" t="str">
-        <f>IF(($T71+$W71-$AB71)&gt;=$T71+8000,W71,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF71" s="25" t="str">
-        <f>IF(AB71&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9214,23 +9235,23 @@
         <v>0</v>
       </c>
       <c r="J72" s="24">
-        <f>(1-$D72)*E72</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K72" s="24">
-        <f>(1-$D72)*F72</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L72" s="24">
-        <f>G72</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M72" s="24">
-        <f>(1-$D72)*H72</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N72" s="24">
-        <f>(1-$D72)*I72</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O72" s="24">
@@ -9267,30 +9288,30 @@
         <v>-500</v>
       </c>
       <c r="Z72" s="24">
-        <f>SUM(J72:Y72)</f>
+        <f t="shared" si="26"/>
         <v>35890</v>
       </c>
       <c r="AA72" s="24">
         <v>0</v>
       </c>
       <c r="AB72" s="20">
-        <f>Z72-AA72</f>
+        <f t="shared" si="27"/>
         <v>35890</v>
       </c>
       <c r="AC72" s="24" t="str">
-        <f>IF(AND($T72=6000, ($T72+$W72-$AB72)&gt;=6000),T72,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD72" s="24" t="str">
-        <f>IF(AND($T72=8000, ($T72+$W72-$AB72)&gt;=8000),T72,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE72" s="24" t="str">
-        <f>IF(($T72+$W72-$AB72)&gt;=$T72+8000,W72,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF72" s="25" t="str">
-        <f>IF(AB72&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9323,23 +9344,23 @@
         <v>0</v>
       </c>
       <c r="J73" s="24">
-        <f>(1-$D73)*E73</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K73" s="24">
-        <f>(1-$D73)*F73</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L73" s="24">
-        <f>G73</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M73" s="24">
-        <f>(1-$D73)*H73</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N73" s="24">
-        <f>(1-$D73)*I73</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O73" s="24">
@@ -9376,30 +9397,30 @@
         <v>0</v>
       </c>
       <c r="Z73" s="24">
-        <f>SUM(J73:Y73)</f>
+        <f t="shared" si="26"/>
         <v>50430</v>
       </c>
       <c r="AA73" s="24">
         <v>0</v>
       </c>
       <c r="AB73" s="20">
-        <f>Z73-AA73</f>
+        <f t="shared" si="27"/>
         <v>50430</v>
       </c>
       <c r="AC73" s="24" t="str">
-        <f>IF(AND($T73=6000, ($T73+$W73-$AB73)&gt;=6000),T73,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD73" s="24" t="str">
-        <f>IF(AND($T73=8000, ($T73+$W73-$AB73)&gt;=8000),T73,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE73" s="24" t="str">
-        <f>IF(($T73+$W73-$AB73)&gt;=$T73+8000,W73,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF73" s="25" t="str">
-        <f>IF(AB73&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9432,23 +9453,23 @@
         <v>0</v>
       </c>
       <c r="J74" s="24">
-        <f>(1-$D74)*E74</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K74" s="24">
-        <f>(1-$D74)*F74</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L74" s="24">
-        <f>G74</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M74" s="24">
-        <f>(1-$D74)*H74</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N74" s="24">
-        <f>(1-$D74)*I74</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O74" s="24">
@@ -9485,30 +9506,30 @@
         <v>0</v>
       </c>
       <c r="Z74" s="24">
-        <f>SUM(J74:Y74)</f>
+        <f t="shared" si="26"/>
         <v>36390</v>
       </c>
       <c r="AA74" s="24">
         <v>0</v>
       </c>
       <c r="AB74" s="20">
-        <f>Z74-AA74</f>
+        <f t="shared" si="27"/>
         <v>36390</v>
       </c>
       <c r="AC74" s="24" t="str">
-        <f>IF(AND($T74=6000, ($T74+$W74-$AB74)&gt;=6000),T74,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD74" s="24" t="str">
-        <f>IF(AND($T74=8000, ($T74+$W74-$AB74)&gt;=8000),T74,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE74" s="24" t="str">
-        <f>IF(($T74+$W74-$AB74)&gt;=$T74+8000,W74,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF74" s="25" t="str">
-        <f>IF(AB74&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9541,23 +9562,23 @@
         <v>0</v>
       </c>
       <c r="J75" s="24">
-        <f>(1-$D75)*E75</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K75" s="24">
-        <f>(1-$D75)*F75</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L75" s="24">
-        <f>G75</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M75" s="24">
-        <f>(1-$D75)*H75</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N75" s="24">
-        <f>(1-$D75)*I75</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O75" s="24">
@@ -9594,30 +9615,30 @@
         <v>0</v>
       </c>
       <c r="Z75" s="24">
-        <f>SUM(J75:Y75)</f>
+        <f t="shared" si="26"/>
         <v>50430</v>
       </c>
       <c r="AA75" s="24">
         <v>0</v>
       </c>
       <c r="AB75" s="20">
-        <f>Z75-AA75</f>
+        <f t="shared" si="27"/>
         <v>50430</v>
       </c>
       <c r="AC75" s="24" t="str">
-        <f>IF(AND($T75=6000, ($T75+$W75-$AB75)&gt;=6000),T75,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD75" s="24" t="str">
-        <f>IF(AND($T75=8000, ($T75+$W75-$AB75)&gt;=8000),T75,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE75" s="24" t="str">
-        <f>IF(($T75+$W75-$AB75)&gt;=$T75+8000,W75,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF75" s="25" t="str">
-        <f>IF(AB75&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9650,23 +9671,23 @@
         <v>5000</v>
       </c>
       <c r="J76" s="24">
-        <f>(1-$D76)*E76</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K76" s="24">
-        <f>(1-$D76)*F76</f>
+        <f t="shared" si="22"/>
         <v>21000</v>
       </c>
       <c r="L76" s="24">
-        <f>G76</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M76" s="24">
-        <f>(1-$D76)*H76</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N76" s="24">
-        <f>(1-$D76)*I76</f>
+        <f t="shared" si="25"/>
         <v>3750</v>
       </c>
       <c r="O76" s="24">
@@ -9703,30 +9724,30 @@
         <v>-695</v>
       </c>
       <c r="Z76" s="24">
-        <f>SUM(J76:Y76)</f>
+        <f t="shared" si="26"/>
         <v>74595</v>
       </c>
       <c r="AA76" s="24">
         <v>0</v>
       </c>
       <c r="AB76" s="20">
-        <f>Z76-AA76</f>
+        <f t="shared" si="27"/>
         <v>74595</v>
       </c>
       <c r="AC76" s="24" t="str">
-        <f>IF(AND($T76=6000, ($T76+$W76-$AB76)&gt;=6000),T76,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD76" s="24" t="str">
-        <f>IF(AND($T76=8000, ($T76+$W76-$AB76)&gt;=8000),T76,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE76" s="24" t="str">
-        <f>IF(($T76+$W76-$AB76)&gt;=$T76+8000,W76,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF76" s="25" t="str">
-        <f>IF(AB76&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9759,23 +9780,23 @@
         <v>0</v>
       </c>
       <c r="J77" s="24">
-        <f>(1-$D77)*E77</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K77" s="24">
-        <f>(1-$D77)*F77</f>
+        <f t="shared" si="22"/>
         <v>26000</v>
       </c>
       <c r="L77" s="24">
-        <f>G77</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M77" s="24">
-        <f>(1-$D77)*H77</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N77" s="24">
-        <f>(1-$D77)*I77</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O77" s="24">
@@ -9812,30 +9833,30 @@
         <v>14000</v>
       </c>
       <c r="Z77" s="24">
-        <f>SUM(J77:Y77)</f>
+        <f t="shared" si="26"/>
         <v>64930</v>
       </c>
       <c r="AA77" s="24">
         <v>0</v>
       </c>
       <c r="AB77" s="20">
-        <f>Z77-AA77</f>
+        <f t="shared" si="27"/>
         <v>64930</v>
       </c>
       <c r="AC77" s="24" t="str">
-        <f>IF(AND($T77=6000, ($T77+$W77-$AB77)&gt;=6000),T77,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD77" s="24" t="str">
-        <f>IF(AND($T77=8000, ($T77+$W77-$AB77)&gt;=8000),T77,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE77" s="24" t="str">
-        <f>IF(($T77+$W77-$AB77)&gt;=$T77+8000,W77,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF77" s="25" t="str">
-        <f>IF(AB77&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9868,23 +9889,23 @@
         <v>6000</v>
       </c>
       <c r="J78" s="24">
-        <f>(1-$D78)*E78</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K78" s="24">
-        <f>(1-$D78)*F78</f>
+        <f t="shared" si="22"/>
         <v>23100</v>
       </c>
       <c r="L78" s="24">
-        <f>G78</f>
+        <f t="shared" si="23"/>
         <v>5000</v>
       </c>
       <c r="M78" s="24">
-        <f>(1-$D78)*H78</f>
+        <f t="shared" si="24"/>
         <v>1400</v>
       </c>
       <c r="N78" s="24">
-        <f>(1-$D78)*I78</f>
+        <f t="shared" si="25"/>
         <v>4200</v>
       </c>
       <c r="O78" s="24">
@@ -9921,30 +9942,30 @@
         <v>0</v>
       </c>
       <c r="Z78" s="24">
-        <f>SUM(J78:Y78)</f>
+        <f t="shared" si="26"/>
         <v>67530</v>
       </c>
       <c r="AA78" s="24">
         <v>0</v>
       </c>
       <c r="AB78" s="20">
-        <f>Z78-AA78</f>
+        <f t="shared" si="27"/>
         <v>67530</v>
       </c>
       <c r="AC78" s="24" t="str">
-        <f>IF(AND($T78=6000, ($T78+$W78-$AB78)&gt;=6000),T78,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD78" s="24" t="str">
-        <f>IF(AND($T78=8000, ($T78+$W78-$AB78)&gt;=8000),T78,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE78" s="24" t="str">
-        <f>IF(($T78+$W78-$AB78)&gt;=$T78+8000,W78,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF78" s="25" t="str">
-        <f>IF(AB78&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -9977,23 +9998,23 @@
         <v>5000</v>
       </c>
       <c r="J79" s="24">
-        <f>(1-$D79)*E79</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K79" s="24">
-        <f>(1-$D79)*F79</f>
+        <f t="shared" si="22"/>
         <v>21000</v>
       </c>
       <c r="L79" s="24">
-        <f>G79</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M79" s="24">
-        <f>(1-$D79)*H79</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N79" s="24">
-        <f>(1-$D79)*I79</f>
+        <f t="shared" si="25"/>
         <v>3750</v>
       </c>
       <c r="O79" s="24">
@@ -10030,30 +10051,30 @@
         <v>450</v>
       </c>
       <c r="Z79" s="24">
-        <f>SUM(J79:Y79)</f>
+        <f t="shared" si="26"/>
         <v>69740</v>
       </c>
       <c r="AA79" s="24">
         <v>0</v>
       </c>
       <c r="AB79" s="20">
-        <f>Z79-AA79</f>
+        <f t="shared" si="27"/>
         <v>69740</v>
       </c>
       <c r="AC79" s="24" t="str">
-        <f>IF(AND($T79=6000, ($T79+$W79-$AB79)&gt;=6000),T79,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD79" s="24" t="str">
-        <f>IF(AND($T79=8000, ($T79+$W79-$AB79)&gt;=8000),T79,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE79" s="24" t="str">
-        <f>IF(($T79+$W79-$AB79)&gt;=$T79+8000,W79,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF79" s="25" t="str">
-        <f>IF(AB79&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10086,23 +10107,23 @@
         <v>8000</v>
       </c>
       <c r="J80" s="24">
-        <f>(1-$D80)*E80</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K80" s="24">
-        <f>(1-$D80)*F80</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L80" s="24">
-        <f>G80</f>
+        <f t="shared" si="23"/>
         <v>5000</v>
       </c>
       <c r="M80" s="24">
-        <f>(1-$D80)*H80</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N80" s="24">
-        <f>(1-$D80)*I80</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O80" s="24">
@@ -10139,30 +10160,30 @@
         <v>0</v>
       </c>
       <c r="Z80" s="24">
-        <f>SUM(J80:Y80)</f>
+        <f t="shared" si="26"/>
         <v>31210</v>
       </c>
       <c r="AA80" s="24">
         <v>0</v>
       </c>
       <c r="AB80" s="20">
-        <f>Z80-AA80</f>
+        <f t="shared" si="27"/>
         <v>31210</v>
       </c>
       <c r="AC80" s="24" t="str">
-        <f>IF(AND($T80=6000, ($T80+$W80-$AB80)&gt;=6000),T80,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD80" s="24" t="str">
-        <f>IF(AND($T80=8000, ($T80+$W80-$AB80)&gt;=8000),T80,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE80" s="24" t="str">
-        <f>IF(($T80+$W80-$AB80)&gt;=$T80+8000,W80,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF80" s="25" t="str">
-        <f>IF(AB80&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10195,23 +10216,23 @@
         <v>0</v>
       </c>
       <c r="J81" s="24">
-        <f>(1-$D81)*E81</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K81" s="24">
-        <f>(1-$D81)*F81</f>
+        <f t="shared" si="22"/>
         <v>26000</v>
       </c>
       <c r="L81" s="24">
-        <f>G81</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M81" s="24">
-        <f>(1-$D81)*H81</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N81" s="24">
-        <f>(1-$D81)*I81</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O81" s="24">
@@ -10248,30 +10269,30 @@
         <v>7000</v>
       </c>
       <c r="Z81" s="24">
-        <f>SUM(J81:Y81)</f>
+        <f t="shared" si="26"/>
         <v>65930</v>
       </c>
       <c r="AA81" s="24">
         <v>0</v>
       </c>
       <c r="AB81" s="20">
-        <f>Z81-AA81</f>
+        <f t="shared" si="27"/>
         <v>65930</v>
       </c>
       <c r="AC81" s="24" t="str">
-        <f>IF(AND($T81=6000, ($T81+$W81-$AB81)&gt;=6000),T81,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD81" s="24" t="str">
-        <f>IF(AND($T81=8000, ($T81+$W81-$AB81)&gt;=8000),T81,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE81" s="24" t="str">
-        <f>IF(($T81+$W81-$AB81)&gt;=$T81+8000,W81,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF81" s="25" t="str">
-        <f>IF(AB81&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10304,23 +10325,23 @@
         <v>0</v>
       </c>
       <c r="J82" s="24">
-        <f>(1-$D82)*E82</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K82" s="24">
-        <f>(1-$D82)*F82</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L82" s="24">
-        <f>G82</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M82" s="24">
-        <f>(1-$D82)*H82</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N82" s="24">
-        <f>(1-$D82)*I82</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O82" s="24">
@@ -10357,30 +10378,30 @@
         <v>19200</v>
       </c>
       <c r="Z82" s="24">
-        <f>SUM(J82:Y82)</f>
+        <f t="shared" si="26"/>
         <v>55590</v>
       </c>
       <c r="AA82" s="24">
         <v>0</v>
       </c>
       <c r="AB82" s="20">
-        <f>Z82-AA82</f>
+        <f t="shared" si="27"/>
         <v>55590</v>
       </c>
       <c r="AC82" s="24" t="str">
-        <f>IF(AND($T82=6000, ($T82+$W82-$AB82)&gt;=6000),T82,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD82" s="24" t="str">
-        <f>IF(AND($T82=8000, ($T82+$W82-$AB82)&gt;=8000),T82,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE82" s="24" t="str">
-        <f>IF(($T82+$W82-$AB82)&gt;=$T82+8000,W82,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF82" s="25" t="str">
-        <f>IF(AB82&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10413,23 +10434,23 @@
         <v>0</v>
       </c>
       <c r="J83" s="24">
-        <f>(1-$D83)*E83</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K83" s="24">
-        <f>(1-$D83)*F83</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L83" s="24">
-        <f>G83</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M83" s="24">
-        <f>(1-$D83)*H83</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N83" s="24">
-        <f>(1-$D83)*I83</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O83" s="24">
@@ -10466,30 +10487,30 @@
         <v>19200</v>
       </c>
       <c r="Z83" s="24">
-        <f>SUM(J83:Y83)</f>
+        <f t="shared" si="26"/>
         <v>55590</v>
       </c>
       <c r="AA83" s="24">
         <v>0</v>
       </c>
       <c r="AB83" s="20">
-        <f>Z83-AA83</f>
+        <f t="shared" si="27"/>
         <v>55590</v>
       </c>
       <c r="AC83" s="24" t="str">
-        <f>IF(AND($T83=6000, ($T83+$W83-$AB83)&gt;=6000),T83,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD83" s="24" t="str">
-        <f>IF(AND($T83=8000, ($T83+$W83-$AB83)&gt;=8000),T83,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE83" s="24" t="str">
-        <f>IF(($T83+$W83-$AB83)&gt;=$T83+8000,W83,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF83" s="25" t="str">
-        <f>IF(AB83&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10522,23 +10543,23 @@
         <v>0</v>
       </c>
       <c r="J84" s="24">
-        <f>(1-$D84)*E84</f>
+        <f t="shared" si="21"/>
         <v>1400</v>
       </c>
       <c r="K84" s="24">
-        <f>(1-$D84)*F84</f>
+        <f t="shared" si="22"/>
         <v>18200</v>
       </c>
       <c r="L84" s="24">
-        <f>G84</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M84" s="24">
-        <f>(1-$D84)*H84</f>
+        <f t="shared" si="24"/>
         <v>700</v>
       </c>
       <c r="N84" s="24">
-        <f>(1-$D84)*I84</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O84" s="24">
@@ -10575,30 +10596,30 @@
         <v>0</v>
       </c>
       <c r="Z84" s="24">
-        <f>SUM(J84:Y84)</f>
+        <f t="shared" si="26"/>
         <v>81330</v>
       </c>
       <c r="AA84" s="24">
         <v>81330</v>
       </c>
       <c r="AB84" s="20">
-        <f>Z84-AA84</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AC84" s="24">
-        <f>IF(AND($T84=6000, ($T84+$W84-$AB84)&gt;=6000),T84,"")</f>
+        <f t="shared" si="28"/>
         <v>6000</v>
       </c>
       <c r="AD84" s="24" t="str">
-        <f>IF(AND($T84=8000, ($T84+$W84-$AB84)&gt;=8000),T84,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE84" s="24" t="str">
-        <f>IF(($T84+$W84-$AB84)&gt;=$T84+8000,W84,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF84" s="25" t="str">
-        <f t="shared" ref="AF84:AF86" si="0">IF(AB84&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -10629,23 +10650,23 @@
         <v>0</v>
       </c>
       <c r="J85" s="24">
-        <f>(1-$D85)*E85</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K85" s="24">
-        <f>(1-$D85)*F85</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L85" s="24">
-        <f>G85</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M85" s="24">
-        <f>(1-$D85)*H85</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N85" s="24">
-        <f>(1-$D85)*I85</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O85" s="24">
@@ -10682,30 +10703,30 @@
         <v>0</v>
       </c>
       <c r="Z85" s="24">
-        <f>SUM(J85:Y85)</f>
+        <f t="shared" si="26"/>
         <v>37000</v>
       </c>
       <c r="AA85" s="24">
         <v>13670</v>
       </c>
       <c r="AB85" s="20">
-        <f>Z85-AA85</f>
+        <f t="shared" si="27"/>
         <v>23330</v>
       </c>
       <c r="AC85" s="24" t="str">
-        <f>IF(AND($T85=6000, ($T85+$W85-$AB85)&gt;=6000),T85,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD85" s="24" t="str">
-        <f>IF(AND($T85=8000, ($T85+$W85-$AB85)&gt;=8000),T85,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE85" s="24" t="str">
-        <f>IF(($T85+$W85-$AB85)&gt;=$T85+8000,W85,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF85" s="25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10738,23 +10759,23 @@
         <v>8000</v>
       </c>
       <c r="J86" s="24">
-        <f>(1-$D86)*E86</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K86" s="24">
-        <f>(1-$D86)*F86</f>
+        <f t="shared" si="22"/>
         <v>40000</v>
       </c>
       <c r="L86" s="24">
-        <f>G86</f>
+        <f t="shared" si="23"/>
         <v>5000</v>
       </c>
       <c r="M86" s="24">
-        <f>(1-$D86)*H86</f>
+        <f t="shared" si="24"/>
         <v>2000</v>
       </c>
       <c r="N86" s="24">
-        <f>(1-$D86)*I86</f>
+        <f t="shared" si="25"/>
         <v>8000</v>
       </c>
       <c r="O86" s="24">
@@ -10791,30 +10812,30 @@
         <v>5830</v>
       </c>
       <c r="Z86" s="24">
-        <f>SUM(J86:Y86)</f>
+        <f t="shared" si="26"/>
         <v>87040</v>
       </c>
       <c r="AA86" s="24">
         <v>0</v>
       </c>
       <c r="AB86" s="20">
-        <f>Z86-AA86</f>
+        <f t="shared" si="27"/>
         <v>87040</v>
       </c>
       <c r="AC86" s="24" t="str">
-        <f>IF(AND($T86=6000, ($T86+$W86-$AB86)&gt;=6000),T86,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD86" s="24" t="str">
-        <f>IF(AND($T86=8000, ($T86+$W86-$AB86)&gt;=8000),T86,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE86" s="24" t="str">
-        <f>IF(($T86+$W86-$AB86)&gt;=$T86+8000,W86,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF86" s="25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10847,23 +10868,23 @@
         <v>0</v>
       </c>
       <c r="J87" s="24">
-        <f>(1-$D87)*E87</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K87" s="24">
-        <f>(1-$D87)*F87</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L87" s="24">
-        <f>G87</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M87" s="24">
-        <f>(1-$D87)*H87</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N87" s="24">
-        <f>(1-$D87)*I87</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O87" s="24">
@@ -10900,30 +10921,30 @@
         <v>0</v>
       </c>
       <c r="Z87" s="24">
-        <f>SUM(J87:Y87)</f>
+        <f t="shared" si="26"/>
         <v>60390</v>
       </c>
       <c r="AA87" s="24">
         <v>0</v>
       </c>
       <c r="AB87" s="20">
-        <f>Z87-AA87</f>
+        <f t="shared" si="27"/>
         <v>60390</v>
       </c>
       <c r="AC87" s="24" t="str">
-        <f>IF(AND($T87=6000, ($T87+$W87-$AB87)&gt;=6000),T87,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD87" s="24" t="str">
-        <f>IF(AND($T87=8000, ($T87+$W87-$AB87)&gt;=8000),T87,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE87" s="24" t="str">
-        <f>IF(($T87+$W87-$AB87)&gt;=$T87+8000,W87,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF87" s="25" t="str">
-        <f>IF(AB87&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -10956,23 +10977,23 @@
         <v>5000</v>
       </c>
       <c r="J88" s="24">
-        <f>(1-$D88)*E88</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K88" s="24">
-        <f>(1-$D88)*F88</f>
+        <f t="shared" si="22"/>
         <v>21000</v>
       </c>
       <c r="L88" s="24">
-        <f>G88</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M88" s="24">
-        <f>(1-$D88)*H88</f>
+        <f t="shared" si="24"/>
         <v>1875</v>
       </c>
       <c r="N88" s="24">
-        <f>(1-$D88)*I88</f>
+        <f t="shared" si="25"/>
         <v>3750</v>
       </c>
       <c r="O88" s="24">
@@ -11009,30 +11030,30 @@
         <v>0</v>
       </c>
       <c r="Z88" s="24">
-        <f>SUM(J88:Y88)</f>
+        <f t="shared" si="26"/>
         <v>83925</v>
       </c>
       <c r="AA88" s="24">
         <v>0</v>
       </c>
       <c r="AB88" s="20">
-        <f>Z88-AA88</f>
+        <f t="shared" si="27"/>
         <v>83925</v>
       </c>
       <c r="AC88" s="24" t="str">
-        <f>IF(AND($T88=6000, ($T88+$W88-$AB88)&gt;=6000),T88,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD88" s="24" t="str">
-        <f>IF(AND($T88=8000, ($T88+$W88-$AB88)&gt;=8000),T88,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE88" s="24" t="str">
-        <f>IF(($T88+$W88-$AB88)&gt;=$T88+8000,W88,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF88" s="25" t="str">
-        <f>IF(AB88&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11065,23 +11086,23 @@
         <v>0</v>
       </c>
       <c r="J89" s="24">
-        <f>(1-$D89)*E89</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K89" s="24">
-        <f>(1-$D89)*F89</f>
+        <f t="shared" si="22"/>
         <v>26000</v>
       </c>
       <c r="L89" s="24">
-        <f>G89</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M89" s="24">
-        <f>(1-$D89)*H89</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N89" s="24">
-        <f>(1-$D89)*I89</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O89" s="24">
@@ -11118,30 +11139,30 @@
         <v>-3030</v>
       </c>
       <c r="Z89" s="24">
-        <f>SUM(J89:Y89)</f>
+        <f t="shared" si="26"/>
         <v>47900</v>
       </c>
       <c r="AA89" s="24">
         <v>0</v>
       </c>
       <c r="AB89" s="20">
-        <f>Z89-AA89</f>
+        <f t="shared" si="27"/>
         <v>47900</v>
       </c>
       <c r="AC89" s="24" t="str">
-        <f>IF(AND($T89=6000, ($T89+$W89-$AB89)&gt;=6000),T89,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD89" s="24" t="str">
-        <f>IF(AND($T89=8000, ($T89+$W89-$AB89)&gt;=8000),T89,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE89" s="24" t="str">
-        <f>IF(($T89+$W89-$AB89)&gt;=$T89+8000,W89,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF89" s="25" t="str">
-        <f>IF(AB89&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11174,23 +11195,23 @@
         <v>0</v>
       </c>
       <c r="J90" s="24">
-        <f>(1-$D90)*E90</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K90" s="24">
-        <f>(1-$D90)*F90</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L90" s="24">
-        <f>G90</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M90" s="24">
-        <f>(1-$D90)*H90</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N90" s="24">
-        <f>(1-$D90)*I90</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O90" s="24">
@@ -11227,30 +11248,30 @@
         <v>3500</v>
       </c>
       <c r="Z90" s="24">
-        <f>SUM(J90:Y90)</f>
+        <f t="shared" si="26"/>
         <v>39890</v>
       </c>
       <c r="AA90" s="24">
         <v>0</v>
       </c>
       <c r="AB90" s="20">
-        <f>Z90-AA90</f>
+        <f t="shared" si="27"/>
         <v>39890</v>
       </c>
       <c r="AC90" s="24" t="str">
-        <f>IF(AND($T90=6000, ($T90+$W90-$AB90)&gt;=6000),T90,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD90" s="24" t="str">
-        <f>IF(AND($T90=8000, ($T90+$W90-$AB90)&gt;=8000),T90,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE90" s="24" t="str">
-        <f>IF(($T90+$W90-$AB90)&gt;=$T90+8000,W90,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF90" s="25" t="str">
-        <f>IF(AB90&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11283,23 +11304,23 @@
         <v>0</v>
       </c>
       <c r="J91" s="24">
-        <f>(1-$D91)*E91</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K91" s="24">
-        <f>(1-$D91)*F91</f>
+        <f t="shared" si="22"/>
         <v>26000</v>
       </c>
       <c r="L91" s="24">
-        <f>G91</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M91" s="24">
-        <f>(1-$D91)*H91</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N91" s="24">
-        <f>(1-$D91)*I91</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O91" s="24">
@@ -11336,30 +11357,30 @@
         <v>0</v>
       </c>
       <c r="Z91" s="24">
-        <f>SUM(J91:Y91)</f>
+        <f t="shared" si="26"/>
         <v>56930</v>
       </c>
       <c r="AA91" s="24">
         <v>24700</v>
       </c>
       <c r="AB91" s="20">
-        <f>Z91-AA91</f>
+        <f t="shared" si="27"/>
         <v>32230</v>
       </c>
       <c r="AC91" s="24" t="str">
-        <f>IF(AND($T91=6000, ($T91+$W91-$AB91)&gt;=6000),T91,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD91" s="24" t="str">
-        <f>IF(AND($T91=8000, ($T91+$W91-$AB91)&gt;=8000),T91,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE91" s="24" t="str">
-        <f>IF(($T91+$W91-$AB91)&gt;=$T91+8000,W91,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF91" s="25" t="str">
-        <f>IF(AB91&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11392,23 +11413,23 @@
         <v>0</v>
       </c>
       <c r="J92" s="24">
-        <f>(1-$D92)*E92</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K92" s="24">
-        <f>(1-$D92)*F92</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L92" s="24">
-        <f>G92</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M92" s="24">
-        <f>(1-$D92)*H92</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N92" s="24">
-        <f>(1-$D92)*I92</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O92" s="24">
@@ -11445,30 +11466,30 @@
         <v>0</v>
       </c>
       <c r="Z92" s="24">
-        <f>SUM(J92:Y92)</f>
+        <f t="shared" si="26"/>
         <v>50430</v>
       </c>
       <c r="AA92" s="24">
         <v>0</v>
       </c>
       <c r="AB92" s="20">
-        <f>Z92-AA92</f>
+        <f t="shared" si="27"/>
         <v>50430</v>
       </c>
       <c r="AC92" s="24" t="str">
-        <f>IF(AND($T92=6000, ($T92+$W92-$AB92)&gt;=6000),T92,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD92" s="24" t="str">
-        <f>IF(AND($T92=8000, ($T92+$W92-$AB92)&gt;=8000),T92,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE92" s="24" t="str">
-        <f>IF(($T92+$W92-$AB92)&gt;=$T92+8000,W92,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF92" s="25" t="str">
-        <f>IF(AB92&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11501,23 +11522,23 @@
         <v>5000</v>
       </c>
       <c r="J93" s="24">
-        <f>(1-$D93)*E93</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K93" s="24">
-        <f>(1-$D93)*F93</f>
+        <f t="shared" si="22"/>
         <v>21000</v>
       </c>
       <c r="L93" s="24">
-        <f>G93</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M93" s="24">
-        <f>(1-$D93)*H93</f>
+        <f t="shared" si="24"/>
         <v>1875</v>
       </c>
       <c r="N93" s="24">
-        <f>(1-$D93)*I93</f>
+        <f t="shared" si="25"/>
         <v>3750</v>
       </c>
       <c r="O93" s="24">
@@ -11554,30 +11575,30 @@
         <v>0</v>
       </c>
       <c r="Z93" s="24">
-        <f>SUM(J93:Y93)</f>
+        <f t="shared" si="26"/>
         <v>73925</v>
       </c>
       <c r="AA93" s="24">
         <v>0</v>
       </c>
       <c r="AB93" s="20">
-        <f>Z93-AA93</f>
+        <f t="shared" si="27"/>
         <v>73925</v>
       </c>
       <c r="AC93" s="24" t="str">
-        <f>IF(AND($T93=6000, ($T93+$W93-$AB93)&gt;=6000),T93,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD93" s="24" t="str">
-        <f>IF(AND($T93=8000, ($T93+$W93-$AB93)&gt;=8000),T93,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE93" s="24" t="str">
-        <f>IF(($T93+$W93-$AB93)&gt;=$T93+8000,W93,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF93" s="25" t="str">
-        <f>IF(AB93&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11610,23 +11631,23 @@
         <v>5000</v>
       </c>
       <c r="J94" s="24">
-        <f>(1-$D94)*E94</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K94" s="24">
-        <f>(1-$D94)*F94</f>
+        <f t="shared" si="22"/>
         <v>21000</v>
       </c>
       <c r="L94" s="24">
-        <f>G94</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M94" s="24">
-        <f>(1-$D94)*H94</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N94" s="24">
-        <f>(1-$D94)*I94</f>
+        <f t="shared" si="25"/>
         <v>3750</v>
       </c>
       <c r="O94" s="24">
@@ -11663,30 +11684,30 @@
         <v>0</v>
       </c>
       <c r="Z94" s="24">
-        <f>SUM(J94:Y94)</f>
+        <f t="shared" si="26"/>
         <v>75290</v>
       </c>
       <c r="AA94" s="24">
         <v>0</v>
       </c>
       <c r="AB94" s="20">
-        <f>Z94-AA94</f>
+        <f t="shared" si="27"/>
         <v>75290</v>
       </c>
       <c r="AC94" s="24" t="str">
-        <f>IF(AND($T94=6000, ($T94+$W94-$AB94)&gt;=6000),T94,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD94" s="24" t="str">
-        <f>IF(AND($T94=8000, ($T94+$W94-$AB94)&gt;=8000),T94,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE94" s="24" t="str">
-        <f>IF(($T94+$W94-$AB94)&gt;=$T94+8000,W94,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF94" s="25" t="str">
-        <f>IF(AB94&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11719,23 +11740,23 @@
         <v>5000</v>
       </c>
       <c r="J95" s="24">
-        <f>(1-$D95)*E95</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K95" s="24">
-        <f>(1-$D95)*F95</f>
+        <f t="shared" si="22"/>
         <v>28000</v>
       </c>
       <c r="L95" s="24">
-        <f>G95</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M95" s="24">
-        <f>(1-$D95)*H95</f>
+        <f t="shared" si="24"/>
         <v>2500</v>
       </c>
       <c r="N95" s="24">
-        <f>(1-$D95)*I95</f>
+        <f t="shared" si="25"/>
         <v>5000</v>
       </c>
       <c r="O95" s="24">
@@ -11772,30 +11793,30 @@
         <v>0</v>
       </c>
       <c r="Z95" s="24">
-        <f>SUM(J95:Y95)</f>
+        <f t="shared" si="26"/>
         <v>76800</v>
       </c>
       <c r="AA95" s="24">
         <v>0</v>
       </c>
       <c r="AB95" s="20">
-        <f>Z95-AA95</f>
+        <f t="shared" si="27"/>
         <v>76800</v>
       </c>
       <c r="AC95" s="24" t="str">
-        <f>IF(AND($T95=6000, ($T95+$W95-$AB95)&gt;=6000),T95,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD95" s="24" t="str">
-        <f>IF(AND($T95=8000, ($T95+$W95-$AB95)&gt;=8000),T95,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE95" s="24" t="str">
-        <f>IF(($T95+$W95-$AB95)&gt;=$T95+8000,W95,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF95" s="25" t="str">
-        <f>IF(AB95&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11828,23 +11849,23 @@
         <v>5000</v>
       </c>
       <c r="J96" s="24">
-        <f>(1-$D96)*E96</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K96" s="24">
-        <f>(1-$D96)*F96</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L96" s="24">
-        <f>G96</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M96" s="24">
-        <f>(1-$D96)*H96</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N96" s="24">
-        <f>(1-$D96)*I96</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O96" s="24">
@@ -11881,30 +11902,30 @@
         <v>0</v>
       </c>
       <c r="Z96" s="24">
-        <f>SUM(J96:Y96)</f>
+        <f t="shared" si="26"/>
         <v>50560</v>
       </c>
       <c r="AA96" s="24">
         <v>0</v>
       </c>
       <c r="AB96" s="20">
-        <f>Z96-AA96</f>
+        <f t="shared" si="27"/>
         <v>50560</v>
       </c>
       <c r="AC96" s="24" t="str">
-        <f>IF(AND($T96=6000, ($T96+$W96-$AB96)&gt;=6000),T96,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD96" s="24" t="str">
-        <f>IF(AND($T96=8000, ($T96+$W96-$AB96)&gt;=8000),T96,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE96" s="24" t="str">
-        <f>IF(($T96+$W96-$AB96)&gt;=$T96+8000,W96,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF96" s="25" t="str">
-        <f>IF(AB96&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11937,23 +11958,23 @@
         <v>0</v>
       </c>
       <c r="J97" s="24">
-        <f>(1-$D97)*E97</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K97" s="24">
-        <f>(1-$D97)*F97</f>
+        <f t="shared" si="22"/>
         <v>19500</v>
       </c>
       <c r="L97" s="24">
-        <f>G97</f>
+        <f t="shared" si="23"/>
         <v>4000</v>
       </c>
       <c r="M97" s="24">
-        <f>(1-$D97)*H97</f>
+        <f t="shared" si="24"/>
         <v>750</v>
       </c>
       <c r="N97" s="24">
-        <f>(1-$D97)*I97</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O97" s="24">
@@ -11990,30 +12011,30 @@
         <v>65</v>
       </c>
       <c r="Z97" s="24">
-        <f>SUM(J97:Y97)</f>
+        <f t="shared" si="26"/>
         <v>50345</v>
       </c>
       <c r="AA97" s="24">
         <v>0</v>
       </c>
       <c r="AB97" s="20">
-        <f>Z97-AA97</f>
+        <f t="shared" si="27"/>
         <v>50345</v>
       </c>
       <c r="AC97" s="24" t="str">
-        <f>IF(AND($T97=6000, ($T97+$W97-$AB97)&gt;=6000),T97,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AD97" s="24" t="str">
-        <f>IF(AND($T97=8000, ($T97+$W97-$AB97)&gt;=8000),T97,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE97" s="24" t="str">
-        <f>IF(($T97+$W97-$AB97)&gt;=$T97+8000,W97,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AF97" s="25" t="str">
-        <f>IF(AB97&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12046,23 +12067,23 @@
         <v>5000</v>
       </c>
       <c r="J98" s="24">
-        <f>(1-$D98)*E98</f>
+        <f t="shared" ref="J98:J124" si="32">(1-$D98)*E98</f>
         <v>0</v>
       </c>
       <c r="K98" s="24">
-        <f>(1-$D98)*F98</f>
+        <f t="shared" ref="K98:K124" si="33">(1-$D98)*F98</f>
         <v>21000</v>
       </c>
       <c r="L98" s="24">
-        <f>G98</f>
+        <f t="shared" ref="L98:L124" si="34">G98</f>
         <v>4000</v>
       </c>
       <c r="M98" s="24">
-        <f>(1-$D98)*H98</f>
+        <f t="shared" ref="M98:M124" si="35">(1-$D98)*H98</f>
         <v>1875</v>
       </c>
       <c r="N98" s="24">
-        <f>(1-$D98)*I98</f>
+        <f t="shared" ref="N98:N124" si="36">(1-$D98)*I98</f>
         <v>3750</v>
       </c>
       <c r="O98" s="24">
@@ -12099,30 +12120,30 @@
         <v>0</v>
       </c>
       <c r="Z98" s="24">
-        <f>SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z129" si="37">SUM(J98:Y98)</f>
         <v>73925</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
-        <f>Z98-AA98</f>
+        <f t="shared" ref="AB98:AB129" si="38">Z98-AA98</f>
         <v>73925</v>
       </c>
       <c r="AC98" s="24" t="str">
-        <f>IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
+        <f t="shared" ref="AC98:AC124" si="39">IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
         <v/>
       </c>
       <c r="AD98" s="24" t="str">
-        <f>IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
+        <f t="shared" ref="AD98:AD124" si="40">IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
         <v/>
       </c>
       <c r="AE98" s="24" t="str">
-        <f>IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
+        <f t="shared" ref="AE98:AE124" si="41">IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
         <v/>
       </c>
       <c r="AF98" s="25" t="str">
-        <f>IF(AB98&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12155,23 +12176,23 @@
         <v>6000</v>
       </c>
       <c r="J99" s="24">
-        <f>(1-$D99)*E99</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K99" s="24">
-        <f>(1-$D99)*F99</f>
+        <f t="shared" si="33"/>
         <v>23100</v>
       </c>
       <c r="L99" s="24">
-        <f>G99</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="M99" s="24">
-        <f>(1-$D99)*H99</f>
+        <f t="shared" si="35"/>
         <v>1400</v>
       </c>
       <c r="N99" s="24">
-        <f>(1-$D99)*I99</f>
+        <f t="shared" si="36"/>
         <v>4200</v>
       </c>
       <c r="O99" s="24">
@@ -12208,30 +12229,30 @@
         <v>0</v>
       </c>
       <c r="Z99" s="24">
-        <f>SUM(J99:Y99)</f>
+        <f t="shared" si="37"/>
         <v>70430</v>
       </c>
       <c r="AA99" s="24">
         <v>0</v>
       </c>
       <c r="AB99" s="20">
-        <f>Z99-AA99</f>
+        <f t="shared" si="38"/>
         <v>70430</v>
       </c>
       <c r="AC99" s="24" t="str">
-        <f>IF(AND($T99=6000, ($T99+$W99-$AB99)&gt;=6000),T99,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD99" s="24" t="str">
-        <f>IF(AND($T99=8000, ($T99+$W99-$AB99)&gt;=8000),T99,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE99" s="24" t="str">
-        <f>IF(($T99+$W99-$AB99)&gt;=$T99+8000,W99,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF99" s="25" t="str">
-        <f>IF(AB99&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12264,23 +12285,23 @@
         <v>0</v>
       </c>
       <c r="J100" s="24">
-        <f>(1-$D100)*E100</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K100" s="24">
-        <f>(1-$D100)*F100</f>
+        <f t="shared" si="33"/>
         <v>24700</v>
       </c>
       <c r="L100" s="24">
-        <f>G100</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M100" s="24">
-        <f>(1-$D100)*H100</f>
+        <f t="shared" si="35"/>
         <v>950</v>
       </c>
       <c r="N100" s="24">
-        <f>(1-$D100)*I100</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O100" s="24">
@@ -12317,30 +12338,30 @@
         <v>-10000</v>
       </c>
       <c r="Z100" s="24">
-        <f>SUM(J100:Y100)</f>
+        <f t="shared" si="37"/>
         <v>31790</v>
       </c>
       <c r="AA100" s="24">
         <v>33140</v>
       </c>
       <c r="AB100" s="20">
-        <f>Z100-AA100</f>
+        <f t="shared" si="38"/>
         <v>-1350</v>
       </c>
       <c r="AC100" s="24" t="str">
-        <f>IF(AND($T100=6000, ($T100+$W100-$AB100)&gt;=6000),T100,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD100" s="24" t="str">
-        <f>IF(AND($T100=8000, ($T100+$W100-$AB100)&gt;=8000),T100,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE100" s="24" t="str">
-        <f>IF(($T100+$W100-$AB100)&gt;=$T100+8000,W100,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF100" s="25" t="str">
-        <f>IF(AB100&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -12373,23 +12394,23 @@
         <v>0</v>
       </c>
       <c r="J101" s="24">
-        <f>(1-$D101)*E101</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K101" s="24">
-        <f>(1-$D101)*F101</f>
+        <f t="shared" si="33"/>
         <v>13000</v>
       </c>
       <c r="L101" s="24">
-        <f>G101</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M101" s="24">
-        <f>(1-$D101)*H101</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N101" s="24">
-        <f>(1-$D101)*I101</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O101" s="24">
@@ -12426,30 +12447,30 @@
         <v>8000</v>
       </c>
       <c r="Z101" s="24">
-        <f>SUM(J101:Y101)</f>
+        <f t="shared" si="37"/>
         <v>45930</v>
       </c>
       <c r="AA101" s="24">
         <v>0</v>
       </c>
       <c r="AB101" s="20">
-        <f>Z101-AA101</f>
+        <f t="shared" si="38"/>
         <v>45930</v>
       </c>
       <c r="AC101" s="24" t="str">
-        <f>IF(AND($T101=6000, ($T101+$W101-$AB101)&gt;=6000),T101,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD101" s="24" t="str">
-        <f>IF(AND($T101=8000, ($T101+$W101-$AB101)&gt;=8000),T101,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE101" s="24" t="str">
-        <f>IF(($T101+$W101-$AB101)&gt;=$T101+8000,W101,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF101" s="25" t="str">
-        <f>IF(AB101&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12482,23 +12503,23 @@
         <v>5000</v>
       </c>
       <c r="J102" s="24">
-        <f>(1-$D102)*E102</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K102" s="24">
-        <f>(1-$D102)*F102</f>
+        <f t="shared" si="33"/>
         <v>14000</v>
       </c>
       <c r="L102" s="24">
-        <f>G102</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M102" s="24">
-        <f>(1-$D102)*H102</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N102" s="24">
-        <f>(1-$D102)*I102</f>
+        <f t="shared" si="36"/>
         <v>2500</v>
       </c>
       <c r="O102" s="24">
@@ -12535,30 +12556,30 @@
         <v>0</v>
       </c>
       <c r="Z102" s="24">
-        <f>SUM(J102:Y102)</f>
+        <f t="shared" si="37"/>
         <v>57980</v>
       </c>
       <c r="AA102" s="24">
         <v>0</v>
       </c>
       <c r="AB102" s="20">
-        <f>Z102-AA102</f>
+        <f t="shared" si="38"/>
         <v>57980</v>
       </c>
       <c r="AC102" s="24" t="str">
-        <f>IF(AND($T102=6000, ($T102+$W102-$AB102)&gt;=6000),T102,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD102" s="24" t="str">
-        <f>IF(AND($T102=8000, ($T102+$W102-$AB102)&gt;=8000),T102,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE102" s="24" t="str">
-        <f>IF(($T102+$W102-$AB102)&gt;=$T102+8000,W102,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF102" s="25" t="str">
-        <f>IF(AB102&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12591,23 +12612,23 @@
         <v>6000</v>
       </c>
       <c r="J103" s="24">
-        <f>(1-$D103)*E103</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K103" s="24">
-        <f>(1-$D103)*F103</f>
+        <f t="shared" si="33"/>
         <v>16500</v>
       </c>
       <c r="L103" s="24">
-        <f>G103</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="M103" s="24">
-        <f>(1-$D103)*H103</f>
+        <f t="shared" si="35"/>
         <v>1000</v>
       </c>
       <c r="N103" s="24">
-        <f>(1-$D103)*I103</f>
+        <f t="shared" si="36"/>
         <v>3000</v>
       </c>
       <c r="O103" s="24">
@@ -12644,30 +12665,30 @@
         <v>-3145</v>
       </c>
       <c r="Z103" s="24">
-        <f>SUM(J103:Y103)</f>
+        <f t="shared" si="37"/>
         <v>67085</v>
       </c>
       <c r="AA103" s="24">
         <v>0</v>
       </c>
       <c r="AB103" s="20">
-        <f>Z103-AA103</f>
+        <f t="shared" si="38"/>
         <v>67085</v>
       </c>
       <c r="AC103" s="24" t="str">
-        <f>IF(AND($T103=6000, ($T103+$W103-$AB103)&gt;=6000),T103,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD103" s="24" t="str">
-        <f>IF(AND($T103=8000, ($T103+$W103-$AB103)&gt;=8000),T103,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE103" s="24" t="str">
-        <f>IF(($T103+$W103-$AB103)&gt;=$T103+8000,W103,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF103" s="25" t="str">
-        <f>IF(AB103&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12700,23 +12721,23 @@
         <v>0</v>
       </c>
       <c r="J104" s="24">
-        <f>(1-$D104)*E104</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K104" s="24">
-        <f>(1-$D104)*F104</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L104" s="24">
-        <f>G104</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M104" s="24">
-        <f>(1-$D104)*H104</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N104" s="24">
-        <f>(1-$D104)*I104</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O104" s="24">
@@ -12753,30 +12774,30 @@
         <v>0</v>
       </c>
       <c r="Z104" s="24">
-        <f>SUM(J104:Y104)</f>
+        <f t="shared" si="37"/>
         <v>52430</v>
       </c>
       <c r="AA104" s="24">
         <v>0</v>
       </c>
       <c r="AB104" s="20">
-        <f>Z104-AA104</f>
+        <f t="shared" si="38"/>
         <v>52430</v>
       </c>
       <c r="AC104" s="24" t="str">
-        <f>IF(AND($T104=6000, ($T104+$W104-$AB104)&gt;=6000),T104,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD104" s="24" t="str">
-        <f>IF(AND($T104=8000, ($T104+$W104-$AB104)&gt;=8000),T104,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE104" s="24" t="str">
-        <f>IF(($T104+$W104-$AB104)&gt;=$T104+8000,W104,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF104" s="25" t="str">
-        <f>IF(AB104&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12809,23 +12830,23 @@
         <v>5000</v>
       </c>
       <c r="J105" s="24">
-        <f>(1-$D105)*E105</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K105" s="24">
-        <f>(1-$D105)*F105</f>
+        <f t="shared" si="33"/>
         <v>21000</v>
       </c>
       <c r="L105" s="24">
-        <f>G105</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M105" s="24">
-        <f>(1-$D105)*H105</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N105" s="24">
-        <f>(1-$D105)*I105</f>
+        <f t="shared" si="36"/>
         <v>3750</v>
       </c>
       <c r="O105" s="24">
@@ -12862,30 +12883,30 @@
         <v>0</v>
       </c>
       <c r="Z105" s="24">
-        <f>SUM(J105:Y105)</f>
+        <f t="shared" si="37"/>
         <v>77290</v>
       </c>
       <c r="AA105" s="24">
         <v>0</v>
       </c>
       <c r="AB105" s="20">
-        <f>Z105-AA105</f>
+        <f t="shared" si="38"/>
         <v>77290</v>
       </c>
       <c r="AC105" s="24" t="str">
-        <f>IF(AND($T105=6000, ($T105+$W105-$AB105)&gt;=6000),T105,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD105" s="24" t="str">
-        <f>IF(AND($T105=8000, ($T105+$W105-$AB105)&gt;=8000),T105,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE105" s="24" t="str">
-        <f>IF(($T105+$W105-$AB105)&gt;=$T105+8000,W105,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF105" s="25" t="str">
-        <f>IF(AB105&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -12918,23 +12939,23 @@
         <v>0</v>
       </c>
       <c r="J106" s="24">
-        <f>(1-$D106)*E106</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K106" s="24">
-        <f>(1-$D106)*F106</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L106" s="24">
-        <f>G106</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M106" s="24">
-        <f>(1-$D106)*H106</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N106" s="24">
-        <f>(1-$D106)*I106</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O106" s="24">
@@ -12971,30 +12992,30 @@
         <v>0</v>
       </c>
       <c r="Z106" s="24">
-        <f>SUM(J106:Y106)</f>
+        <f t="shared" si="37"/>
         <v>65160</v>
       </c>
       <c r="AA106" s="24">
         <v>0</v>
       </c>
       <c r="AB106" s="20">
-        <f>Z106-AA106</f>
+        <f t="shared" si="38"/>
         <v>65160</v>
       </c>
       <c r="AC106" s="24" t="str">
-        <f>IF(AND($T106=6000, ($T106+$W106-$AB106)&gt;=6000),T106,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD106" s="24" t="str">
-        <f>IF(AND($T106=8000, ($T106+$W106-$AB106)&gt;=8000),T106,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE106" s="24" t="str">
-        <f>IF(($T106+$W106-$AB106)&gt;=$T106+8000,W106,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF106" s="25" t="str">
-        <f>IF(AB106&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13027,23 +13048,23 @@
         <v>5000</v>
       </c>
       <c r="J107" s="24">
-        <f>(1-$D107)*E107</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K107" s="24">
-        <f>(1-$D107)*F107</f>
+        <f t="shared" si="33"/>
         <v>21000</v>
       </c>
       <c r="L107" s="24">
-        <f>G107</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M107" s="24">
-        <f>(1-$D107)*H107</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N107" s="24">
-        <f>(1-$D107)*I107</f>
+        <f t="shared" si="36"/>
         <v>3750</v>
       </c>
       <c r="O107" s="24">
@@ -13080,30 +13101,30 @@
         <v>0</v>
       </c>
       <c r="Z107" s="24">
-        <f>SUM(J107:Y107)</f>
+        <f t="shared" si="37"/>
         <v>75290</v>
       </c>
       <c r="AA107" s="24">
         <v>0</v>
       </c>
       <c r="AB107" s="20">
-        <f>Z107-AA107</f>
+        <f t="shared" si="38"/>
         <v>75290</v>
       </c>
       <c r="AC107" s="24" t="str">
-        <f>IF(AND($T107=6000, ($T107+$W107-$AB107)&gt;=6000),T107,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD107" s="24" t="str">
-        <f>IF(AND($T107=8000, ($T107+$W107-$AB107)&gt;=8000),T107,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE107" s="24" t="str">
-        <f>IF(($T107+$W107-$AB107)&gt;=$T107+8000,W107,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF107" s="25" t="str">
-        <f>IF(AB107&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13136,23 +13157,23 @@
         <v>0</v>
       </c>
       <c r="J108" s="24">
-        <f>(1-$D108)*E108</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K108" s="24">
-        <f>(1-$D108)*F108</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L108" s="24">
-        <f>G108</f>
+        <f t="shared" si="34"/>
         <v>2000</v>
       </c>
       <c r="M108" s="24">
-        <f>(1-$D108)*H108</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N108" s="24">
-        <f>(1-$D108)*I108</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O108" s="24">
@@ -13189,30 +13210,30 @@
         <v>0</v>
       </c>
       <c r="Z108" s="24">
-        <f>SUM(J108:Y108)</f>
+        <f t="shared" si="37"/>
         <v>24550</v>
       </c>
       <c r="AA108" s="24">
         <v>0</v>
       </c>
       <c r="AB108" s="20">
-        <f>Z108-AA108</f>
+        <f t="shared" si="38"/>
         <v>24550</v>
       </c>
       <c r="AC108" s="24" t="str">
-        <f>IF(AND($T108=6000, ($T108+$W108-$AB108)&gt;=6000),T108,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD108" s="24" t="str">
-        <f>IF(AND($T108=8000, ($T108+$W108-$AB108)&gt;=8000),T108,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE108" s="24" t="str">
-        <f>IF(($T108+$W108-$AB108)&gt;=$T108+8000,W108,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF108" s="25" t="str">
-        <f>IF(AB108&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13245,23 +13266,23 @@
         <v>0</v>
       </c>
       <c r="J109" s="24">
-        <f>(1-$D109)*E109</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K109" s="24">
-        <f>(1-$D109)*F109</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L109" s="24">
-        <f>G109</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M109" s="24">
-        <f>(1-$D109)*H109</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N109" s="24">
-        <f>(1-$D109)*I109</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O109" s="24">
@@ -13298,30 +13319,30 @@
         <v>0</v>
       </c>
       <c r="Z109" s="24">
-        <f>SUM(J109:Y109)</f>
+        <f t="shared" si="37"/>
         <v>65160</v>
       </c>
       <c r="AA109" s="24">
         <v>0</v>
       </c>
       <c r="AB109" s="20">
-        <f>Z109-AA109</f>
+        <f t="shared" si="38"/>
         <v>65160</v>
       </c>
       <c r="AC109" s="24" t="str">
-        <f>IF(AND($T109=6000, ($T109+$W109-$AB109)&gt;=6000),T109,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD109" s="24" t="str">
-        <f>IF(AND($T109=8000, ($T109+$W109-$AB109)&gt;=8000),T109,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE109" s="24" t="str">
-        <f>IF(($T109+$W109-$AB109)&gt;=$T109+8000,W109,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF109" s="25" t="str">
-        <f>IF(AB109&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13354,23 +13375,23 @@
         <v>0</v>
       </c>
       <c r="J110" s="24">
-        <f>(1-$D110)*E110</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K110" s="24">
-        <f>(1-$D110)*F110</f>
+        <f t="shared" si="33"/>
         <v>26000</v>
       </c>
       <c r="L110" s="24">
-        <f>G110</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M110" s="24">
-        <f>(1-$D110)*H110</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N110" s="24">
-        <f>(1-$D110)*I110</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O110" s="24">
@@ -13407,30 +13428,30 @@
         <v>14240</v>
       </c>
       <c r="Z110" s="24">
-        <f>SUM(J110:Y110)</f>
+        <f t="shared" si="37"/>
         <v>85900</v>
       </c>
       <c r="AA110" s="24">
         <v>50000</v>
       </c>
       <c r="AB110" s="20">
-        <f>Z110-AA110</f>
+        <f t="shared" si="38"/>
         <v>35900</v>
       </c>
       <c r="AC110" s="24" t="str">
-        <f>IF(AND($T110=6000, ($T110+$W110-$AB110)&gt;=6000),T110,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD110" s="24" t="str">
-        <f>IF(AND($T110=8000, ($T110+$W110-$AB110)&gt;=8000),T110,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE110" s="24" t="str">
-        <f>IF(($T110+$W110-$AB110)&gt;=$T110+8000,W110,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF110" s="25" t="str">
-        <f>IF(AB110&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13463,23 +13484,23 @@
         <v>0</v>
       </c>
       <c r="J111" s="24">
-        <f>(1-$D111)*E111</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K111" s="24">
-        <f>(1-$D111)*F111</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L111" s="24">
-        <f>G111</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M111" s="24">
-        <f>(1-$D111)*H111</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N111" s="24">
-        <f>(1-$D111)*I111</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O111" s="24">
@@ -13516,30 +13537,30 @@
         <v>0</v>
       </c>
       <c r="Z111" s="24">
-        <f>SUM(J111:Y111)</f>
+        <f t="shared" si="37"/>
         <v>44430</v>
       </c>
       <c r="AA111" s="24">
         <v>0</v>
       </c>
       <c r="AB111" s="20">
-        <f>Z111-AA111</f>
+        <f t="shared" si="38"/>
         <v>44430</v>
       </c>
       <c r="AC111" s="24" t="str">
-        <f>IF(AND($T111=6000, ($T111+$W111-$AB111)&gt;=6000),T111,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD111" s="24" t="str">
-        <f>IF(AND($T111=8000, ($T111+$W111-$AB111)&gt;=8000),T111,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE111" s="24" t="str">
-        <f>IF(($T111+$W111-$AB111)&gt;=$T111+8000,W111,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF111" s="25" t="str">
-        <f>IF(AB111&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13572,23 +13593,23 @@
         <v>5000</v>
       </c>
       <c r="J112" s="24">
-        <f>(1-$D112)*E112</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K112" s="24">
-        <f>(1-$D112)*F112</f>
+        <f t="shared" si="33"/>
         <v>21000</v>
       </c>
       <c r="L112" s="24">
-        <f>G112</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M112" s="24">
-        <f>(1-$D112)*H112</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N112" s="24">
-        <f>(1-$D112)*I112</f>
+        <f t="shared" si="36"/>
         <v>3750</v>
       </c>
       <c r="O112" s="24">
@@ -13625,30 +13646,30 @@
         <v>0</v>
       </c>
       <c r="Z112" s="24">
-        <f>SUM(J112:Y112)</f>
+        <f t="shared" si="37"/>
         <v>66230</v>
       </c>
       <c r="AA112" s="24">
         <v>0</v>
       </c>
       <c r="AB112" s="20">
-        <f>Z112-AA112</f>
+        <f t="shared" si="38"/>
         <v>66230</v>
       </c>
       <c r="AC112" s="24" t="str">
-        <f>IF(AND($T112=6000, ($T112+$W112-$AB112)&gt;=6000),T112,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD112" s="24" t="str">
-        <f>IF(AND($T112=8000, ($T112+$W112-$AB112)&gt;=8000),T112,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE112" s="24" t="str">
-        <f>IF(($T112+$W112-$AB112)&gt;=$T112+8000,W112,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF112" s="25" t="str">
-        <f>IF(AB112&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13681,23 +13702,23 @@
         <v>5000</v>
       </c>
       <c r="J113" s="24">
-        <f>(1-$D113)*E113</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K113" s="24">
-        <f>(1-$D113)*F113</f>
+        <f t="shared" si="33"/>
         <v>21000</v>
       </c>
       <c r="L113" s="24">
-        <f>G113</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M113" s="24">
-        <f>(1-$D113)*H113</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N113" s="24">
-        <f>(1-$D113)*I113</f>
+        <f t="shared" si="36"/>
         <v>3750</v>
       </c>
       <c r="O113" s="24">
@@ -13734,30 +13755,30 @@
         <v>0</v>
       </c>
       <c r="Z113" s="24">
-        <f>SUM(J113:Y113)</f>
+        <f t="shared" si="37"/>
         <v>76770</v>
       </c>
       <c r="AA113" s="24">
         <v>0</v>
       </c>
       <c r="AB113" s="20">
-        <f>Z113-AA113</f>
+        <f t="shared" si="38"/>
         <v>76770</v>
       </c>
       <c r="AC113" s="24" t="str">
-        <f>IF(AND($T113=6000, ($T113+$W113-$AB113)&gt;=6000),T113,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD113" s="24" t="str">
-        <f>IF(AND($T113=8000, ($T113+$W113-$AB113)&gt;=8000),T113,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE113" s="24" t="str">
-        <f>IF(($T113+$W113-$AB113)&gt;=$T113+8000,W113,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF113" s="25" t="str">
-        <f>IF(AB113&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13790,23 +13811,23 @@
         <v>8000</v>
       </c>
       <c r="J114" s="24">
-        <f>(1-$D114)*E114</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K114" s="24">
-        <f>(1-$D114)*F114</f>
+        <f t="shared" si="33"/>
         <v>30000</v>
       </c>
       <c r="L114" s="24">
-        <f>G114</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="M114" s="24">
-        <f>(1-$D114)*H114</f>
+        <f t="shared" si="35"/>
         <v>1500</v>
       </c>
       <c r="N114" s="24">
-        <f>(1-$D114)*I114</f>
+        <f t="shared" si="36"/>
         <v>6000</v>
       </c>
       <c r="O114" s="24">
@@ -13843,30 +13864,30 @@
         <v>2660</v>
       </c>
       <c r="Z114" s="24">
-        <f>SUM(J114:Y114)</f>
+        <f t="shared" si="37"/>
         <v>79370</v>
       </c>
       <c r="AA114" s="24">
         <v>0</v>
       </c>
       <c r="AB114" s="20">
-        <f>Z114-AA114</f>
+        <f t="shared" si="38"/>
         <v>79370</v>
       </c>
       <c r="AC114" s="24" t="str">
-        <f>IF(AND($T114=6000, ($T114+$W114-$AB114)&gt;=6000),T114,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD114" s="24" t="str">
-        <f>IF(AND($T114=8000, ($T114+$W114-$AB114)&gt;=8000),T114,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE114" s="24" t="str">
-        <f>IF(($T114+$W114-$AB114)&gt;=$T114+8000,W114,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF114" s="25" t="str">
-        <f>IF(AB114&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13899,23 +13920,23 @@
         <v>0</v>
       </c>
       <c r="J115" s="24">
-        <f>(1-$D115)*E115</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K115" s="24">
-        <f>(1-$D115)*F115</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L115" s="24">
-        <f>G115</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M115" s="24">
-        <f>(1-$D115)*H115</f>
+        <f t="shared" si="35"/>
         <v>750</v>
       </c>
       <c r="N115" s="24">
-        <f>(1-$D115)*I115</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O115" s="24">
@@ -13952,30 +13973,30 @@
         <v>1250</v>
       </c>
       <c r="Z115" s="24">
-        <f>SUM(J115:Y115)</f>
+        <f t="shared" si="37"/>
         <v>51530</v>
       </c>
       <c r="AA115" s="24">
         <v>10000</v>
       </c>
       <c r="AB115" s="20">
-        <f>Z115-AA115</f>
+        <f t="shared" si="38"/>
         <v>41530</v>
       </c>
       <c r="AC115" s="24" t="str">
-        <f>IF(AND($T115=6000, ($T115+$W115-$AB115)&gt;=6000),T115,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD115" s="24" t="str">
-        <f>IF(AND($T115=8000, ($T115+$W115-$AB115)&gt;=8000),T115,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE115" s="24" t="str">
-        <f>IF(($T115+$W115-$AB115)&gt;=$T115+8000,W115,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF115" s="25" t="str">
-        <f>IF(AB115&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14008,23 +14029,23 @@
         <v>5000</v>
       </c>
       <c r="J116" s="24">
-        <f>(1-$D116)*E116</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K116" s="24">
-        <f>(1-$D116)*F116</f>
+        <f t="shared" si="33"/>
         <v>21000</v>
       </c>
       <c r="L116" s="24">
-        <f>G116</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M116" s="24">
-        <f>(1-$D116)*H116</f>
+        <f t="shared" si="35"/>
         <v>1875</v>
       </c>
       <c r="N116" s="24">
-        <f>(1-$D116)*I116</f>
+        <f t="shared" si="36"/>
         <v>3750</v>
       </c>
       <c r="O116" s="24">
@@ -14061,30 +14082,30 @@
         <v>9500</v>
       </c>
       <c r="Z116" s="24">
-        <f>SUM(J116:Y116)</f>
+        <f t="shared" si="37"/>
         <v>83425</v>
       </c>
       <c r="AA116" s="24">
         <v>0</v>
       </c>
       <c r="AB116" s="20">
-        <f>Z116-AA116</f>
+        <f t="shared" si="38"/>
         <v>83425</v>
       </c>
       <c r="AC116" s="24" t="str">
-        <f>IF(AND($T116=6000, ($T116+$W116-$AB116)&gt;=6000),T116,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD116" s="24" t="str">
-        <f>IF(AND($T116=8000, ($T116+$W116-$AB116)&gt;=8000),T116,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE116" s="24" t="str">
-        <f>IF(($T116+$W116-$AB116)&gt;=$T116+8000,W116,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF116" s="25" t="str">
-        <f>IF(AB116&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14117,23 +14138,23 @@
         <v>5000</v>
       </c>
       <c r="J117" s="24">
-        <f>(1-$D117)*E117</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K117" s="24">
-        <f>(1-$D117)*F117</f>
+        <f t="shared" si="33"/>
         <v>21000</v>
       </c>
       <c r="L117" s="24">
-        <f>G117</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M117" s="24">
-        <f>(1-$D117)*H117</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N117" s="24">
-        <f>(1-$D117)*I117</f>
+        <f t="shared" si="36"/>
         <v>3750</v>
       </c>
       <c r="O117" s="24">
@@ -14170,30 +14191,30 @@
         <v>0</v>
       </c>
       <c r="Z117" s="24">
-        <f>SUM(J117:Y117)</f>
+        <f t="shared" si="37"/>
         <v>75310</v>
       </c>
       <c r="AA117" s="24">
         <v>0</v>
       </c>
       <c r="AB117" s="20">
-        <f>Z117-AA117</f>
+        <f t="shared" si="38"/>
         <v>75310</v>
       </c>
       <c r="AC117" s="24" t="str">
-        <f>IF(AND($T117=6000, ($T117+$W117-$AB117)&gt;=6000),T117,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD117" s="24" t="str">
-        <f>IF(AND($T117=8000, ($T117+$W117-$AB117)&gt;=8000),T117,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE117" s="24" t="str">
-        <f>IF(($T117+$W117-$AB117)&gt;=$T117+8000,W117,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF117" s="25" t="str">
-        <f>IF(AB117&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14226,23 +14247,23 @@
         <v>0</v>
       </c>
       <c r="J118" s="24">
-        <f>(1-$D118)*E118</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K118" s="24">
-        <f>(1-$D118)*F118</f>
+        <f t="shared" si="33"/>
         <v>26000</v>
       </c>
       <c r="L118" s="24">
-        <f>G118</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M118" s="24">
-        <f>(1-$D118)*H118</f>
+        <f t="shared" si="35"/>
         <v>1000</v>
       </c>
       <c r="N118" s="24">
-        <f>(1-$D118)*I118</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O118" s="24">
@@ -14279,30 +14300,30 @@
         <v>1000</v>
       </c>
       <c r="Z118" s="24">
-        <f>SUM(J118:Y118)</f>
+        <f t="shared" si="37"/>
         <v>44140</v>
       </c>
       <c r="AA118" s="24">
         <v>0</v>
       </c>
       <c r="AB118" s="20">
-        <f>Z118-AA118</f>
+        <f t="shared" si="38"/>
         <v>44140</v>
       </c>
       <c r="AC118" s="24" t="str">
-        <f>IF(AND($T118=6000, ($T118+$W118-$AB118)&gt;=6000),T118,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD118" s="24" t="str">
-        <f>IF(AND($T118=8000, ($T118+$W118-$AB118)&gt;=8000),T118,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE118" s="24" t="str">
-        <f>IF(($T118+$W118-$AB118)&gt;=$T118+8000,W118,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF118" s="25" t="str">
-        <f>IF(AB118&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14335,23 +14356,23 @@
         <v>6000</v>
       </c>
       <c r="J119" s="24">
-        <f>(1-$D119)*E119</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K119" s="24">
-        <f>(1-$D119)*F119</f>
+        <f t="shared" si="33"/>
         <v>23100</v>
       </c>
       <c r="L119" s="24">
-        <f>G119</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="M119" s="24">
-        <f>(1-$D119)*H119</f>
+        <f t="shared" si="35"/>
         <v>1400</v>
       </c>
       <c r="N119" s="24">
-        <f>(1-$D119)*I119</f>
+        <f t="shared" si="36"/>
         <v>4200</v>
       </c>
       <c r="O119" s="24">
@@ -14388,30 +14409,30 @@
         <v>0</v>
       </c>
       <c r="Z119" s="24">
-        <f>SUM(J119:Y119)</f>
+        <f t="shared" si="37"/>
         <v>78430</v>
       </c>
       <c r="AA119" s="24">
         <v>0</v>
       </c>
       <c r="AB119" s="20">
-        <f>Z119-AA119</f>
+        <f t="shared" si="38"/>
         <v>78430</v>
       </c>
       <c r="AC119" s="24" t="str">
-        <f>IF(AND($T119=6000, ($T119+$W119-$AB119)&gt;=6000),T119,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD119" s="24" t="str">
-        <f>IF(AND($T119=8000, ($T119+$W119-$AB119)&gt;=8000),T119,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE119" s="24" t="str">
-        <f>IF(($T119+$W119-$AB119)&gt;=$T119+8000,W119,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF119" s="25" t="str">
-        <f>IF(AB119&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14444,23 +14465,23 @@
         <v>8000</v>
       </c>
       <c r="J120" s="24">
-        <f>(1-$D120)*E120</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K120" s="24">
-        <f>(1-$D120)*F120</f>
+        <f t="shared" si="33"/>
         <v>30000</v>
       </c>
       <c r="L120" s="24">
-        <f>G120</f>
+        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="M120" s="24">
-        <f>(1-$D120)*H120</f>
+        <f t="shared" si="35"/>
         <v>1500</v>
       </c>
       <c r="N120" s="24">
-        <f>(1-$D120)*I120</f>
+        <f t="shared" si="36"/>
         <v>6000</v>
       </c>
       <c r="O120" s="24">
@@ -14497,30 +14518,30 @@
         <v>0</v>
       </c>
       <c r="Z120" s="24">
-        <f>SUM(J120:Y120)</f>
+        <f t="shared" si="37"/>
         <v>68710</v>
       </c>
       <c r="AA120" s="24">
         <v>0</v>
       </c>
       <c r="AB120" s="20">
-        <f>Z120-AA120</f>
+        <f t="shared" si="38"/>
         <v>68710</v>
       </c>
       <c r="AC120" s="24" t="str">
-        <f>IF(AND($T120=6000, ($T120+$W120-$AB120)&gt;=6000),T120,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD120" s="24" t="str">
-        <f>IF(AND($T120=8000, ($T120+$W120-$AB120)&gt;=8000),T120,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE120" s="24" t="str">
-        <f>IF(($T120+$W120-$AB120)&gt;=$T120+8000,W120,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF120" s="25" t="str">
-        <f>IF(AB120&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14553,23 +14574,23 @@
         <v>5000</v>
       </c>
       <c r="J121" s="24">
-        <f>(1-$D121)*E121</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K121" s="24">
-        <f>(1-$D121)*F121</f>
+        <f t="shared" si="33"/>
         <v>28000</v>
       </c>
       <c r="L121" s="24">
-        <f>G121</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M121" s="24">
-        <f>(1-$D121)*H121</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N121" s="24">
-        <f>(1-$D121)*I121</f>
+        <f t="shared" si="36"/>
         <v>5000</v>
       </c>
       <c r="O121" s="24">
@@ -14606,30 +14627,30 @@
         <v>4020</v>
       </c>
       <c r="Z121" s="24">
-        <f>SUM(J121:Y121)</f>
+        <f t="shared" si="37"/>
         <v>78500</v>
       </c>
       <c r="AA121" s="24">
         <v>0</v>
       </c>
       <c r="AB121" s="20">
-        <f>Z121-AA121</f>
+        <f t="shared" si="38"/>
         <v>78500</v>
       </c>
       <c r="AC121" s="24" t="str">
-        <f>IF(AND($T121=6000, ($T121+$W121-$AB121)&gt;=6000),T121,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD121" s="24" t="str">
-        <f>IF(AND($T121=8000, ($T121+$W121-$AB121)&gt;=8000),T121,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE121" s="24" t="str">
-        <f>IF(($T121+$W121-$AB121)&gt;=$T121+8000,W121,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF121" s="25" t="str">
-        <f>IF(AB121&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14662,23 +14683,23 @@
         <v>0</v>
       </c>
       <c r="J122" s="24">
-        <f>(1-$D122)*E122</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K122" s="24">
-        <f>(1-$D122)*F122</f>
+        <f t="shared" si="33"/>
         <v>19500</v>
       </c>
       <c r="L122" s="24">
-        <f>G122</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M122" s="24">
-        <f>(1-$D122)*H122</f>
+        <f t="shared" si="35"/>
         <v>750</v>
       </c>
       <c r="N122" s="24">
-        <f>(1-$D122)*I122</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O122" s="24">
@@ -14715,30 +14736,30 @@
         <v>0</v>
       </c>
       <c r="Z122" s="24">
-        <f>SUM(J122:Y122)</f>
+        <f t="shared" si="37"/>
         <v>36390</v>
       </c>
       <c r="AA122" s="24">
         <v>7070</v>
       </c>
       <c r="AB122" s="20">
-        <f>Z122-AA122</f>
+        <f t="shared" si="38"/>
         <v>29320</v>
       </c>
       <c r="AC122" s="24" t="str">
-        <f>IF(AND($T122=6000, ($T122+$W122-$AB122)&gt;=6000),T122,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD122" s="24" t="str">
-        <f>IF(AND($T122=8000, ($T122+$W122-$AB122)&gt;=8000),T122,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE122" s="24" t="str">
-        <f>IF(($T122+$W122-$AB122)&gt;=$T122+8000,W122,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF122" s="25" t="str">
-        <f>IF(AB122&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14771,23 +14792,23 @@
         <v>0</v>
       </c>
       <c r="J123" s="24">
-        <f>(1-$D123)*E123</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K123" s="24">
-        <f>(1-$D123)*F123</f>
+        <f t="shared" si="33"/>
         <v>18200</v>
       </c>
       <c r="L123" s="24">
-        <f>G123</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M123" s="24">
-        <f>(1-$D123)*H123</f>
+        <f t="shared" si="35"/>
         <v>700</v>
       </c>
       <c r="N123" s="24">
-        <f>(1-$D123)*I123</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O123" s="24">
@@ -14824,30 +14845,30 @@
         <v>0</v>
       </c>
       <c r="Z123" s="24">
-        <f>SUM(J123:Y123)</f>
+        <f t="shared" si="37"/>
         <v>42930</v>
       </c>
       <c r="AA123" s="24">
         <v>42930</v>
       </c>
       <c r="AB123" s="20">
-        <f>Z123-AA123</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AC123" s="24" t="str">
-        <f>IF(AND($T123=6000, ($T123+$W123-$AB123)&gt;=6000),T123,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD123" s="24" t="str">
-        <f>IF(AND($T123=8000, ($T123+$W123-$AB123)&gt;=8000),T123,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE123" s="24" t="str">
-        <f>IF(($T123+$W123-$AB123)&gt;=$T123+8000,W123,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF123" s="25" t="str">
-        <f>IF(AB123&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -14880,23 +14901,23 @@
         <v>0</v>
       </c>
       <c r="J124" s="24">
-        <f>(1-$D124)*E124</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K124" s="24">
-        <f>(1-$D124)*F124</f>
+        <f t="shared" si="33"/>
         <v>26000</v>
       </c>
       <c r="L124" s="24">
-        <f>G124</f>
+        <f t="shared" si="34"/>
         <v>4000</v>
       </c>
       <c r="M124" s="24">
-        <f>(1-$D124)*H124</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N124" s="24">
-        <f>(1-$D124)*I124</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O124" s="24">
@@ -14933,30 +14954,30 @@
         <v>0</v>
       </c>
       <c r="Z124" s="24">
-        <f>SUM(J124:Y124)</f>
+        <f t="shared" si="37"/>
         <v>50930</v>
       </c>
       <c r="AA124" s="24">
         <v>0</v>
       </c>
       <c r="AB124" s="20">
-        <f>Z124-AA124</f>
+        <f t="shared" si="38"/>
         <v>50930</v>
       </c>
       <c r="AC124" s="24" t="str">
-        <f>IF(AND($T124=6000, ($T124+$W124-$AB124)&gt;=6000),T124,"")</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AD124" s="24" t="str">
-        <f>IF(AND($T124=8000, ($T124+$W124-$AB124)&gt;=8000),T124,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AE124" s="24" t="str">
-        <f>IF(($T124+$W124-$AB124)&gt;=$T124+8000,W124,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF124" s="25" t="str">
-        <f>IF(AB124&lt;=0,"BONUS","")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -14975,80 +14996,80 @@
       <c r="L125" s="28"/>
       <c r="M125" s="28"/>
       <c r="N125" s="28">
-        <f>SUM(N2:N124)</f>
-        <v>259800</v>
+        <f t="shared" ref="N125:AF125" si="42">SUM(N2:N124)</f>
+        <v>259500</v>
       </c>
       <c r="O125" s="28">
-        <f>SUM(O2:O124)</f>
+        <f t="shared" si="42"/>
         <v>2150670</v>
       </c>
       <c r="P125" s="28">
-        <f>SUM(P2:P124)</f>
+        <f t="shared" si="42"/>
         <v>1239600</v>
       </c>
       <c r="Q125" s="28">
-        <f>SUM(Q2:Q124)</f>
+        <f t="shared" si="42"/>
         <v>140000</v>
       </c>
       <c r="R125" s="28">
-        <f>SUM(R2:R124)</f>
+        <f t="shared" si="42"/>
         <v>40000</v>
       </c>
       <c r="S125" s="28">
-        <f>SUM(S2:S124)</f>
+        <f t="shared" si="42"/>
         <v>30000</v>
       </c>
       <c r="T125" s="28">
-        <f>SUM(T2:T124)</f>
+        <f t="shared" si="42"/>
         <v>264000</v>
       </c>
       <c r="U125" s="28">
-        <f>SUM(U2:U124)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="V125" s="28">
-        <f>SUM(V2:V124)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="W125" s="28">
-        <f>SUM(W2:W124)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="X125" s="28">
-        <f>SUM(X2:X124)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="Y125" s="28">
-        <f>SUM(Y2:Y124)</f>
+        <f t="shared" si="42"/>
         <v>188670</v>
       </c>
       <c r="Z125" s="28">
-        <f>SUM(Z2:Z124)</f>
-        <v>7616965</v>
+        <f t="shared" si="42"/>
+        <v>7613565</v>
       </c>
       <c r="AA125" s="28">
-        <f>SUM(AA2:AA124)</f>
-        <v>1109165</v>
+        <f t="shared" si="42"/>
+        <v>1291035</v>
       </c>
       <c r="AB125" s="28">
-        <f>SUM(AB2:AB124)</f>
-        <v>6507800</v>
+        <f t="shared" si="42"/>
+        <v>6322530</v>
       </c>
       <c r="AC125" s="28">
-        <f>SUM(AC2:AC124)</f>
+        <f t="shared" si="42"/>
         <v>12000</v>
       </c>
       <c r="AD125" s="28">
-        <f>SUM(AD2:AD124)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AE125" s="28">
-        <f>SUM(AE2:AE124)</f>
-        <v>0</v>
-      </c>
-      <c r="AF125" s="28">
-        <f>SUM(AF2:AF124)</f>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AF125" s="25" t="str">
+        <f t="shared" si="31"/>
+        <v/>
       </c>
     </row>
     <row r="126" spans="1:32" x14ac:dyDescent="0.25">
@@ -23233,7 +23254,7 @@
     <sortCondition ref="A2:A125"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AC1:AF1 E125:AF125 AB126:AB982 AB1:AB124">
+  <conditionalFormatting sqref="AC1:AF1 AB1:AB124 E125:AE125 AB126:AB982">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -23263,7 +23284,7 @@
     <col min="3" max="3" width="68.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.85546875" style="7" customWidth="1"/>
     <col min="8" max="23" width="24.140625" style="7" customWidth="1"/>
     <col min="24" max="16384" width="14.42578125" style="7"/>
@@ -23285,7 +23306,10 @@
       <c r="E1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F1" s="4"/>
+      <c r="F1" s="36">
+        <f>SUM(D2:D1000)</f>
+        <v>1291035</v>
+      </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -23962,10 +23986,21 @@
       <c r="X25" s="7"/>
     </row>
     <row r="26" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="7"/>
+      <c r="A26" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" s="9">
+        <v>9640</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -23987,10 +24022,21 @@
       <c r="X26" s="7"/>
     </row>
     <row r="27" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="7"/>
+      <c r="A27" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D27" s="9">
+        <v>50000</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>302</v>
+      </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -24012,10 +24058,21 @@
       <c r="X27" s="7"/>
     </row>
     <row r="28" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="7"/>
+      <c r="A28" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" s="9">
+        <v>60000</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>304</v>
+      </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -24037,10 +24094,21 @@
       <c r="X28" s="7"/>
     </row>
     <row r="29" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="7"/>
+      <c r="A29" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D29" s="9">
+        <v>62230</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>303</v>
+      </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11F32D7-9D41-4AE4-AC61-9359E3DBF28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A39421B-28DF-4BA5-994C-6BB39D92F96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="308">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -953,6 +953,15 @@
   <si>
     <t>ABDULAZEEZ FAMILY</t>
   </si>
+  <si>
+    <t>NIP:PAUL ADEDOJA</t>
+  </si>
+  <si>
+    <t>ISLAMIAT YETUNDE TIRIMISIYU</t>
+  </si>
+  <si>
+    <t>ADIGUN AHNAF</t>
+  </si>
 </sst>
 </file>
 
@@ -2136,7 +2145,7 @@
         <v>44</v>
       </c>
       <c r="D7" s="23">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="24">
         <v>0</v>
@@ -2159,7 +2168,7 @@
       </c>
       <c r="K7" s="24">
         <f t="shared" si="1"/>
-        <v>18200</v>
+        <v>19500</v>
       </c>
       <c r="L7" s="24">
         <f t="shared" si="2"/>
@@ -2208,14 +2217,14 @@
       </c>
       <c r="Z7" s="24">
         <f t="shared" si="5"/>
-        <v>43130</v>
+        <v>44430</v>
       </c>
       <c r="AA7" s="24">
-        <v>43130</v>
+        <v>20000</v>
       </c>
       <c r="AB7" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>24430</v>
       </c>
       <c r="AC7" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2231,7 +2240,7 @@
       </c>
       <c r="AF7" s="25" t="str">
         <f t="shared" si="10"/>
-        <v>BONUS</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -2429,11 +2438,11 @@
         <v>44280</v>
       </c>
       <c r="AA9" s="24">
-        <v>16870</v>
+        <v>20000</v>
       </c>
       <c r="AB9" s="20">
         <f t="shared" si="6"/>
-        <v>27410</v>
+        <v>24280</v>
       </c>
       <c r="AC9" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2538,11 +2547,11 @@
         <v>69290</v>
       </c>
       <c r="AA10" s="24">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AB10" s="20">
         <f t="shared" si="6"/>
-        <v>69290</v>
+        <v>49290</v>
       </c>
       <c r="AC10" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3444,7 +3453,7 @@
         <v>33</v>
       </c>
       <c r="D19" s="23">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E19" s="24">
         <v>0</v>
@@ -3467,7 +3476,7 @@
       </c>
       <c r="K19" s="24">
         <f t="shared" si="1"/>
-        <v>21000</v>
+        <v>19600</v>
       </c>
       <c r="L19" s="24">
         <f t="shared" si="2"/>
@@ -3475,11 +3484,11 @@
       </c>
       <c r="M19" s="24">
         <f t="shared" si="3"/>
-        <v>1875</v>
+        <v>1750</v>
       </c>
       <c r="N19" s="24">
         <f t="shared" si="4"/>
-        <v>3750</v>
+        <v>3500</v>
       </c>
       <c r="O19" s="24">
         <v>25970</v>
@@ -3516,18 +3525,18 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="5"/>
-        <v>73925</v>
+        <v>72150</v>
       </c>
       <c r="AA19" s="24">
-        <v>51685</v>
+        <v>72150</v>
       </c>
       <c r="AB19" s="20">
         <f t="shared" si="6"/>
-        <v>22240</v>
-      </c>
-      <c r="AC19" s="24" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="24">
         <f t="shared" si="7"/>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="AD19" s="24" t="str">
         <f t="shared" si="8"/>
@@ -3539,7 +3548,7 @@
       </c>
       <c r="AF19" s="25" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
@@ -3628,11 +3637,11 @@
         <v>76770</v>
       </c>
       <c r="AA20" s="24">
-        <v>0</v>
+        <v>9535</v>
       </c>
       <c r="AB20" s="20">
         <f t="shared" si="6"/>
-        <v>76770</v>
+        <v>67235</v>
       </c>
       <c r="AC20" s="24" t="str">
         <f t="shared" si="7"/>
@@ -4752,7 +4761,7 @@
         <v>49</v>
       </c>
       <c r="D31" s="23">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E31" s="24">
         <v>0</v>
@@ -4775,7 +4784,7 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="1"/>
-        <v>26000</v>
+        <v>24700</v>
       </c>
       <c r="L31" s="24">
         <f t="shared" si="2"/>
@@ -4783,7 +4792,7 @@
       </c>
       <c r="M31" s="24">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="N31" s="24">
         <f t="shared" si="4"/>
@@ -4824,14 +4833,14 @@
       </c>
       <c r="Z31" s="24">
         <f t="shared" si="5"/>
+        <v>41790</v>
+      </c>
+      <c r="AA31" s="24">
         <v>43140</v>
-      </c>
-      <c r="AA31" s="24">
-        <v>0</v>
       </c>
       <c r="AB31" s="20">
         <f t="shared" si="6"/>
-        <v>43140</v>
+        <v>-1350</v>
       </c>
       <c r="AC31" s="24" t="str">
         <f t="shared" si="7"/>
@@ -4847,7 +4856,7 @@
       </c>
       <c r="AF31" s="25" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
@@ -12120,14 +12129,14 @@
         <v>0</v>
       </c>
       <c r="Z98" s="24">
-        <f t="shared" ref="Z98:Z129" si="37">SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z124" si="37">SUM(J98:Y98)</f>
         <v>73925</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
-        <f t="shared" ref="AB98:AB129" si="38">Z98-AA98</f>
+        <f t="shared" ref="AB98:AB124" si="38">Z98-AA98</f>
         <v>73925</v>
       </c>
       <c r="AC98" s="24" t="str">
@@ -14996,8 +15005,8 @@
       <c r="L125" s="28"/>
       <c r="M125" s="28"/>
       <c r="N125" s="28">
-        <f t="shared" ref="N125:AF125" si="42">SUM(N2:N124)</f>
-        <v>259500</v>
+        <f t="shared" ref="N125:AE125" si="42">SUM(N2:N124)</f>
+        <v>259250</v>
       </c>
       <c r="O125" s="28">
         <f t="shared" si="42"/>
@@ -15045,19 +15054,19 @@
       </c>
       <c r="Z125" s="28">
         <f t="shared" si="42"/>
-        <v>7613565</v>
+        <v>7611740</v>
       </c>
       <c r="AA125" s="28">
         <f t="shared" si="42"/>
-        <v>1291035</v>
+        <v>1364175</v>
       </c>
       <c r="AB125" s="28">
         <f t="shared" si="42"/>
-        <v>6322530</v>
+        <v>6247565</v>
       </c>
       <c r="AC125" s="28">
         <f t="shared" si="42"/>
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="AD125" s="28">
         <f t="shared" si="42"/>
@@ -23308,7 +23317,7 @@
       </c>
       <c r="F1" s="36">
         <f>SUM(D2:D1000)</f>
-        <v>1291035</v>
+        <v>1364175</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -24130,10 +24139,21 @@
       <c r="X29" s="7"/>
     </row>
     <row r="30" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="7"/>
+      <c r="A30" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" s="9">
+        <v>30000</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -24155,10 +24175,21 @@
       <c r="X30" s="7"/>
     </row>
     <row r="31" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="7"/>
+      <c r="A31" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" s="9">
+        <v>43140</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>307</v>
+      </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -38184,17 +38215,17 @@
       </c>
       <c r="B2" s="15">
         <f>'1ST TERM ACCOUNT'!AC125</f>
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="C2" s="15">
         <f>B2*0.7</f>
-        <v>8400</v>
+        <v>12600</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
       <c r="F2" s="15">
         <f>$C$2-D2</f>
-        <v>8400</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -38210,7 +38241,7 @@
       <c r="E3" s="16"/>
       <c r="F3" s="15">
         <f>$C$2-(D2+D3)</f>
-        <v>8400</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -38219,14 +38250,14 @@
       </c>
       <c r="B4" s="15">
         <f>B3-B2</f>
-        <v>204000</v>
+        <v>198000</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
       <c r="F4" s="15">
         <f>$C$2-(D2+D3+D4)</f>
-        <v>8400</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -38236,7 +38267,7 @@
       <c r="E5" s="16"/>
       <c r="F5" s="15">
         <f>$C$2-(D2+D3+D4+D5)</f>
-        <v>8400</v>
+        <v>12600</v>
       </c>
       <c r="H5" s="17"/>
     </row>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509D76EA-8349-4561-BD0A-BCB99C049F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F37F3DD-24FE-4729-8069-F8D7965C8870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="406">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -1200,9 +1200,6 @@
     <t>TESTIMONY AYANFE</t>
   </si>
   <si>
-    <t>PRINARY 2</t>
-  </si>
-  <si>
     <t>OLADOSU</t>
   </si>
   <si>
@@ -1252,6 +1249,12 @@
   </si>
   <si>
     <t>MOSES HEPHZIBAH</t>
+  </si>
+  <si>
+    <t>OFURE DIVINE EDIALE</t>
+  </si>
+  <si>
+    <t>OSIGWE FAMILY</t>
   </si>
 </sst>
 </file>
@@ -6089,10 +6092,10 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="B41" s="22" t="s">
         <v>390</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>391</v>
       </c>
       <c r="C41" s="22" t="s">
         <v>44</v>
@@ -9320,7 +9323,7 @@
         <v>368</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>387</v>
+        <v>48</v>
       </c>
       <c r="D71" s="23">
         <v>0.25</v>
@@ -12544,10 +12547,10 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B101" s="22" t="s">
         <v>388</v>
-      </c>
-      <c r="B101" s="22" t="s">
-        <v>389</v>
       </c>
       <c r="C101" s="22" t="s">
         <v>44</v>
@@ -14054,10 +14057,10 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="B115" s="22" t="s">
         <v>392</v>
-      </c>
-      <c r="B115" s="22" t="s">
-        <v>393</v>
       </c>
       <c r="C115" s="22" t="s">
         <v>47</v>
@@ -14354,11 +14357,11 @@
         <v>50180</v>
       </c>
       <c r="AA117" s="24">
-        <v>0</v>
+        <v>27120</v>
       </c>
       <c r="AB117" s="20">
         <f>Z117-AA117</f>
-        <v>50180</v>
+        <v>23060</v>
       </c>
       <c r="AC117" s="24" t="str">
         <f>IF(AND($T117=6000, ($T117+$W117-$AB117)&gt;=6000),T117,"")</f>
@@ -14462,11 +14465,11 @@
         <v>72310</v>
       </c>
       <c r="AA118" s="24">
-        <v>0</v>
+        <v>27120</v>
       </c>
       <c r="AB118" s="20">
         <f>Z118-AA118</f>
-        <v>72310</v>
+        <v>45190</v>
       </c>
       <c r="AC118" s="24" t="str">
         <f>IF(AND($T118=6000, ($T118+$W118-$AB118)&gt;=6000),T118,"")</f>
@@ -16620,11 +16623,11 @@
         <v>46880</v>
       </c>
       <c r="AA138" s="24">
-        <v>30000</v>
+        <v>46880</v>
       </c>
       <c r="AB138" s="20">
         <f>Z138-AA138</f>
-        <v>16880</v>
+        <v>0</v>
       </c>
       <c r="AC138" s="24" t="str">
         <f>IF(AND($T138=6000, ($T138+$W138-$AB138)&gt;=6000),T138,"")</f>
@@ -16722,11 +16725,11 @@
       </c>
       <c r="AA139" s="28">
         <f>SUM(AA2:AA138)</f>
-        <v>3390735</v>
+        <v>3461855</v>
       </c>
       <c r="AB139" s="28">
         <f>SUM(AB2:AB138)</f>
-        <v>5479325</v>
+        <v>5408205</v>
       </c>
       <c r="AC139" s="28">
         <f>SUM(AC2:AC138)</f>
@@ -24213,7 +24216,7 @@
     <sortCondition ref="A2:A139"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AC1:AF10 E139:AF139 AB140:AB996 AB1:AB138">
+  <conditionalFormatting sqref="AC1:AF10 AB1:AB138 E139:AF139 AB140:AB996">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -24267,7 +24270,7 @@
       </c>
       <c r="F1" s="36">
         <f>SUMIF(E1:E1000, "&lt;&gt;", D1:D1000)</f>
-        <v>3390735</v>
+        <v>3461855</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -25067,7 +25070,7 @@
         <v>50000</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -25097,13 +25100,13 @@
         <v>250</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D30" s="9">
         <v>30000</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -25745,13 +25748,13 @@
         <v>250</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D48" s="9">
         <v>100000</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -26033,13 +26036,13 @@
         <v>250</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D56" s="9">
         <v>22000</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
@@ -26321,13 +26324,13 @@
         <v>250</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D64" s="9">
         <v>124270</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
@@ -26399,7 +26402,7 @@
         <v>80000</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
@@ -26423,19 +26426,19 @@
     </row>
     <row r="67" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <v>46270</v>
+        <v>46290</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>270</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>272</v>
+        <v>404</v>
       </c>
       <c r="D67" s="9">
-        <v>50000</v>
+        <v>54240</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>273</v>
+        <v>405</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
@@ -26459,19 +26462,19 @@
     </row>
     <row r="68" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
-        <v>46280</v>
+        <v>46270</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="D68" s="9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -26495,19 +26498,19 @@
     </row>
     <row r="69" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
-        <v>46285</v>
+        <v>46280</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>371</v>
+        <v>315</v>
       </c>
       <c r="D69" s="9">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
@@ -26531,19 +26534,19 @@
     </row>
     <row r="70" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="D70" s="9">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
@@ -26567,19 +26570,19 @@
     </row>
     <row r="71" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D71" s="9">
-        <v>44140</v>
+        <v>10000</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
@@ -26603,19 +26606,19 @@
     </row>
     <row r="72" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
-        <v>46266</v>
+        <v>46280</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="D72" s="9">
-        <v>50000</v>
+        <v>44140</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>264</v>
+        <v>348</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
@@ -26639,19 +26642,19 @@
     </row>
     <row r="73" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
-        <v>46281</v>
+        <v>46266</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>345</v>
+        <v>263</v>
       </c>
       <c r="D73" s="9">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
@@ -26675,7 +26678,7 @@
     </row>
     <row r="74" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>250</v>
@@ -26684,7 +26687,7 @@
         <v>345</v>
       </c>
       <c r="D74" s="9">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>346</v>
@@ -26711,18 +26714,20 @@
     </row>
     <row r="75" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="D75" s="9">
-        <v>36050</v>
-      </c>
-      <c r="E75" s="7"/>
+        <v>10000</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
@@ -26745,18 +26750,20 @@
     </row>
     <row r="76" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
-        <v>46279</v>
+        <v>46290</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="D76" s="9">
-        <v>100000</v>
-      </c>
-      <c r="E76" s="7"/>
+        <v>16880</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
@@ -26782,13 +26789,13 @@
         <v>46279</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D77" s="9">
-        <v>20180</v>
+        <v>36050</v>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
@@ -26813,18 +26820,18 @@
     </row>
     <row r="78" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="D78" s="12">
-        <v>10000</v>
-      </c>
-      <c r="E78" s="11"/>
+      <c r="C78" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D78" s="9">
+        <v>100000</v>
+      </c>
+      <c r="E78" s="7"/>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -26847,16 +26854,16 @@
     </row>
     <row r="79" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D79" s="9">
-        <v>10000</v>
+        <v>20180</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
@@ -26881,18 +26888,18 @@
     </row>
     <row r="80" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C80" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D80" s="9">
-        <v>40000</v>
-      </c>
-      <c r="E80" s="7"/>
+      <c r="C80" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="12">
+        <v>10000</v>
+      </c>
+      <c r="E80" s="11"/>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -26915,16 +26922,16 @@
     </row>
     <row r="81" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>372</v>
+        <v>316</v>
       </c>
       <c r="D81" s="9">
-        <v>90000</v>
+        <v>10000</v>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
@@ -26949,13 +26956,13 @@
     </row>
     <row r="82" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="D82" s="9">
         <v>40000</v>
@@ -26982,9 +26989,18 @@
       <c r="X82" s="7"/>
     </row>
     <row r="83" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="9"/>
+      <c r="A83" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D83" s="9">
+        <v>90000</v>
+      </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
@@ -27007,9 +27023,18 @@
       <c r="X83" s="7"/>
     </row>
     <row r="84" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="9"/>
+      <c r="A84" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D84" s="9">
+        <v>40000</v>
+      </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
@@ -39656,8 +39681,8 @@
       <c r="X589" s="7"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F82">
-    <sortCondition ref="E2:E82"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F84">
+    <sortCondition ref="E2:E84"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F37F3DD-24FE-4729-8069-F8D7965C8870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA47E402-3FA1-48DB-A3E3-31F6433C5FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="1ST TERM REMIT" sheetId="12" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1ST TERM ACCOUNT'!$A$1:$AE$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1ST TERM ACCOUNT'!$A$1:$AE$139</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1ST TERM ACCOUNT'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="418">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -1256,6 +1256,42 @@
   <si>
     <t>OSIGWE FAMILY</t>
   </si>
+  <si>
+    <t>NURUDEEN</t>
+  </si>
+  <si>
+    <t>ABU-BAKIR</t>
+  </si>
+  <si>
+    <t>NURUDEEN ABU-BAKIR</t>
+  </si>
+  <si>
+    <t>NIP:PATRICK OBEH ONOJA</t>
+  </si>
+  <si>
+    <t>NIP:RUTH KEMI OLADEHINDE</t>
+  </si>
+  <si>
+    <t>NIP:TIAMIYU ADEWALE NAJEEM</t>
+  </si>
+  <si>
+    <t>NIP:OLAKUNLE ISAAC OLADAPO</t>
+  </si>
+  <si>
+    <t>ONOJA MIRACLE</t>
+  </si>
+  <si>
+    <t>JOHN FAMILY</t>
+  </si>
+  <si>
+    <t>OLUNIYI DAVID</t>
+  </si>
+  <si>
+    <t>OLADAPO FAMILY</t>
+  </si>
+  <si>
+    <t>TIAMIYU AISHAT</t>
+  </si>
 </sst>
 </file>
 
@@ -1750,7 +1786,7 @@
   <sheetPr codeName="Sheet10">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF997"/>
+  <dimension ref="A1:AF998"/>
   <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="21" bestFit="1" customWidth="1"/>
@@ -8287,7 +8323,7 @@
         <v>22400</v>
       </c>
       <c r="P61" s="24">
-        <v>14330</v>
+        <v>25730</v>
       </c>
       <c r="Q61" s="24">
         <v>12000</v>
@@ -8318,14 +8354,14 @@
       </c>
       <c r="Z61" s="24">
         <f>SUM(J61:Y61)</f>
-        <v>102730</v>
+        <v>114130</v>
       </c>
       <c r="AA61" s="24">
         <v>100000</v>
       </c>
       <c r="AB61" s="20">
         <f>Z61-AA61</f>
-        <v>2730</v>
+        <v>14130</v>
       </c>
       <c r="AC61" s="24" t="str">
         <f>IF(AND($T61=6000, ($T61+$W61-$AB61)&gt;=6000),T61,"")</f>
@@ -9829,11 +9865,11 @@
         <v>45930</v>
       </c>
       <c r="AA75" s="24">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="AB75" s="20">
         <f>Z75-AA75</f>
-        <v>45930</v>
+        <v>30930</v>
       </c>
       <c r="AC75" s="24" t="str">
         <f>IF(AND($T75=6000, ($T75+$W75-$AB75)&gt;=6000),T75,"")</f>
@@ -9937,11 +9973,11 @@
         <v>45930</v>
       </c>
       <c r="AA76" s="24">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="AB76" s="20">
         <f>Z76-AA76</f>
-        <v>45930</v>
+        <v>30930</v>
       </c>
       <c r="AC76" s="24" t="str">
         <f>IF(AND($T76=6000, ($T76+$W76-$AB76)&gt;=6000),T76,"")</f>
@@ -10045,11 +10081,11 @@
         <v>69140</v>
       </c>
       <c r="AA77" s="24">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AB77" s="20">
         <f>Z77-AA77</f>
-        <v>69140</v>
+        <v>49140</v>
       </c>
       <c r="AC77" s="24" t="str">
         <f>IF(AND($T77=6000, ($T77+$W77-$AB77)&gt;=6000),T77,"")</f>
@@ -11577,66 +11613,66 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="22" t="s">
-        <v>207</v>
+        <v>406</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>217</v>
+        <v>407</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>49</v>
+        <v>332</v>
       </c>
       <c r="D92" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E92" s="24">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F92" s="24">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="G92" s="24">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H92" s="24">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I92" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J92" s="24">
         <f>(1-$D92)*E92</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K92" s="24">
         <f>(1-$D92)*F92</f>
-        <v>19500</v>
+        <v>33000</v>
       </c>
       <c r="L92" s="24">
         <f>G92</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M92" s="24">
         <f>(1-$D92)*H92</f>
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="N92" s="24">
         <f>(1-$D92)*I92</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="O92" s="24">
-        <v>6840</v>
+        <v>19320</v>
       </c>
       <c r="P92" s="24">
-        <v>5300</v>
+        <v>16190</v>
       </c>
       <c r="Q92" s="24">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="R92" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="S92" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T92" s="24">
         <v>0</v>
@@ -11654,18 +11690,18 @@
         <v>0</v>
       </c>
       <c r="Y92" s="24">
-        <v>19200</v>
+        <v>0</v>
       </c>
       <c r="Z92" s="24">
         <f>SUM(J92:Y92)</f>
-        <v>55590</v>
+        <v>112510</v>
       </c>
       <c r="AA92" s="24">
-        <v>25000</v>
+        <v>90000</v>
       </c>
       <c r="AB92" s="20">
         <f>Z92-AA92</f>
-        <v>30590</v>
+        <v>22510</v>
       </c>
       <c r="AC92" s="24" t="str">
         <f>IF(AND($T92=6000, ($T92+$W92-$AB92)&gt;=6000),T92,"")</f>
@@ -11679,16 +11715,14 @@
         <f>IF(($T92+$W92-$AB92)&gt;=$T92+8000,W92,"")</f>
         <v/>
       </c>
-      <c r="AF92" s="25" t="s">
-        <v>325</v>
-      </c>
+      <c r="AF92" s="25"/>
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
         <v>207</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C93" s="22" t="s">
         <v>49</v>
@@ -11793,19 +11827,19 @@
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="22" t="s">
-        <v>349</v>
+        <v>207</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D94" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E94" s="24">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F94" s="24">
         <v>26000</v>
@@ -11821,11 +11855,11 @@
       </c>
       <c r="J94" s="24">
         <f>(1-$D94)*E94</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K94" s="24">
         <f>(1-$D94)*F94</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L94" s="24">
         <f>G94</f>
@@ -11833,26 +11867,26 @@
       </c>
       <c r="M94" s="24">
         <f>(1-$D94)*H94</f>
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="N94" s="24">
         <f>(1-$D94)*I94</f>
         <v>0</v>
       </c>
       <c r="O94" s="24">
-        <v>13380</v>
+        <v>6840</v>
       </c>
       <c r="P94" s="24">
-        <v>7550</v>
+        <v>5300</v>
       </c>
       <c r="Q94" s="24">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R94" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S94" s="24">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T94" s="24">
         <v>0</v>
@@ -11870,18 +11904,18 @@
         <v>0</v>
       </c>
       <c r="Y94" s="24">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="Z94" s="24">
         <f>SUM(J94:Y94)</f>
-        <v>84930</v>
+        <v>55590</v>
       </c>
       <c r="AA94" s="24">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="AB94" s="20">
         <f>Z94-AA94</f>
-        <v>84930</v>
+        <v>30590</v>
       </c>
       <c r="AC94" s="24" t="str">
         <f>IF(AND($T94=6000, ($T94+$W94-$AB94)&gt;=6000),T94,"")</f>
@@ -11895,20 +11929,22 @@
         <f>IF(($T94+$W94-$AB94)&gt;=$T94+8000,W94,"")</f>
         <v/>
       </c>
-      <c r="AF94" s="24"/>
+      <c r="AF94" s="25" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="22" t="s">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D95" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E95" s="24">
         <v>2000</v>
@@ -11927,11 +11963,11 @@
       </c>
       <c r="J95" s="24">
         <f>(1-$D95)*E95</f>
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="K95" s="24">
         <f>(1-$D95)*F95</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L95" s="24">
         <f>G95</f>
@@ -11939,17 +11975,17 @@
       </c>
       <c r="M95" s="24">
         <f>(1-$D95)*H95</f>
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N95" s="24">
         <f>(1-$D95)*I95</f>
         <v>0</v>
       </c>
       <c r="O95" s="24">
-        <v>24930</v>
+        <v>13380</v>
       </c>
       <c r="P95" s="24">
-        <v>10730</v>
+        <v>7550</v>
       </c>
       <c r="Q95" s="24">
         <v>16000</v>
@@ -11980,14 +12016,14 @@
       </c>
       <c r="Z95" s="24">
         <f>SUM(J95:Y95)</f>
-        <v>92410</v>
+        <v>84930</v>
       </c>
       <c r="AA95" s="24">
-        <v>13670</v>
+        <v>0</v>
       </c>
       <c r="AB95" s="20">
         <f>Z95-AA95</f>
-        <v>78740</v>
+        <v>84930</v>
       </c>
       <c r="AC95" s="24" t="str">
         <f>IF(AND($T95=6000, ($T95+$W95-$AB95)&gt;=6000),T95,"")</f>
@@ -12001,19 +12037,17 @@
         <f>IF(($T95+$W95-$AB95)&gt;=$T95+8000,W95,"")</f>
         <v/>
       </c>
-      <c r="AF95" s="25" t="s">
-        <v>325</v>
-      </c>
+      <c r="AF95" s="24"/>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="22" t="s">
         <v>288</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D96" s="23">
         <v>0.25</v>
@@ -12054,10 +12088,10 @@
         <v>0</v>
       </c>
       <c r="O96" s="24">
-        <v>6840</v>
+        <v>24930</v>
       </c>
       <c r="P96" s="24">
-        <v>5300</v>
+        <v>10730</v>
       </c>
       <c r="Q96" s="24">
         <v>16000</v>
@@ -12088,14 +12122,14 @@
       </c>
       <c r="Z96" s="24">
         <f>SUM(J96:Y96)</f>
-        <v>68890</v>
+        <v>92410</v>
       </c>
       <c r="AA96" s="24">
-        <v>81330</v>
+        <v>13670</v>
       </c>
       <c r="AB96" s="20">
         <f>Z96-AA96</f>
-        <v>-12440</v>
+        <v>78740</v>
       </c>
       <c r="AC96" s="24" t="str">
         <f>IF(AND($T96=6000, ($T96+$W96-$AB96)&gt;=6000),T96,"")</f>
@@ -12105,76 +12139,76 @@
         <f>IF(AND($T96=8000, ($T96+$W96-$AB96)&gt;=8000),T96,"")</f>
         <v/>
       </c>
-      <c r="AE96" s="24">
+      <c r="AE96" s="24" t="str">
         <f>IF(($T96+$W96-$AB96)&gt;=$T96+8000,W96,"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AF96" s="25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="22" t="s">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>96</v>
+        <v>289</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D97" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E97" s="24">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F97" s="24">
-        <v>40000</v>
+        <v>26000</v>
       </c>
       <c r="G97" s="24">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H97" s="24">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I97" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="J97" s="24">
         <f>(1-$D97)*E97</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K97" s="24">
         <f>(1-$D97)*F97</f>
-        <v>40000</v>
+        <v>19500</v>
       </c>
       <c r="L97" s="24">
         <f>G97</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M97" s="24">
         <f>(1-$D97)*H97</f>
-        <v>2000</v>
+        <v>750</v>
       </c>
       <c r="N97" s="24">
         <f>(1-$D97)*I97</f>
+        <v>0</v>
+      </c>
+      <c r="O97" s="24">
+        <v>6840</v>
+      </c>
+      <c r="P97" s="24">
+        <v>5300</v>
+      </c>
+      <c r="Q97" s="24">
+        <v>16000</v>
+      </c>
+      <c r="R97" s="24">
         <v>8000</v>
       </c>
-      <c r="O97" s="24">
-        <v>11880</v>
-      </c>
-      <c r="P97" s="24">
-        <v>14330</v>
-      </c>
-      <c r="Q97" s="24">
-        <v>0</v>
-      </c>
-      <c r="R97" s="24">
-        <v>0</v>
-      </c>
       <c r="S97" s="24">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T97" s="24">
         <v>0</v>
@@ -12192,18 +12226,18 @@
         <v>0</v>
       </c>
       <c r="Y97" s="24">
-        <v>5830</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="24">
         <f>SUM(J97:Y97)</f>
-        <v>87040</v>
+        <v>68890</v>
       </c>
       <c r="AA97" s="24">
-        <v>0</v>
+        <v>81330</v>
       </c>
       <c r="AB97" s="20">
         <f>Z97-AA97</f>
-        <v>87040</v>
+        <v>-12440</v>
       </c>
       <c r="AC97" s="24" t="str">
         <f>IF(AND($T97=6000, ($T97+$W97-$AB97)&gt;=6000),T97,"")</f>
@@ -12213,41 +12247,41 @@
         <f>IF(AND($T97=8000, ($T97+$W97-$AB97)&gt;=8000),T97,"")</f>
         <v/>
       </c>
-      <c r="AE97" s="24" t="str">
+      <c r="AE97" s="24">
         <f>IF(($T97+$W97-$AB97)&gt;=$T97+8000,W97,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF97" s="25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D98" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E98" s="24">
         <v>0</v>
       </c>
       <c r="F98" s="24">
-        <v>26000</v>
+        <v>40000</v>
       </c>
       <c r="G98" s="24">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H98" s="24">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I98" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J98" s="24">
         <f>(1-$D98)*E98</f>
@@ -12255,31 +12289,31 @@
       </c>
       <c r="K98" s="24">
         <f>(1-$D98)*F98</f>
-        <v>19500</v>
+        <v>40000</v>
       </c>
       <c r="L98" s="24">
         <f>G98</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M98" s="24">
         <f>(1-$D98)*H98</f>
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="N98" s="24">
         <f>(1-$D98)*I98</f>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="O98" s="24">
-        <v>6840</v>
+        <v>11880</v>
       </c>
       <c r="P98" s="24">
-        <v>5300</v>
+        <v>14330</v>
       </c>
       <c r="Q98" s="24">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R98" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S98" s="24">
         <v>0</v>
@@ -12300,18 +12334,18 @@
         <v>0</v>
       </c>
       <c r="Y98" s="24">
-        <v>0</v>
+        <v>5830</v>
       </c>
       <c r="Z98" s="24">
         <f>SUM(J98:Y98)</f>
-        <v>60390</v>
+        <v>87040</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
         <f>Z98-AA98</f>
-        <v>60390</v>
+        <v>87040</v>
       </c>
       <c r="AC98" s="24" t="str">
         <f>IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
@@ -12334,10 +12368,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D99" s="23">
         <v>0.25</v>
@@ -12346,16 +12380,16 @@
         <v>0</v>
       </c>
       <c r="F99" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G99" s="24">
         <v>4000</v>
       </c>
       <c r="H99" s="24">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="I99" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J99" s="24">
         <f>(1-$D99)*E99</f>
@@ -12363,7 +12397,7 @@
       </c>
       <c r="K99" s="24">
         <f>(1-$D99)*F99</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L99" s="24">
         <f>G99</f>
@@ -12371,23 +12405,23 @@
       </c>
       <c r="M99" s="24">
         <f>(1-$D99)*H99</f>
-        <v>1875</v>
+        <v>750</v>
       </c>
       <c r="N99" s="24">
         <f>(1-$D99)*I99</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O99" s="24">
-        <v>25970</v>
+        <v>6840</v>
       </c>
       <c r="P99" s="24">
-        <v>11330</v>
+        <v>5300</v>
       </c>
       <c r="Q99" s="24">
         <v>16000</v>
       </c>
       <c r="R99" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="S99" s="24">
         <v>0</v>
@@ -12412,14 +12446,14 @@
       </c>
       <c r="Z99" s="24">
         <f>SUM(J99:Y99)</f>
-        <v>83925</v>
+        <v>60390</v>
       </c>
       <c r="AA99" s="24">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AB99" s="20">
         <f>Z99-AA99</f>
-        <v>83925</v>
+        <v>20390</v>
       </c>
       <c r="AC99" s="24" t="str">
         <f>IF(AND($T99=6000, ($T99+$W99-$AB99)&gt;=6000),T99,"")</f>
@@ -12439,31 +12473,31 @@
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D100" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E100" s="24">
         <v>0</v>
       </c>
       <c r="F100" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G100" s="24">
         <v>4000</v>
       </c>
       <c r="H100" s="24">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I100" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J100" s="24">
         <f>(1-$D100)*E100</f>
@@ -12471,7 +12505,7 @@
       </c>
       <c r="K100" s="24">
         <f>(1-$D100)*F100</f>
-        <v>26000</v>
+        <v>21000</v>
       </c>
       <c r="L100" s="24">
         <f>G100</f>
@@ -12479,20 +12513,20 @@
       </c>
       <c r="M100" s="24">
         <f>(1-$D100)*H100</f>
-        <v>0</v>
+        <v>1875</v>
       </c>
       <c r="N100" s="24">
         <f>(1-$D100)*I100</f>
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="O100" s="24">
-        <v>13380</v>
+        <v>25970</v>
       </c>
       <c r="P100" s="24">
-        <v>7550</v>
+        <v>11330</v>
       </c>
       <c r="Q100" s="24">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="R100" s="24">
         <v>0</v>
@@ -12516,18 +12550,18 @@
         <v>0</v>
       </c>
       <c r="Y100" s="24">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="24">
         <f>SUM(J100:Y100)</f>
-        <v>47900</v>
+        <v>83925</v>
       </c>
       <c r="AA100" s="24">
-        <v>27900</v>
+        <v>40000</v>
       </c>
       <c r="AB100" s="20">
         <f>Z100-AA100</f>
-        <v>20000</v>
+        <v>43925</v>
       </c>
       <c r="AC100" s="24" t="str">
         <f>IF(AND($T100=6000, ($T100+$W100-$AB100)&gt;=6000),T100,"")</f>
@@ -12547,10 +12581,10 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="s">
-        <v>387</v>
+        <v>100</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>388</v>
+        <v>101</v>
       </c>
       <c r="C101" s="22" t="s">
         <v>44</v>
@@ -12559,7 +12593,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="24">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F101" s="24">
         <v>26000</v>
@@ -12568,14 +12602,14 @@
         <v>4000</v>
       </c>
       <c r="H101" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I101" s="24">
         <v>0</v>
       </c>
       <c r="J101" s="24">
         <f>(1-$D101)*E101</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K101" s="24">
         <f>(1-$D101)*F101</f>
@@ -12587,7 +12621,7 @@
       </c>
       <c r="M101" s="24">
         <f>(1-$D101)*H101</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N101" s="24">
         <f>(1-$D101)*I101</f>
@@ -12600,13 +12634,13 @@
         <v>7550</v>
       </c>
       <c r="Q101" s="24">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R101" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S101" s="24">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T101" s="24">
         <v>0</v>
@@ -12624,18 +12658,18 @@
         <v>0</v>
       </c>
       <c r="Y101" s="24">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="Z101" s="24">
         <f>SUM(J101:Y101)</f>
-        <v>84930</v>
+        <v>47900</v>
       </c>
       <c r="AA101" s="24">
-        <v>0</v>
+        <v>27900</v>
       </c>
       <c r="AB101" s="20">
         <f>Z101-AA101</f>
-        <v>84930</v>
+        <v>20000</v>
       </c>
       <c r="AC101" s="24" t="str">
         <f>IF(AND($T101=6000, ($T101+$W101-$AB101)&gt;=6000),T101,"")</f>
@@ -12649,23 +12683,25 @@
         <f>IF(($T101+$W101-$AB101)&gt;=$T101+8000,W101,"")</f>
         <v/>
       </c>
-      <c r="AF101" s="24"/>
+      <c r="AF101" s="25" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" s="22" t="s">
-        <v>204</v>
+        <v>387</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>205</v>
+        <v>388</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D102" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E102" s="24">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F102" s="24">
         <v>26000</v>
@@ -12681,11 +12717,11 @@
       </c>
       <c r="J102" s="24">
         <f>(1-$D102)*E102</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K102" s="24">
         <f>(1-$D102)*F102</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L102" s="24">
         <f>G102</f>
@@ -12693,26 +12729,26 @@
       </c>
       <c r="M102" s="24">
         <f>(1-$D102)*H102</f>
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="N102" s="24">
         <f>(1-$D102)*I102</f>
         <v>0</v>
       </c>
       <c r="O102" s="24">
-        <v>6840</v>
+        <v>13380</v>
       </c>
       <c r="P102" s="24">
-        <v>5300</v>
+        <v>7550</v>
       </c>
       <c r="Q102" s="24">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="R102" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="S102" s="24">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T102" s="24">
         <v>0</v>
@@ -12730,18 +12766,18 @@
         <v>0</v>
       </c>
       <c r="Y102" s="24">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="24">
         <f>SUM(J102:Y102)</f>
-        <v>39890</v>
+        <v>84930</v>
       </c>
       <c r="AA102" s="24">
         <v>0</v>
       </c>
       <c r="AB102" s="20">
         <f>Z102-AA102</f>
-        <v>39890</v>
+        <v>84930</v>
       </c>
       <c r="AC102" s="24" t="str">
         <f>IF(AND($T102=6000, ($T102+$W102-$AB102)&gt;=6000),T102,"")</f>
@@ -12755,22 +12791,20 @@
         <f>IF(($T102+$W102-$AB102)&gt;=$T102+8000,W102,"")</f>
         <v/>
       </c>
-      <c r="AF102" s="25" t="s">
-        <v>325</v>
-      </c>
+      <c r="AF102" s="24"/>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D103" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E103" s="24">
         <v>0</v>
@@ -12782,7 +12816,7 @@
         <v>4000</v>
       </c>
       <c r="H103" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I103" s="24">
         <v>0</v>
@@ -12793,7 +12827,7 @@
       </c>
       <c r="K103" s="24">
         <f>(1-$D103)*F103</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L103" s="24">
         <f>G103</f>
@@ -12801,17 +12835,17 @@
       </c>
       <c r="M103" s="24">
         <f>(1-$D103)*H103</f>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="N103" s="24">
         <f>(1-$D103)*I103</f>
         <v>0</v>
       </c>
       <c r="O103" s="24">
-        <v>13380</v>
+        <v>6840</v>
       </c>
       <c r="P103" s="24">
-        <v>4850</v>
+        <v>5300</v>
       </c>
       <c r="Q103" s="24">
         <v>0</v>
@@ -12823,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="T103" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U103" s="24">
         <v>0</v>
@@ -12838,18 +12872,18 @@
         <v>0</v>
       </c>
       <c r="Y103" s="24">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="Z103" s="24">
         <f>SUM(J103:Y103)</f>
-        <v>54230</v>
+        <v>39890</v>
       </c>
       <c r="AA103" s="24">
-        <v>44700</v>
+        <v>0</v>
       </c>
       <c r="AB103" s="20">
         <f>Z103-AA103</f>
-        <v>9530</v>
+        <v>39890</v>
       </c>
       <c r="AC103" s="24" t="str">
         <f>IF(AND($T103=6000, ($T103+$W103-$AB103)&gt;=6000),T103,"")</f>
@@ -12869,16 +12903,16 @@
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="C104" s="22" t="s">
         <v>44</v>
       </c>
       <c r="D104" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E104" s="24">
         <v>0</v>
@@ -12901,7 +12935,7 @@
       </c>
       <c r="K104" s="24">
         <f>(1-$D104)*F104</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L104" s="24">
         <f>G104</f>
@@ -12919,7 +12953,7 @@
         <v>13380</v>
       </c>
       <c r="P104" s="24">
-        <v>7550</v>
+        <v>4850</v>
       </c>
       <c r="Q104" s="24">
         <v>0</v>
@@ -12950,14 +12984,14 @@
       </c>
       <c r="Z104" s="24">
         <f>SUM(J104:Y104)</f>
-        <v>50430</v>
+        <v>54230</v>
       </c>
       <c r="AA104" s="24">
-        <v>0</v>
+        <v>44700</v>
       </c>
       <c r="AB104" s="20">
         <f>Z104-AA104</f>
-        <v>50430</v>
+        <v>9530</v>
       </c>
       <c r="AC104" s="24" t="str">
         <f>IF(AND($T104=6000, ($T104+$W104-$AB104)&gt;=6000),T104,"")</f>
@@ -12980,10 +13014,10 @@
         <v>102</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D105" s="23">
         <v>0.25</v>
@@ -12992,16 +13026,16 @@
         <v>0</v>
       </c>
       <c r="F105" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G105" s="24">
         <v>4000</v>
       </c>
       <c r="H105" s="24">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I105" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J105" s="24">
         <f>(1-$D105)*E105</f>
@@ -13009,7 +13043,7 @@
       </c>
       <c r="K105" s="24">
         <f>(1-$D105)*F105</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L105" s="24">
         <f>G105</f>
@@ -13017,17 +13051,17 @@
       </c>
       <c r="M105" s="24">
         <f>(1-$D105)*H105</f>
-        <v>1875</v>
+        <v>0</v>
       </c>
       <c r="N105" s="24">
         <f>(1-$D105)*I105</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O105" s="24">
-        <v>25970</v>
+        <v>13380</v>
       </c>
       <c r="P105" s="24">
-        <v>11330</v>
+        <v>7550</v>
       </c>
       <c r="Q105" s="24">
         <v>0</v>
@@ -13058,14 +13092,14 @@
       </c>
       <c r="Z105" s="24">
         <f>SUM(J105:Y105)</f>
-        <v>73925</v>
+        <v>50430</v>
       </c>
       <c r="AA105" s="24">
         <v>0</v>
       </c>
       <c r="AB105" s="20">
         <f>Z105-AA105</f>
-        <v>73925</v>
+        <v>50430</v>
       </c>
       <c r="AC105" s="24" t="str">
         <f>IF(AND($T105=6000, ($T105+$W105-$AB105)&gt;=6000),T105,"")</f>
@@ -13088,10 +13122,10 @@
         <v>102</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D106" s="23">
         <v>0.25</v>
@@ -13106,7 +13140,7 @@
         <v>4000</v>
       </c>
       <c r="H106" s="24">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I106" s="24">
         <v>5000</v>
@@ -13125,17 +13159,17 @@
       </c>
       <c r="M106" s="24">
         <f>(1-$D106)*H106</f>
-        <v>0</v>
+        <v>1875</v>
       </c>
       <c r="N106" s="24">
         <f>(1-$D106)*I106</f>
         <v>3750</v>
       </c>
       <c r="O106" s="24">
-        <v>27310</v>
+        <v>25970</v>
       </c>
       <c r="P106" s="24">
-        <v>13230</v>
+        <v>11330</v>
       </c>
       <c r="Q106" s="24">
         <v>0</v>
@@ -13166,14 +13200,14 @@
       </c>
       <c r="Z106" s="24">
         <f>SUM(J106:Y106)</f>
-        <v>75290</v>
+        <v>73925</v>
       </c>
       <c r="AA106" s="24">
         <v>0</v>
       </c>
       <c r="AB106" s="20">
         <f>Z106-AA106</f>
-        <v>75290</v>
+        <v>73925</v>
       </c>
       <c r="AC106" s="24" t="str">
         <f>IF(AND($T106=6000, ($T106+$W106-$AB106)&gt;=6000),T106,"")</f>
@@ -13193,16 +13227,16 @@
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D107" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E107" s="24">
         <v>0</v>
@@ -13214,7 +13248,7 @@
         <v>4000</v>
       </c>
       <c r="H107" s="24">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I107" s="24">
         <v>5000</v>
@@ -13225,7 +13259,7 @@
       </c>
       <c r="K107" s="24">
         <f>(1-$D107)*F107</f>
-        <v>28000</v>
+        <v>21000</v>
       </c>
       <c r="L107" s="24">
         <f>G107</f>
@@ -13233,17 +13267,17 @@
       </c>
       <c r="M107" s="24">
         <f>(1-$D107)*H107</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="N107" s="24">
         <f>(1-$D107)*I107</f>
-        <v>5000</v>
+        <v>3750</v>
       </c>
       <c r="O107" s="24">
-        <v>25970</v>
+        <v>27310</v>
       </c>
       <c r="P107" s="24">
-        <v>11330</v>
+        <v>13230</v>
       </c>
       <c r="Q107" s="24">
         <v>0</v>
@@ -13255,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="T107" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U107" s="24">
         <v>0</v>
@@ -13274,14 +13308,14 @@
       </c>
       <c r="Z107" s="24">
         <f>SUM(J107:Y107)</f>
-        <v>76800</v>
+        <v>75290</v>
       </c>
       <c r="AA107" s="24">
         <v>0</v>
       </c>
       <c r="AB107" s="20">
         <f>Z107-AA107</f>
-        <v>76800</v>
+        <v>75290</v>
       </c>
       <c r="AC107" s="24" t="str">
         <f>IF(AND($T107=6000, ($T107+$W107-$AB107)&gt;=6000),T107,"")</f>
@@ -13301,16 +13335,16 @@
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="D108" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="24">
         <v>0</v>
@@ -13322,7 +13356,7 @@
         <v>4000</v>
       </c>
       <c r="H108" s="24">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I108" s="24">
         <v>5000</v>
@@ -13333,7 +13367,7 @@
       </c>
       <c r="K108" s="24">
         <f>(1-$D108)*F108</f>
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="L108" s="24">
         <f>G108</f>
@@ -13341,17 +13375,17 @@
       </c>
       <c r="M108" s="24">
         <f>(1-$D108)*H108</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="N108" s="24">
         <f>(1-$D108)*I108</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O108" s="24">
-        <v>27330</v>
+        <v>25970</v>
       </c>
       <c r="P108" s="24">
-        <v>13230</v>
+        <v>11330</v>
       </c>
       <c r="Q108" s="24">
         <v>0</v>
@@ -13363,7 +13397,7 @@
         <v>0</v>
       </c>
       <c r="T108" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U108" s="24">
         <v>0</v>
@@ -13382,14 +13416,14 @@
       </c>
       <c r="Z108" s="24">
         <f>SUM(J108:Y108)</f>
-        <v>50560</v>
+        <v>76800</v>
       </c>
       <c r="AA108" s="24">
         <v>0</v>
       </c>
       <c r="AB108" s="20">
         <f>Z108-AA108</f>
-        <v>50560</v>
+        <v>76800</v>
       </c>
       <c r="AC108" s="24" t="str">
         <f>IF(AND($T108=6000, ($T108+$W108-$AB108)&gt;=6000),T108,"")</f>
@@ -13409,31 +13443,31 @@
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B109" s="22" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D109" s="23">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E109" s="24">
         <v>0</v>
       </c>
       <c r="F109" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G109" s="24">
         <v>4000</v>
       </c>
       <c r="H109" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I109" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J109" s="24">
         <f>(1-$D109)*E109</f>
@@ -13441,7 +13475,7 @@
       </c>
       <c r="K109" s="24">
         <f>(1-$D109)*F109</f>
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L109" s="24">
         <f>G109</f>
@@ -13449,17 +13483,17 @@
       </c>
       <c r="M109" s="24">
         <f>(1-$D109)*H109</f>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="N109" s="24">
         <f>(1-$D109)*I109</f>
         <v>0</v>
       </c>
       <c r="O109" s="24">
-        <v>12480</v>
+        <v>27330</v>
       </c>
       <c r="P109" s="24">
-        <v>7550</v>
+        <v>13230</v>
       </c>
       <c r="Q109" s="24">
         <v>0</v>
@@ -13486,22 +13520,22 @@
         <v>0</v>
       </c>
       <c r="Y109" s="24">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z109" s="24">
         <f>SUM(J109:Y109)</f>
-        <v>50345</v>
+        <v>50560</v>
       </c>
       <c r="AA109" s="24">
-        <v>50345</v>
+        <v>30000</v>
       </c>
       <c r="AB109" s="20">
         <f>Z109-AA109</f>
-        <v>0</v>
-      </c>
-      <c r="AC109" s="24">
+        <v>20560</v>
+      </c>
+      <c r="AC109" s="24" t="str">
         <f>IF(AND($T109=6000, ($T109+$W109-$AB109)&gt;=6000),T109,"")</f>
-        <v>6000</v>
+        <v/>
       </c>
       <c r="AD109" s="24" t="str">
         <f>IF(AND($T109=8000, ($T109+$W109-$AB109)&gt;=8000),T109,"")</f>
@@ -13520,10 +13554,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D110" s="23">
         <v>0.25</v>
@@ -13532,16 +13566,16 @@
         <v>0</v>
       </c>
       <c r="F110" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G110" s="24">
         <v>4000</v>
       </c>
       <c r="H110" s="24">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="I110" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J110" s="24">
         <f>(1-$D110)*E110</f>
@@ -13549,7 +13583,7 @@
       </c>
       <c r="K110" s="24">
         <f>(1-$D110)*F110</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L110" s="24">
         <f>G110</f>
@@ -13557,17 +13591,17 @@
       </c>
       <c r="M110" s="24">
         <f>(1-$D110)*H110</f>
-        <v>1875</v>
+        <v>750</v>
       </c>
       <c r="N110" s="24">
         <f>(1-$D110)*I110</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O110" s="24">
-        <v>25970</v>
+        <v>12480</v>
       </c>
       <c r="P110" s="24">
-        <v>11330</v>
+        <v>7550</v>
       </c>
       <c r="Q110" s="24">
         <v>0</v>
@@ -13594,14 +13628,14 @@
         <v>0</v>
       </c>
       <c r="Y110" s="24">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Z110" s="24">
         <f>SUM(J110:Y110)</f>
-        <v>73925</v>
+        <v>50345</v>
       </c>
       <c r="AA110" s="24">
-        <v>73925</v>
+        <v>50345</v>
       </c>
       <c r="AB110" s="20">
         <f>Z110-AA110</f>
@@ -13625,31 +13659,31 @@
     </row>
     <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="D111" s="23">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E111" s="24">
         <v>0</v>
       </c>
       <c r="F111" s="24">
-        <v>33000</v>
+        <v>28000</v>
       </c>
       <c r="G111" s="24">
+        <v>4000</v>
+      </c>
+      <c r="H111" s="24">
+        <v>2500</v>
+      </c>
+      <c r="I111" s="24">
         <v>5000</v>
-      </c>
-      <c r="H111" s="24">
-        <v>2000</v>
-      </c>
-      <c r="I111" s="24">
-        <v>6000</v>
       </c>
       <c r="J111" s="24">
         <f>(1-$D111)*E111</f>
@@ -13657,25 +13691,25 @@
       </c>
       <c r="K111" s="24">
         <f>(1-$D111)*F111</f>
-        <v>23100</v>
+        <v>21000</v>
       </c>
       <c r="L111" s="24">
         <f>G111</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M111" s="24">
         <f>(1-$D111)*H111</f>
-        <v>1400</v>
+        <v>1875</v>
       </c>
       <c r="N111" s="24">
         <f>(1-$D111)*I111</f>
-        <v>4200</v>
+        <v>3750</v>
       </c>
       <c r="O111" s="24">
-        <v>22400</v>
+        <v>25970</v>
       </c>
       <c r="P111" s="24">
-        <v>14330</v>
+        <v>11330</v>
       </c>
       <c r="Q111" s="24">
         <v>0</v>
@@ -13687,7 +13721,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U111" s="24">
         <v>0</v>
@@ -13706,18 +13740,18 @@
       </c>
       <c r="Z111" s="24">
         <f>SUM(J111:Y111)</f>
-        <v>70430</v>
+        <v>73925</v>
       </c>
       <c r="AA111" s="24">
-        <v>0</v>
+        <v>73925</v>
       </c>
       <c r="AB111" s="20">
         <f>Z111-AA111</f>
-        <v>70430</v>
-      </c>
-      <c r="AC111" s="24" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="24">
         <f>IF(AND($T111=6000, ($T111+$W111-$AB111)&gt;=6000),T111,"")</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="AD111" s="24" t="str">
         <f>IF(AND($T111=8000, ($T111+$W111-$AB111)&gt;=8000),T111,"")</f>
@@ -13733,31 +13767,31 @@
     </row>
     <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D112" s="23">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="E112" s="24">
         <v>0</v>
       </c>
       <c r="F112" s="24">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="G112" s="24">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H112" s="24">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I112" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J112" s="24">
         <f>(1-$D112)*E112</f>
@@ -13765,25 +13799,25 @@
       </c>
       <c r="K112" s="24">
         <f>(1-$D112)*F112</f>
-        <v>24700</v>
+        <v>23100</v>
       </c>
       <c r="L112" s="24">
         <f>G112</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M112" s="24">
         <f>(1-$D112)*H112</f>
-        <v>950</v>
+        <v>1400</v>
       </c>
       <c r="N112" s="24">
         <f>(1-$D112)*I112</f>
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="O112" s="24">
-        <v>6840</v>
+        <v>22400</v>
       </c>
       <c r="P112" s="24">
-        <v>5300</v>
+        <v>14330</v>
       </c>
       <c r="Q112" s="24">
         <v>0</v>
@@ -13810,18 +13844,18 @@
         <v>0</v>
       </c>
       <c r="Y112" s="24">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="Z112" s="24">
         <f>SUM(J112:Y112)</f>
-        <v>31790</v>
+        <v>70430</v>
       </c>
       <c r="AA112" s="24">
-        <v>33140</v>
+        <v>0</v>
       </c>
       <c r="AB112" s="20">
         <f>Z112-AA112</f>
-        <v>-1350</v>
+        <v>70430</v>
       </c>
       <c r="AC112" s="24" t="str">
         <f>IF(AND($T112=6000, ($T112+$W112-$AB112)&gt;=6000),T112,"")</f>
@@ -13836,21 +13870,21 @@
         <v/>
       </c>
       <c r="AF112" s="25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D113" s="23">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="E113" s="24">
         <v>0</v>
@@ -13862,7 +13896,7 @@
         <v>4000</v>
       </c>
       <c r="H113" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I113" s="24">
         <v>0</v>
@@ -13873,7 +13907,7 @@
       </c>
       <c r="K113" s="24">
         <f>(1-$D113)*F113</f>
-        <v>13000</v>
+        <v>24700</v>
       </c>
       <c r="L113" s="24">
         <f>G113</f>
@@ -13881,17 +13915,17 @@
       </c>
       <c r="M113" s="24">
         <f>(1-$D113)*H113</f>
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="N113" s="24">
         <f>(1-$D113)*I113</f>
         <v>0</v>
       </c>
       <c r="O113" s="24">
-        <v>13380</v>
+        <v>6840</v>
       </c>
       <c r="P113" s="24">
-        <v>7550</v>
+        <v>5300</v>
       </c>
       <c r="Q113" s="24">
         <v>0</v>
@@ -13918,18 +13952,18 @@
         <v>0</v>
       </c>
       <c r="Y113" s="24">
-        <v>8000</v>
+        <v>-10000</v>
       </c>
       <c r="Z113" s="24">
         <f>SUM(J113:Y113)</f>
-        <v>45930</v>
+        <v>31790</v>
       </c>
       <c r="AA113" s="24">
-        <v>0</v>
+        <v>33140</v>
       </c>
       <c r="AB113" s="20">
         <f>Z113-AA113</f>
-        <v>45930</v>
+        <v>-1350</v>
       </c>
       <c r="AC113" s="24" t="str">
         <f>IF(AND($T113=6000, ($T113+$W113-$AB113)&gt;=6000),T113,"")</f>
@@ -13944,7 +13978,7 @@
         <v/>
       </c>
       <c r="AF113" s="25" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.25">
@@ -13952,10 +13986,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D114" s="23">
         <v>0.5</v>
@@ -13964,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G114" s="24">
         <v>4000</v>
@@ -13973,7 +14007,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J114" s="24">
         <f>(1-$D114)*E114</f>
@@ -13981,7 +14015,7 @@
       </c>
       <c r="K114" s="24">
         <f>(1-$D114)*F114</f>
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="L114" s="24">
         <f>G114</f>
@@ -13993,13 +14027,13 @@
       </c>
       <c r="N114" s="24">
         <f>(1-$D114)*I114</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="O114" s="24">
-        <v>26150</v>
+        <v>13380</v>
       </c>
       <c r="P114" s="24">
-        <v>11330</v>
+        <v>7550</v>
       </c>
       <c r="Q114" s="24">
         <v>0</v>
@@ -14026,18 +14060,18 @@
         <v>0</v>
       </c>
       <c r="Y114" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="Z114" s="24">
         <f>SUM(J114:Y114)</f>
-        <v>57980</v>
+        <v>45930</v>
       </c>
       <c r="AA114" s="24">
         <v>0</v>
       </c>
       <c r="AB114" s="20">
         <f>Z114-AA114</f>
-        <v>57980</v>
+        <v>45930</v>
       </c>
       <c r="AC114" s="24" t="str">
         <f>IF(AND($T114=6000, ($T114+$W114-$AB114)&gt;=6000),T114,"")</f>
@@ -14057,39 +14091,39 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="22" t="s">
-        <v>391</v>
+        <v>113</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>392</v>
+        <v>114</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D115" s="23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E115" s="24">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F115" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G115" s="24">
         <v>4000</v>
       </c>
       <c r="H115" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I115" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J115" s="24">
         <f>(1-$D115)*E115</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K115" s="24">
         <f>(1-$D115)*F115</f>
-        <v>26000</v>
+        <v>14000</v>
       </c>
       <c r="L115" s="24">
         <f>G115</f>
@@ -14097,26 +14131,26 @@
       </c>
       <c r="M115" s="24">
         <f>(1-$D115)*H115</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N115" s="24">
         <f>(1-$D115)*I115</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="O115" s="24">
-        <v>24930</v>
+        <v>26150</v>
       </c>
       <c r="P115" s="24">
-        <v>10730</v>
+        <v>11330</v>
       </c>
       <c r="Q115" s="24">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="R115" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="S115" s="24">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T115" s="24">
         <v>0</v>
@@ -14138,14 +14172,14 @@
       </c>
       <c r="Z115" s="24">
         <f>SUM(J115:Y115)</f>
-        <v>99660</v>
+        <v>57980</v>
       </c>
       <c r="AA115" s="24">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="AB115" s="20">
         <f>Z115-AA115</f>
-        <v>19660</v>
+        <v>57980</v>
       </c>
       <c r="AC115" s="24" t="str">
         <f>IF(AND($T115=6000, ($T115+$W115-$AB115)&gt;=6000),T115,"")</f>
@@ -14165,43 +14199,43 @@
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" s="22" t="s">
-        <v>116</v>
+        <v>391</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>117</v>
+        <v>392</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D116" s="23">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E116" s="24">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F116" s="24">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="G116" s="24">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H116" s="24">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I116" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J116" s="24">
         <f>(1-$D116)*E116</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K116" s="24">
         <f>(1-$D116)*F116</f>
-        <v>16500</v>
+        <v>26000</v>
       </c>
       <c r="L116" s="24">
         <f>G116</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M116" s="24">
         <f>(1-$D116)*H116</f>
@@ -14209,25 +14243,25 @@
       </c>
       <c r="N116" s="24">
         <f>(1-$D116)*I116</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="O116" s="24">
-        <v>22400</v>
+        <v>24930</v>
       </c>
       <c r="P116" s="24">
-        <v>14330</v>
+        <v>10730</v>
       </c>
       <c r="Q116" s="24">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="R116" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="S116" s="24">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T116" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U116" s="24">
         <v>0</v>
@@ -14242,18 +14276,18 @@
         <v>0</v>
       </c>
       <c r="Y116" s="24">
-        <v>-3145</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="24">
         <f>SUM(J116:Y116)</f>
-        <v>67085</v>
+        <v>99660</v>
       </c>
       <c r="AA116" s="24">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="AB116" s="20">
         <f>Z116-AA116</f>
-        <v>67085</v>
+        <v>19660</v>
       </c>
       <c r="AC116" s="24" t="str">
         <f>IF(AND($T116=6000, ($T116+$W116-$AB116)&gt;=6000),T116,"")</f>
@@ -14273,31 +14307,31 @@
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" s="22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D117" s="23">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E117" s="24">
         <v>0</v>
       </c>
       <c r="F117" s="24">
-        <v>26000</v>
+        <v>33000</v>
       </c>
       <c r="G117" s="24">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H117" s="24">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I117" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="J117" s="24">
         <f>(1-$D117)*E117</f>
@@ -14305,38 +14339,38 @@
       </c>
       <c r="K117" s="24">
         <f>(1-$D117)*F117</f>
-        <v>19500</v>
+        <v>16500</v>
       </c>
       <c r="L117" s="24">
         <f>G117</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M117" s="24">
         <f>(1-$D117)*H117</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N117" s="24">
         <f>(1-$D117)*I117</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="O117" s="24">
-        <v>13380</v>
+        <v>22400</v>
       </c>
       <c r="P117" s="24">
-        <v>5300</v>
+        <v>14330</v>
       </c>
       <c r="Q117" s="24">
+        <v>0</v>
+      </c>
+      <c r="R117" s="24">
+        <v>0</v>
+      </c>
+      <c r="S117" s="24">
+        <v>0</v>
+      </c>
+      <c r="T117" s="24">
         <v>8000</v>
       </c>
-      <c r="R117" s="24">
-        <v>0</v>
-      </c>
-      <c r="S117" s="24">
-        <v>0</v>
-      </c>
-      <c r="T117" s="24">
-        <v>0</v>
-      </c>
       <c r="U117" s="24">
         <v>0</v>
       </c>
@@ -14350,18 +14384,18 @@
         <v>0</v>
       </c>
       <c r="Y117" s="24">
-        <v>0</v>
+        <v>-3145</v>
       </c>
       <c r="Z117" s="24">
         <f>SUM(J117:Y117)</f>
-        <v>50180</v>
+        <v>67085</v>
       </c>
       <c r="AA117" s="24">
-        <v>27120</v>
+        <v>30000</v>
       </c>
       <c r="AB117" s="20">
         <f>Z117-AA117</f>
-        <v>23060</v>
+        <v>37085</v>
       </c>
       <c r="AC117" s="24" t="str">
         <f>IF(AND($T117=6000, ($T117+$W117-$AB117)&gt;=6000),T117,"")</f>
@@ -14384,10 +14418,10 @@
         <v>118</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D118" s="23">
         <v>0.25</v>
@@ -14396,7 +14430,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G118" s="24">
         <v>4000</v>
@@ -14405,7 +14439,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J118" s="24">
         <f>(1-$D118)*E118</f>
@@ -14413,7 +14447,7 @@
       </c>
       <c r="K118" s="24">
         <f>(1-$D118)*F118</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L118" s="24">
         <f>G118</f>
@@ -14425,13 +14459,13 @@
       </c>
       <c r="N118" s="24">
         <f>(1-$D118)*I118</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O118" s="24">
-        <v>27310</v>
+        <v>13380</v>
       </c>
       <c r="P118" s="24">
-        <v>8250</v>
+        <v>5300</v>
       </c>
       <c r="Q118" s="24">
         <v>8000</v>
@@ -14462,14 +14496,14 @@
       </c>
       <c r="Z118" s="24">
         <f>SUM(J118:Y118)</f>
-        <v>72310</v>
+        <v>50180</v>
       </c>
       <c r="AA118" s="24">
         <v>27120</v>
       </c>
       <c r="AB118" s="20">
         <f>Z118-AA118</f>
-        <v>45190</v>
+        <v>23060</v>
       </c>
       <c r="AC118" s="24" t="str">
         <f>IF(AND($T118=6000, ($T118+$W118-$AB118)&gt;=6000),T118,"")</f>
@@ -14489,13 +14523,13 @@
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="C119" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D119" s="23">
         <v>0.25</v>
@@ -14504,7 +14538,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G119" s="24">
         <v>4000</v>
@@ -14513,7 +14547,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J119" s="24">
         <f>(1-$D119)*E119</f>
@@ -14521,7 +14555,7 @@
       </c>
       <c r="K119" s="24">
         <f>(1-$D119)*F119</f>
-        <v>19500</v>
+        <v>21000</v>
       </c>
       <c r="L119" s="24">
         <f>G119</f>
@@ -14533,16 +14567,16 @@
       </c>
       <c r="N119" s="24">
         <f>(1-$D119)*I119</f>
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="O119" s="24">
-        <v>24930</v>
+        <v>27310</v>
       </c>
       <c r="P119" s="24">
-        <v>10730</v>
+        <v>8250</v>
       </c>
       <c r="Q119" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="R119" s="24">
         <v>0</v>
@@ -14551,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="T119" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U119" s="24">
         <v>0</v>
@@ -14570,14 +14604,14 @@
       </c>
       <c r="Z119" s="24">
         <f>SUM(J119:Y119)</f>
-        <v>65160</v>
+        <v>72310</v>
       </c>
       <c r="AA119" s="24">
-        <v>0</v>
+        <v>27120</v>
       </c>
       <c r="AB119" s="20">
         <f>Z119-AA119</f>
-        <v>65160</v>
+        <v>45190</v>
       </c>
       <c r="AC119" s="24" t="str">
         <f>IF(AND($T119=6000, ($T119+$W119-$AB119)&gt;=6000),T119,"")</f>
@@ -14600,10 +14634,10 @@
         <v>198</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D120" s="23">
         <v>0.25</v>
@@ -14612,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G120" s="24">
         <v>4000</v>
@@ -14621,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J120" s="24">
         <f>(1-$D120)*E120</f>
@@ -14629,7 +14663,7 @@
       </c>
       <c r="K120" s="24">
         <f>(1-$D120)*F120</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L120" s="24">
         <f>G120</f>
@@ -14641,13 +14675,13 @@
       </c>
       <c r="N120" s="24">
         <f>(1-$D120)*I120</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O120" s="24">
-        <v>27310</v>
+        <v>24930</v>
       </c>
       <c r="P120" s="24">
-        <v>13230</v>
+        <v>10730</v>
       </c>
       <c r="Q120" s="24">
         <v>0</v>
@@ -14678,14 +14712,14 @@
       </c>
       <c r="Z120" s="24">
         <f>SUM(J120:Y120)</f>
-        <v>75290</v>
+        <v>65160</v>
       </c>
       <c r="AA120" s="24">
         <v>0</v>
       </c>
       <c r="AB120" s="20">
         <f>Z120-AA120</f>
-        <v>75290</v>
+        <v>65160</v>
       </c>
       <c r="AC120" s="24" t="str">
         <f>IF(AND($T120=6000, ($T120+$W120-$AB120)&gt;=6000),T120,"")</f>
@@ -14705,13 +14739,13 @@
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" s="22" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="B121" s="22" t="s">
-        <v>242</v>
+        <v>32</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>252</v>
+        <v>46</v>
       </c>
       <c r="D121" s="23">
         <v>0.25</v>
@@ -14720,16 +14754,16 @@
         <v>0</v>
       </c>
       <c r="F121" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G121" s="24">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H121" s="24">
         <v>0</v>
       </c>
       <c r="I121" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J121" s="24">
         <f>(1-$D121)*E121</f>
@@ -14737,11 +14771,11 @@
       </c>
       <c r="K121" s="24">
         <f>(1-$D121)*F121</f>
-        <v>19500</v>
+        <v>21000</v>
       </c>
       <c r="L121" s="24">
         <f>G121</f>
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M121" s="24">
         <f>(1-$D121)*H121</f>
@@ -14749,13 +14783,13 @@
       </c>
       <c r="N121" s="24">
         <f>(1-$D121)*I121</f>
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="O121" s="24">
-        <v>0</v>
+        <v>27310</v>
       </c>
       <c r="P121" s="24">
-        <v>3050</v>
+        <v>13230</v>
       </c>
       <c r="Q121" s="24">
         <v>0</v>
@@ -14767,7 +14801,7 @@
         <v>0</v>
       </c>
       <c r="T121" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U121" s="24">
         <v>0</v>
@@ -14786,14 +14820,14 @@
       </c>
       <c r="Z121" s="24">
         <f>SUM(J121:Y121)</f>
-        <v>24550</v>
+        <v>75290</v>
       </c>
       <c r="AA121" s="24">
         <v>0</v>
       </c>
       <c r="AB121" s="20">
         <f>Z121-AA121</f>
-        <v>24550</v>
+        <v>75290</v>
       </c>
       <c r="AC121" s="24" t="str">
         <f>IF(AND($T121=6000, ($T121+$W121-$AB121)&gt;=6000),T121,"")</f>
@@ -14816,10 +14850,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="22" t="s">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
       <c r="D122" s="23">
         <v>0.25</v>
@@ -14831,7 +14865,7 @@
         <v>26000</v>
       </c>
       <c r="G122" s="24">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H122" s="24">
         <v>0</v>
@@ -14849,7 +14883,7 @@
       </c>
       <c r="L122" s="24">
         <f>G122</f>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="M122" s="24">
         <f>(1-$D122)*H122</f>
@@ -14860,10 +14894,10 @@
         <v>0</v>
       </c>
       <c r="O122" s="24">
-        <v>24930</v>
+        <v>0</v>
       </c>
       <c r="P122" s="24">
-        <v>10730</v>
+        <v>3050</v>
       </c>
       <c r="Q122" s="24">
         <v>0</v>
@@ -14875,7 +14909,7 @@
         <v>0</v>
       </c>
       <c r="T122" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U122" s="24">
         <v>0</v>
@@ -14894,14 +14928,14 @@
       </c>
       <c r="Z122" s="24">
         <f>SUM(J122:Y122)</f>
-        <v>65160</v>
+        <v>24550</v>
       </c>
       <c r="AA122" s="24">
         <v>0</v>
       </c>
       <c r="AB122" s="20">
         <f>Z122-AA122</f>
-        <v>65160</v>
+        <v>24550</v>
       </c>
       <c r="AC122" s="24" t="str">
         <f>IF(AND($T122=6000, ($T122+$W122-$AB122)&gt;=6000),T122,"")</f>
@@ -14921,25 +14955,25 @@
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" s="22" t="s">
-        <v>358</v>
+        <v>121</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>359</v>
+        <v>122</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="D123" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E123" s="24">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F123" s="24">
         <v>26000</v>
       </c>
       <c r="G123" s="24">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H123" s="24">
         <v>0</v>
@@ -14949,15 +14983,15 @@
       </c>
       <c r="J123" s="24">
         <f>(1-$D123)*E123</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="K123" s="24">
         <f>(1-$D123)*F123</f>
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="L123" s="24">
         <f>G123</f>
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M123" s="24">
         <f>(1-$D123)*H123</f>
@@ -14968,10 +15002,10 @@
         <v>0</v>
       </c>
       <c r="O123" s="24">
-        <v>0</v>
+        <v>24930</v>
       </c>
       <c r="P123" s="24">
-        <v>3050</v>
+        <v>10730</v>
       </c>
       <c r="Q123" s="24">
         <v>0</v>
@@ -14983,7 +15017,7 @@
         <v>0</v>
       </c>
       <c r="T123" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U123" s="24">
         <v>0</v>
@@ -15002,14 +15036,14 @@
       </c>
       <c r="Z123" s="24">
         <f>SUM(J123:Y123)</f>
-        <v>33050</v>
+        <v>65160</v>
       </c>
       <c r="AA123" s="24">
         <v>0</v>
       </c>
       <c r="AB123" s="20">
         <f>Z123-AA123</f>
-        <v>33050</v>
+        <v>65160</v>
       </c>
       <c r="AC123" s="24" t="str">
         <f>IF(AND($T123=6000, ($T123+$W123-$AB123)&gt;=6000),T123,"")</f>
@@ -15023,29 +15057,31 @@
         <f>IF(($T123+$W123-$AB123)&gt;=$T123+8000,W123,"")</f>
         <v/>
       </c>
-      <c r="AF123" s="24"/>
+      <c r="AF123" s="25" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" s="22" t="s">
-        <v>123</v>
+        <v>358</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>124</v>
+        <v>359</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
       <c r="D124" s="23">
         <v>0</v>
       </c>
       <c r="E124" s="24">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F124" s="24">
         <v>26000</v>
       </c>
       <c r="G124" s="24">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H124" s="24">
         <v>0</v>
@@ -15055,7 +15091,7 @@
       </c>
       <c r="J124" s="24">
         <f>(1-$D124)*E124</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K124" s="24">
         <f>(1-$D124)*F124</f>
@@ -15063,7 +15099,7 @@
       </c>
       <c r="L124" s="24">
         <f>G124</f>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="M124" s="24">
         <f>(1-$D124)*H124</f>
@@ -15074,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="O124" s="24">
-        <v>24930</v>
+        <v>0</v>
       </c>
       <c r="P124" s="24">
-        <v>10730</v>
+        <v>3050</v>
       </c>
       <c r="Q124" s="24">
         <v>0</v>
@@ -15089,7 +15125,7 @@
         <v>0</v>
       </c>
       <c r="T124" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U124" s="24">
         <v>0</v>
@@ -15104,18 +15140,18 @@
         <v>0</v>
       </c>
       <c r="Y124" s="24">
-        <v>14240</v>
+        <v>0</v>
       </c>
       <c r="Z124" s="24">
         <f>SUM(J124:Y124)</f>
-        <v>85900</v>
+        <v>33050</v>
       </c>
       <c r="AA124" s="24">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AB124" s="20">
         <f>Z124-AA124</f>
-        <v>35900</v>
+        <v>33050</v>
       </c>
       <c r="AC124" s="24" t="str">
         <f>IF(AND($T124=6000, ($T124+$W124-$AB124)&gt;=6000),T124,"")</f>
@@ -15129,22 +15165,20 @@
         <f>IF(($T124+$W124-$AB124)&gt;=$T124+8000,W124,"")</f>
         <v/>
       </c>
-      <c r="AF124" s="25" t="s">
-        <v>325</v>
-      </c>
+      <c r="AF124" s="24"/>
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D125" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E125" s="24">
         <v>0</v>
@@ -15167,7 +15201,7 @@
       </c>
       <c r="K125" s="24">
         <f>(1-$D125)*F125</f>
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="L125" s="24">
         <f>G125</f>
@@ -15182,10 +15216,10 @@
         <v>0</v>
       </c>
       <c r="O125" s="24">
-        <v>13380</v>
+        <v>24930</v>
       </c>
       <c r="P125" s="24">
-        <v>7550</v>
+        <v>10730</v>
       </c>
       <c r="Q125" s="24">
         <v>0</v>
@@ -15197,7 +15231,7 @@
         <v>0</v>
       </c>
       <c r="T125" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U125" s="24">
         <v>0</v>
@@ -15212,18 +15246,18 @@
         <v>0</v>
       </c>
       <c r="Y125" s="24">
-        <v>0</v>
+        <v>14240</v>
       </c>
       <c r="Z125" s="24">
         <f>SUM(J125:Y125)</f>
-        <v>44430</v>
+        <v>85900</v>
       </c>
       <c r="AA125" s="24">
-        <v>44430</v>
+        <v>50000</v>
       </c>
       <c r="AB125" s="20">
         <f>Z125-AA125</f>
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="AC125" s="24" t="str">
         <f>IF(AND($T125=6000, ($T125+$W125-$AB125)&gt;=6000),T125,"")</f>
@@ -15246,10 +15280,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D126" s="23">
         <v>0.25</v>
@@ -15258,7 +15292,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G126" s="24">
         <v>4000</v>
@@ -15267,7 +15301,7 @@
         <v>0</v>
       </c>
       <c r="I126" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J126" s="24">
         <f>(1-$D126)*E126</f>
@@ -15275,7 +15309,7 @@
       </c>
       <c r="K126" s="24">
         <f>(1-$D126)*F126</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L126" s="24">
         <f>G126</f>
@@ -15287,13 +15321,13 @@
       </c>
       <c r="N126" s="24">
         <f>(1-$D126)*I126</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O126" s="24">
-        <v>26150</v>
+        <v>13380</v>
       </c>
       <c r="P126" s="24">
-        <v>11330</v>
+        <v>7550</v>
       </c>
       <c r="Q126" s="24">
         <v>0</v>
@@ -15324,14 +15358,14 @@
       </c>
       <c r="Z126" s="24">
         <f>SUM(J126:Y126)</f>
-        <v>66230</v>
+        <v>44430</v>
       </c>
       <c r="AA126" s="24">
-        <v>55570</v>
+        <v>44430</v>
       </c>
       <c r="AB126" s="20">
         <f>Z126-AA126</f>
-        <v>10660</v>
+        <v>0</v>
       </c>
       <c r="AC126" s="24" t="str">
         <f>IF(AND($T126=6000, ($T126+$W126-$AB126)&gt;=6000),T126,"")</f>
@@ -15354,10 +15388,10 @@
         <v>125</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>248</v>
+        <v>48</v>
       </c>
       <c r="D127" s="23">
         <v>0.25</v>
@@ -15398,10 +15432,10 @@
         <v>3750</v>
       </c>
       <c r="O127" s="24">
-        <v>28790</v>
+        <v>26150</v>
       </c>
       <c r="P127" s="24">
-        <v>13230</v>
+        <v>11330</v>
       </c>
       <c r="Q127" s="24">
         <v>0</v>
@@ -15413,7 +15447,7 @@
         <v>0</v>
       </c>
       <c r="T127" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="U127" s="24">
         <v>0</v>
@@ -15432,14 +15466,14 @@
       </c>
       <c r="Z127" s="24">
         <f>SUM(J127:Y127)</f>
-        <v>76770</v>
+        <v>66230</v>
       </c>
       <c r="AA127" s="24">
-        <v>25000</v>
+        <v>55570</v>
       </c>
       <c r="AB127" s="20">
         <f>Z127-AA127</f>
-        <v>51770</v>
+        <v>10660</v>
       </c>
       <c r="AC127" s="24" t="str">
         <f>IF(AND($T127=6000, ($T127+$W127-$AB127)&gt;=6000),T127,"")</f>
@@ -15462,10 +15496,10 @@
         <v>125</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>70</v>
+        <v>248</v>
       </c>
       <c r="D128" s="23">
         <v>0.25</v>
@@ -15474,16 +15508,16 @@
         <v>0</v>
       </c>
       <c r="F128" s="24">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="G128" s="24">
+        <v>4000</v>
+      </c>
+      <c r="H128" s="24">
+        <v>0</v>
+      </c>
+      <c r="I128" s="24">
         <v>5000</v>
-      </c>
-      <c r="H128" s="24">
-        <v>2000</v>
-      </c>
-      <c r="I128" s="24">
-        <v>8000</v>
       </c>
       <c r="J128" s="24">
         <f>(1-$D128)*E128</f>
@@ -15491,38 +15525,38 @@
       </c>
       <c r="K128" s="24">
         <f>(1-$D128)*F128</f>
-        <v>30000</v>
+        <v>21000</v>
       </c>
       <c r="L128" s="24">
         <f>G128</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M128" s="24">
         <f>(1-$D128)*H128</f>
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="N128" s="24">
         <f>(1-$D128)*I128</f>
+        <v>3750</v>
+      </c>
+      <c r="O128" s="24">
+        <v>28790</v>
+      </c>
+      <c r="P128" s="24">
+        <v>13230</v>
+      </c>
+      <c r="Q128" s="24">
+        <v>0</v>
+      </c>
+      <c r="R128" s="24">
+        <v>0</v>
+      </c>
+      <c r="S128" s="24">
+        <v>0</v>
+      </c>
+      <c r="T128" s="24">
         <v>6000</v>
       </c>
-      <c r="O128" s="24">
-        <v>11880</v>
-      </c>
-      <c r="P128" s="24">
-        <v>14330</v>
-      </c>
-      <c r="Q128" s="24">
-        <v>0</v>
-      </c>
-      <c r="R128" s="24">
-        <v>0</v>
-      </c>
-      <c r="S128" s="24">
-        <v>0</v>
-      </c>
-      <c r="T128" s="24">
-        <v>8000</v>
-      </c>
       <c r="U128" s="24">
         <v>0</v>
       </c>
@@ -15536,18 +15570,18 @@
         <v>0</v>
       </c>
       <c r="Y128" s="24">
-        <v>2660</v>
+        <v>0</v>
       </c>
       <c r="Z128" s="24">
         <f>SUM(J128:Y128)</f>
-        <v>79370</v>
+        <v>76770</v>
       </c>
       <c r="AA128" s="24">
         <v>25000</v>
       </c>
       <c r="AB128" s="20">
         <f>Z128-AA128</f>
-        <v>54370</v>
+        <v>51770</v>
       </c>
       <c r="AC128" s="24" t="str">
         <f>IF(AND($T128=6000, ($T128+$W128-$AB128)&gt;=6000),T128,"")</f>
@@ -15567,13 +15601,13 @@
     </row>
     <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" s="22" t="s">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D129" s="23">
         <v>0.25</v>
@@ -15582,16 +15616,16 @@
         <v>0</v>
       </c>
       <c r="F129" s="24">
-        <v>26000</v>
+        <v>40000</v>
       </c>
       <c r="G129" s="24">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H129" s="24">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I129" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J129" s="24">
         <f>(1-$D129)*E129</f>
@@ -15599,25 +15633,25 @@
       </c>
       <c r="K129" s="24">
         <f>(1-$D129)*F129</f>
-        <v>19500</v>
+        <v>30000</v>
       </c>
       <c r="L129" s="24">
         <f>G129</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M129" s="24">
         <f>(1-$D129)*H129</f>
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="N129" s="24">
         <f>(1-$D129)*I129</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="O129" s="24">
-        <v>12480</v>
+        <v>11880</v>
       </c>
       <c r="P129" s="24">
-        <v>7550</v>
+        <v>14330</v>
       </c>
       <c r="Q129" s="24">
         <v>0</v>
@@ -15629,7 +15663,7 @@
         <v>0</v>
       </c>
       <c r="T129" s="24">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="U129" s="24">
         <v>0</v>
@@ -15644,18 +15678,18 @@
         <v>0</v>
       </c>
       <c r="Y129" s="24">
-        <v>1250</v>
+        <v>2660</v>
       </c>
       <c r="Z129" s="24">
         <f>SUM(J129:Y129)</f>
-        <v>51530</v>
+        <v>79370</v>
       </c>
       <c r="AA129" s="24">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="AB129" s="20">
         <f>Z129-AA129</f>
-        <v>41530</v>
+        <v>54370</v>
       </c>
       <c r="AC129" s="24" t="str">
         <f>IF(AND($T129=6000, ($T129+$W129-$AB129)&gt;=6000),T129,"")</f>
@@ -15678,10 +15712,10 @@
         <v>184</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D130" s="23">
         <v>0.25</v>
@@ -15690,16 +15724,16 @@
         <v>0</v>
       </c>
       <c r="F130" s="24">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="G130" s="24">
         <v>4000</v>
       </c>
       <c r="H130" s="24">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="I130" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J130" s="24">
         <f>(1-$D130)*E130</f>
@@ -15707,7 +15741,7 @@
       </c>
       <c r="K130" s="24">
         <f>(1-$D130)*F130</f>
-        <v>21000</v>
+        <v>19500</v>
       </c>
       <c r="L130" s="24">
         <f>G130</f>
@@ -15715,17 +15749,17 @@
       </c>
       <c r="M130" s="24">
         <f>(1-$D130)*H130</f>
-        <v>1875</v>
+        <v>750</v>
       </c>
       <c r="N130" s="24">
         <f>(1-$D130)*I130</f>
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="O130" s="24">
-        <v>25970</v>
+        <v>12480</v>
       </c>
       <c r="P130" s="24">
-        <v>11330</v>
+        <v>7550</v>
       </c>
       <c r="Q130" s="24">
         <v>0</v>
@@ -15752,18 +15786,18 @@
         <v>0</v>
       </c>
       <c r="Y130" s="24">
-        <v>9500</v>
+        <v>1250</v>
       </c>
       <c r="Z130" s="24">
         <f>SUM(J130:Y130)</f>
-        <v>83425</v>
+        <v>51530</v>
       </c>
       <c r="AA130" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AB130" s="20">
         <f>Z130-AA130</f>
-        <v>83425</v>
+        <v>41530</v>
       </c>
       <c r="AC130" s="24" t="str">
         <f>IF(AND($T130=6000, ($T130+$W130-$AB130)&gt;=6000),T130,"")</f>
@@ -15786,10 +15820,10 @@
         <v>184</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="D131" s="23">
         <v>0.25</v>
@@ -15804,7 +15838,7 @@
         <v>4000</v>
       </c>
       <c r="H131" s="24">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I131" s="24">
         <v>5000</v>
@@ -15823,17 +15857,17 @@
       </c>
       <c r="M131" s="24">
         <f>(1-$D131)*H131</f>
-        <v>0</v>
+        <v>1875</v>
       </c>
       <c r="N131" s="24">
         <f>(1-$D131)*I131</f>
         <v>3750</v>
       </c>
       <c r="O131" s="24">
-        <v>27330</v>
+        <v>25970</v>
       </c>
       <c r="P131" s="24">
-        <v>13230</v>
+        <v>11330</v>
       </c>
       <c r="Q131" s="24">
         <v>0</v>
@@ -15860,18 +15894,18 @@
         <v>0</v>
       </c>
       <c r="Y131" s="24">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="Z131" s="24">
         <f>SUM(J131:Y131)</f>
-        <v>75310</v>
+        <v>83425</v>
       </c>
       <c r="AA131" s="24">
         <v>0</v>
       </c>
       <c r="AB131" s="20">
         <f>Z131-AA131</f>
-        <v>75310</v>
+        <v>83425</v>
       </c>
       <c r="AC131" s="24" t="str">
         <f>IF(AND($T131=6000, ($T131+$W131-$AB131)&gt;=6000),T131,"")</f>
@@ -15891,31 +15925,31 @@
     </row>
     <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" s="22" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D132" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E132" s="24">
         <v>0</v>
       </c>
       <c r="F132" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G132" s="24">
         <v>4000</v>
       </c>
       <c r="H132" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I132" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J132" s="24">
         <f>(1-$D132)*E132</f>
@@ -15923,7 +15957,7 @@
       </c>
       <c r="K132" s="24">
         <f>(1-$D132)*F132</f>
-        <v>26000</v>
+        <v>21000</v>
       </c>
       <c r="L132" s="24">
         <f>G132</f>
@@ -15931,17 +15965,17 @@
       </c>
       <c r="M132" s="24">
         <f>(1-$D132)*H132</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N132" s="24">
         <f>(1-$D132)*I132</f>
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="O132" s="24">
-        <v>6840</v>
+        <v>27330</v>
       </c>
       <c r="P132" s="24">
-        <v>5300</v>
+        <v>13230</v>
       </c>
       <c r="Q132" s="24">
         <v>0</v>
@@ -15953,7 +15987,7 @@
         <v>0</v>
       </c>
       <c r="T132" s="24">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="U132" s="24">
         <v>0</v>
@@ -15968,18 +16002,18 @@
         <v>0</v>
       </c>
       <c r="Y132" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z132" s="24">
         <f>SUM(J132:Y132)</f>
-        <v>44140</v>
+        <v>75310</v>
       </c>
       <c r="AA132" s="24">
-        <v>44140</v>
+        <v>0</v>
       </c>
       <c r="AB132" s="20">
         <f>Z132-AA132</f>
-        <v>0</v>
+        <v>75310</v>
       </c>
       <c r="AC132" s="24" t="str">
         <f>IF(AND($T132=6000, ($T132+$W132-$AB132)&gt;=6000),T132,"")</f>
@@ -15999,31 +16033,31 @@
     </row>
     <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" s="22" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D133" s="23">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E133" s="24">
         <v>0</v>
       </c>
       <c r="F133" s="24">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="G133" s="24">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H133" s="24">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I133" s="24">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="J133" s="24">
         <f>(1-$D133)*E133</f>
@@ -16031,25 +16065,25 @@
       </c>
       <c r="K133" s="24">
         <f>(1-$D133)*F133</f>
-        <v>23100</v>
+        <v>26000</v>
       </c>
       <c r="L133" s="24">
         <f>G133</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="M133" s="24">
         <f>(1-$D133)*H133</f>
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="N133" s="24">
         <f>(1-$D133)*I133</f>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="O133" s="24">
-        <v>22400</v>
+        <v>6840</v>
       </c>
       <c r="P133" s="24">
-        <v>14330</v>
+        <v>5300</v>
       </c>
       <c r="Q133" s="24">
         <v>0</v>
@@ -16061,7 +16095,7 @@
         <v>0</v>
       </c>
       <c r="T133" s="24">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U133" s="24">
         <v>0</v>
@@ -16076,18 +16110,18 @@
         <v>0</v>
       </c>
       <c r="Y133" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z133" s="24">
         <f>SUM(J133:Y133)</f>
-        <v>78430</v>
+        <v>44140</v>
       </c>
       <c r="AA133" s="24">
-        <v>0</v>
+        <v>44140</v>
       </c>
       <c r="AB133" s="20">
         <f>Z133-AA133</f>
-        <v>78430</v>
+        <v>0</v>
       </c>
       <c r="AC133" s="24" t="str">
         <f>IF(AND($T133=6000, ($T133+$W133-$AB133)&gt;=6000),T133,"")</f>
@@ -16110,19 +16144,19 @@
         <v>130</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D134" s="23">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E134" s="24">
         <v>0</v>
       </c>
       <c r="F134" s="24">
-        <v>40000</v>
+        <v>33000</v>
       </c>
       <c r="G134" s="24">
         <v>5000</v>
@@ -16131,7 +16165,7 @@
         <v>2000</v>
       </c>
       <c r="I134" s="24">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="J134" s="24">
         <f>(1-$D134)*E134</f>
@@ -16139,7 +16173,7 @@
       </c>
       <c r="K134" s="24">
         <f>(1-$D134)*F134</f>
-        <v>30000</v>
+        <v>23100</v>
       </c>
       <c r="L134" s="24">
         <f>G134</f>
@@ -16147,14 +16181,14 @@
       </c>
       <c r="M134" s="24">
         <f>(1-$D134)*H134</f>
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="N134" s="24">
         <f>(1-$D134)*I134</f>
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="O134" s="24">
-        <v>11880</v>
+        <v>22400</v>
       </c>
       <c r="P134" s="24">
         <v>14330</v>
@@ -16169,7 +16203,7 @@
         <v>0</v>
       </c>
       <c r="T134" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="U134" s="24">
         <v>0</v>
@@ -16188,14 +16222,14 @@
       </c>
       <c r="Z134" s="24">
         <f>SUM(J134:Y134)</f>
-        <v>68710</v>
+        <v>78430</v>
       </c>
       <c r="AA134" s="24">
         <v>0</v>
       </c>
       <c r="AB134" s="20">
         <f>Z134-AA134</f>
-        <v>68710</v>
+        <v>78430</v>
       </c>
       <c r="AC134" s="24" t="str">
         <f>IF(AND($T134=6000, ($T134+$W134-$AB134)&gt;=6000),T134,"")</f>
@@ -16215,31 +16249,31 @@
     </row>
     <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="D135" s="23">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E135" s="24">
         <v>0</v>
       </c>
       <c r="F135" s="24">
-        <v>28000</v>
+        <v>40000</v>
       </c>
       <c r="G135" s="24">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H135" s="24">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I135" s="24">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="J135" s="24">
         <f>(1-$D135)*E135</f>
@@ -16247,25 +16281,25 @@
       </c>
       <c r="K135" s="24">
         <f>(1-$D135)*F135</f>
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="L135" s="24">
         <f>G135</f>
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="M135" s="24">
         <f>(1-$D135)*H135</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N135" s="24">
         <f>(1-$D135)*I135</f>
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="O135" s="24">
-        <v>26150</v>
+        <v>11880</v>
       </c>
       <c r="P135" s="24">
-        <v>11330</v>
+        <v>14330</v>
       </c>
       <c r="Q135" s="24">
         <v>0</v>
@@ -16292,18 +16326,18 @@
         <v>0</v>
       </c>
       <c r="Y135" s="24">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="24">
         <f>SUM(J135:Y135)</f>
-        <v>78500</v>
+        <v>68710</v>
       </c>
       <c r="AA135" s="24">
         <v>0</v>
       </c>
       <c r="AB135" s="20">
         <f>Z135-AA135</f>
-        <v>78500</v>
+        <v>68710</v>
       </c>
       <c r="AC135" s="24" t="str">
         <f>IF(AND($T135=6000, ($T135+$W135-$AB135)&gt;=6000),T135,"")</f>
@@ -16323,31 +16357,31 @@
     </row>
     <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" s="22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D136" s="23">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E136" s="24">
         <v>0</v>
       </c>
       <c r="F136" s="24">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="G136" s="24">
         <v>4000</v>
       </c>
       <c r="H136" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I136" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J136" s="24">
         <f>(1-$D136)*E136</f>
@@ -16355,7 +16389,7 @@
       </c>
       <c r="K136" s="24">
         <f>(1-$D136)*F136</f>
-        <v>19500</v>
+        <v>28000</v>
       </c>
       <c r="L136" s="24">
         <f>G136</f>
@@ -16363,17 +16397,17 @@
       </c>
       <c r="M136" s="24">
         <f>(1-$D136)*H136</f>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="N136" s="24">
         <f>(1-$D136)*I136</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O136" s="24">
-        <v>6840</v>
+        <v>26150</v>
       </c>
       <c r="P136" s="24">
-        <v>5300</v>
+        <v>11330</v>
       </c>
       <c r="Q136" s="24">
         <v>0</v>
@@ -16400,18 +16434,18 @@
         <v>0</v>
       </c>
       <c r="Y136" s="24">
-        <v>0</v>
+        <v>4020</v>
       </c>
       <c r="Z136" s="24">
         <f>SUM(J136:Y136)</f>
-        <v>36390</v>
+        <v>78500</v>
       </c>
       <c r="AA136" s="24">
-        <v>7070</v>
+        <v>50000</v>
       </c>
       <c r="AB136" s="20">
         <f>Z136-AA136</f>
-        <v>29320</v>
+        <v>28500</v>
       </c>
       <c r="AC136" s="24" t="str">
         <f>IF(AND($T136=6000, ($T136+$W136-$AB136)&gt;=6000),T136,"")</f>
@@ -16434,13 +16468,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D137" s="23">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E137" s="24">
         <v>0</v>
@@ -16463,7 +16497,7 @@
       </c>
       <c r="K137" s="24">
         <f>(1-$D137)*F137</f>
-        <v>18200</v>
+        <v>19500</v>
       </c>
       <c r="L137" s="24">
         <f>G137</f>
@@ -16471,17 +16505,17 @@
       </c>
       <c r="M137" s="24">
         <f>(1-$D137)*H137</f>
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="N137" s="24">
         <f>(1-$D137)*I137</f>
         <v>0</v>
       </c>
       <c r="O137" s="24">
-        <v>12480</v>
+        <v>6840</v>
       </c>
       <c r="P137" s="24">
-        <v>7550</v>
+        <v>5300</v>
       </c>
       <c r="Q137" s="24">
         <v>0</v>
@@ -16512,14 +16546,14 @@
       </c>
       <c r="Z137" s="24">
         <f>SUM(J137:Y137)</f>
-        <v>42930</v>
+        <v>36390</v>
       </c>
       <c r="AA137" s="24">
-        <v>42930</v>
+        <v>7070</v>
       </c>
       <c r="AB137" s="20">
         <f>Z137-AA137</f>
-        <v>0</v>
+        <v>29320</v>
       </c>
       <c r="AC137" s="24" t="str">
         <f>IF(AND($T137=6000, ($T137+$W137-$AB137)&gt;=6000),T137,"")</f>
@@ -16534,21 +16568,21 @@
         <v/>
       </c>
       <c r="AF137" s="25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A138" s="22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D138" s="23">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E138" s="24">
         <v>0</v>
@@ -16560,7 +16594,7 @@
         <v>4000</v>
       </c>
       <c r="H138" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I138" s="24">
         <v>0</v>
@@ -16571,7 +16605,7 @@
       </c>
       <c r="K138" s="24">
         <f>(1-$D138)*F138</f>
-        <v>26000</v>
+        <v>18200</v>
       </c>
       <c r="L138" s="24">
         <f>G138</f>
@@ -16579,17 +16613,17 @@
       </c>
       <c r="M138" s="24">
         <f>(1-$D138)*H138</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N138" s="24">
         <f>(1-$D138)*I138</f>
         <v>0</v>
       </c>
       <c r="O138" s="24">
-        <v>13380</v>
+        <v>12480</v>
       </c>
       <c r="P138" s="24">
-        <v>3500</v>
+        <v>7550</v>
       </c>
       <c r="Q138" s="24">
         <v>0</v>
@@ -16620,10 +16654,10 @@
       </c>
       <c r="Z138" s="24">
         <f>SUM(J138:Y138)</f>
-        <v>46880</v>
+        <v>42930</v>
       </c>
       <c r="AA138" s="24">
-        <v>46880</v>
+        <v>42930</v>
       </c>
       <c r="AB138" s="20">
         <f>Z138-AA138</f>
@@ -16642,143 +16676,219 @@
         <v/>
       </c>
       <c r="AF138" s="25" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A139" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C139" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" s="23">
+        <v>0</v>
+      </c>
+      <c r="E139" s="24">
+        <v>0</v>
+      </c>
+      <c r="F139" s="24">
+        <v>26000</v>
+      </c>
+      <c r="G139" s="24">
+        <v>4000</v>
+      </c>
+      <c r="H139" s="24">
+        <v>0</v>
+      </c>
+      <c r="I139" s="24">
+        <v>0</v>
+      </c>
+      <c r="J139" s="24">
+        <f>(1-$D139)*E139</f>
+        <v>0</v>
+      </c>
+      <c r="K139" s="24">
+        <f>(1-$D139)*F139</f>
+        <v>26000</v>
+      </c>
+      <c r="L139" s="24">
+        <f>G139</f>
+        <v>4000</v>
+      </c>
+      <c r="M139" s="24">
+        <f>(1-$D139)*H139</f>
+        <v>0</v>
+      </c>
+      <c r="N139" s="24">
+        <f>(1-$D139)*I139</f>
+        <v>0</v>
+      </c>
+      <c r="O139" s="24">
+        <v>13380</v>
+      </c>
+      <c r="P139" s="24">
+        <v>3500</v>
+      </c>
+      <c r="Q139" s="24">
+        <v>0</v>
+      </c>
+      <c r="R139" s="24">
+        <v>0</v>
+      </c>
+      <c r="S139" s="24">
+        <v>0</v>
+      </c>
+      <c r="T139" s="24">
+        <v>0</v>
+      </c>
+      <c r="U139" s="24">
+        <v>0</v>
+      </c>
+      <c r="V139" s="24">
+        <v>0</v>
+      </c>
+      <c r="W139" s="24">
+        <v>0</v>
+      </c>
+      <c r="X139" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="24">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="24">
+        <f>SUM(J139:Y139)</f>
+        <v>46880</v>
+      </c>
+      <c r="AA139" s="24">
+        <v>46880</v>
+      </c>
+      <c r="AB139" s="20">
+        <f>Z139-AA139</f>
+        <v>0</v>
+      </c>
+      <c r="AC139" s="24" t="str">
+        <f>IF(AND($T139=6000, ($T139+$W139-$AB139)&gt;=6000),T139,"")</f>
+        <v/>
+      </c>
+      <c r="AD139" s="24" t="str">
+        <f>IF(AND($T139=8000, ($T139+$W139-$AB139)&gt;=8000),T139,"")</f>
+        <v/>
+      </c>
+      <c r="AE139" s="24" t="str">
+        <f>IF(($T139+$W139-$AB139)&gt;=$T139+8000,W139,"")</f>
+        <v/>
+      </c>
+      <c r="AF139" s="25" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A139" s="26"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
-      <c r="D139" s="27"/>
-      <c r="E139" s="28"/>
-      <c r="F139" s="28"/>
-      <c r="G139" s="28"/>
-      <c r="H139" s="28"/>
-      <c r="I139" s="28"/>
-      <c r="J139" s="28">
-        <f>SUM(J2:J138)</f>
-        <v>35500</v>
-      </c>
-      <c r="K139" s="28">
-        <f>SUM(K2:K138)</f>
-        <v>3089300</v>
-      </c>
-      <c r="L139" s="28">
-        <f>SUM(L2:L138)</f>
-        <v>567000</v>
-      </c>
-      <c r="M139" s="28">
-        <f>SUM(M2:M138)</f>
-        <v>101200</v>
-      </c>
-      <c r="N139" s="28">
-        <f>SUM(N2:N138)</f>
-        <v>290750</v>
-      </c>
-      <c r="O139" s="28">
-        <f>SUM(O2:O138)</f>
-        <v>2394850</v>
-      </c>
-      <c r="P139" s="28">
-        <f>SUM(P2:P138)</f>
-        <v>1354790</v>
-      </c>
-      <c r="Q139" s="28">
-        <f>SUM(Q2:Q138)</f>
-        <v>332000</v>
-      </c>
-      <c r="R139" s="28">
-        <f>SUM(R2:R138)</f>
-        <v>136000</v>
-      </c>
-      <c r="S139" s="28">
-        <f>SUM(S2:S138)</f>
-        <v>116000</v>
-      </c>
-      <c r="T139" s="28">
-        <f>SUM(T2:T138)</f>
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A140" s="26"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
+      <c r="D140" s="27"/>
+      <c r="E140" s="28"/>
+      <c r="F140" s="28"/>
+      <c r="G140" s="28"/>
+      <c r="H140" s="28"/>
+      <c r="I140" s="28"/>
+      <c r="J140" s="28">
+        <f>SUM(J2:J139)</f>
+        <v>38500</v>
+      </c>
+      <c r="K140" s="28">
+        <f>SUM(K2:K139)</f>
+        <v>3122300</v>
+      </c>
+      <c r="L140" s="28">
+        <f>SUM(L2:L139)</f>
+        <v>572000</v>
+      </c>
+      <c r="M140" s="28">
+        <f>SUM(M2:M139)</f>
+        <v>103200</v>
+      </c>
+      <c r="N140" s="28">
+        <f>SUM(N2:N139)</f>
+        <v>296750</v>
+      </c>
+      <c r="O140" s="28">
+        <f>SUM(O2:O139)</f>
+        <v>2414170</v>
+      </c>
+      <c r="P140" s="28">
+        <f>SUM(P2:P139)</f>
+        <v>1382380</v>
+      </c>
+      <c r="Q140" s="28">
+        <f>SUM(Q2:Q139)</f>
+        <v>344000</v>
+      </c>
+      <c r="R140" s="28">
+        <f>SUM(R2:R139)</f>
+        <v>144000</v>
+      </c>
+      <c r="S140" s="28">
+        <f>SUM(S2:S139)</f>
+        <v>124000</v>
+      </c>
+      <c r="T140" s="28">
+        <f>SUM(T2:T139)</f>
         <v>264000</v>
       </c>
-      <c r="U139" s="28">
-        <f>SUM(U2:U138)</f>
-        <v>0</v>
-      </c>
-      <c r="V139" s="28">
-        <f>SUM(V2:V138)</f>
-        <v>0</v>
-      </c>
-      <c r="W139" s="28">
-        <f>SUM(W2:W138)</f>
-        <v>0</v>
-      </c>
-      <c r="X139" s="28">
-        <f>SUM(X2:X138)</f>
-        <v>0</v>
-      </c>
-      <c r="Y139" s="28">
-        <f>SUM(Y2:Y138)</f>
+      <c r="U140" s="28">
+        <f>SUM(U2:U139)</f>
+        <v>0</v>
+      </c>
+      <c r="V140" s="28">
+        <f>SUM(V2:V139)</f>
+        <v>0</v>
+      </c>
+      <c r="W140" s="28">
+        <f>SUM(W2:W139)</f>
+        <v>0</v>
+      </c>
+      <c r="X140" s="28">
+        <f>SUM(X2:X139)</f>
+        <v>0</v>
+      </c>
+      <c r="Y140" s="28">
+        <f>SUM(Y2:Y139)</f>
         <v>188670</v>
       </c>
-      <c r="Z139" s="28">
-        <f>SUM(Z2:Z138)</f>
-        <v>8870060</v>
-      </c>
-      <c r="AA139" s="28">
-        <f>SUM(AA2:AA138)</f>
-        <v>3461855</v>
-      </c>
-      <c r="AB139" s="28">
-        <f>SUM(AB2:AB138)</f>
-        <v>5408205</v>
-      </c>
-      <c r="AC139" s="28">
-        <f>SUM(AC2:AC138)</f>
+      <c r="Z140" s="28">
+        <f>SUM(Z2:Z139)</f>
+        <v>8993970</v>
+      </c>
+      <c r="AA140" s="28">
+        <f>SUM(AA2:AA139)</f>
+        <v>3791855</v>
+      </c>
+      <c r="AB140" s="28">
+        <f>SUM(AB2:AB139)</f>
+        <v>5202115</v>
+      </c>
+      <c r="AC140" s="28">
+        <f>SUM(AC2:AC139)</f>
         <v>42000</v>
       </c>
-      <c r="AD139" s="28">
-        <f>SUM(AD2:AD138)</f>
-        <v>0</v>
-      </c>
-      <c r="AE139" s="28">
-        <f>SUM(AE2:AE138)</f>
-        <v>0</v>
-      </c>
-      <c r="AF139" s="28">
-        <f>SUM(AF2:AF138)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="29"/>
-      <c r="D140" s="30"/>
-      <c r="E140" s="31"/>
-      <c r="F140" s="31"/>
-      <c r="G140" s="31"/>
-      <c r="H140" s="31"/>
-      <c r="I140" s="31"/>
-      <c r="J140" s="31"/>
-      <c r="K140" s="31"/>
-      <c r="L140" s="31"/>
-      <c r="M140" s="31"/>
-      <c r="N140" s="31"/>
-      <c r="O140" s="31"/>
-      <c r="P140" s="31"/>
-      <c r="Q140" s="31"/>
-      <c r="R140" s="31"/>
-      <c r="S140" s="31"/>
-      <c r="T140" s="31"/>
-      <c r="U140" s="31"/>
-      <c r="V140" s="31"/>
-      <c r="W140" s="31"/>
-      <c r="X140" s="31"/>
-      <c r="Y140" s="31"/>
-      <c r="Z140" s="31"/>
-      <c r="AA140" s="31"/>
-      <c r="AB140" s="32"/>
-      <c r="AC140" s="33"/>
-      <c r="AD140" s="33"/>
+      <c r="AD140" s="28">
+        <f>SUM(AD2:AD139)</f>
+        <v>0</v>
+      </c>
+      <c r="AE140" s="28">
+        <f>SUM(AE2:AE139)</f>
+        <v>0</v>
+      </c>
+      <c r="AF140" s="28">
+        <f>SUM(AF2:AF139)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A141" s="29"/>
@@ -20040,7 +20150,7 @@
       <c r="Y242" s="31"/>
       <c r="Z242" s="31"/>
       <c r="AA242" s="31"/>
-      <c r="AB242" s="34"/>
+      <c r="AB242" s="32"/>
       <c r="AC242" s="33"/>
       <c r="AD242" s="33"/>
     </row>
@@ -20055,23 +20165,23 @@
       <c r="H243" s="31"/>
       <c r="I243" s="31"/>
       <c r="J243" s="31"/>
-      <c r="K243" s="29"/>
-      <c r="L243" s="29"/>
-      <c r="M243" s="29"/>
-      <c r="N243" s="29"/>
-      <c r="O243" s="29"/>
-      <c r="P243" s="29"/>
-      <c r="Q243" s="29"/>
-      <c r="R243" s="29"/>
-      <c r="S243" s="29"/>
-      <c r="T243" s="29"/>
-      <c r="U243" s="29"/>
-      <c r="V243" s="29"/>
-      <c r="W243" s="29"/>
-      <c r="X243" s="29"/>
-      <c r="Y243" s="29"/>
-      <c r="Z243" s="29"/>
-      <c r="AA243" s="29"/>
+      <c r="K243" s="31"/>
+      <c r="L243" s="31"/>
+      <c r="M243" s="31"/>
+      <c r="N243" s="31"/>
+      <c r="O243" s="31"/>
+      <c r="P243" s="31"/>
+      <c r="Q243" s="31"/>
+      <c r="R243" s="31"/>
+      <c r="S243" s="31"/>
+      <c r="T243" s="31"/>
+      <c r="U243" s="31"/>
+      <c r="V243" s="31"/>
+      <c r="W243" s="31"/>
+      <c r="X243" s="31"/>
+      <c r="Y243" s="31"/>
+      <c r="Z243" s="31"/>
+      <c r="AA243" s="31"/>
       <c r="AB243" s="34"/>
       <c r="AC243" s="33"/>
       <c r="AD243" s="33"/>
@@ -21352,10 +21462,38 @@
       <c r="Y283" s="29"/>
       <c r="Z283" s="29"/>
       <c r="AA283" s="29"/>
+      <c r="AB283" s="34"/>
       <c r="AC283" s="33"/>
       <c r="AD283" s="33"/>
     </row>
     <row r="284" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A284" s="29"/>
+      <c r="B284" s="29"/>
+      <c r="C284" s="29"/>
+      <c r="D284" s="30"/>
+      <c r="E284" s="31"/>
+      <c r="F284" s="31"/>
+      <c r="G284" s="31"/>
+      <c r="H284" s="31"/>
+      <c r="I284" s="31"/>
+      <c r="J284" s="31"/>
+      <c r="K284" s="29"/>
+      <c r="L284" s="29"/>
+      <c r="M284" s="29"/>
+      <c r="N284" s="29"/>
+      <c r="O284" s="29"/>
+      <c r="P284" s="29"/>
+      <c r="Q284" s="29"/>
+      <c r="R284" s="29"/>
+      <c r="S284" s="29"/>
+      <c r="T284" s="29"/>
+      <c r="U284" s="29"/>
+      <c r="V284" s="29"/>
+      <c r="W284" s="29"/>
+      <c r="X284" s="29"/>
+      <c r="Y284" s="29"/>
+      <c r="Z284" s="29"/>
+      <c r="AA284" s="29"/>
       <c r="AC284" s="33"/>
       <c r="AD284" s="33"/>
     </row>
@@ -24211,19 +24349,23 @@
       <c r="AC997" s="33"/>
       <c r="AD997" s="33"/>
     </row>
+    <row r="998" spans="29:30" x14ac:dyDescent="0.25">
+      <c r="AC998" s="33"/>
+      <c r="AD998" s="33"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AF139">
-    <sortCondition ref="A2:A139"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AF140">
+    <sortCondition ref="A2:A140"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AC1:AF10 AB1:AB138 E139:AF139 AB140:AB996">
+  <conditionalFormatting sqref="E140:AF140 AB141:AB997 AB9:AB139 AC9:AF11 AB1:AF8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="Y101:Y102 Y105:Y117 D124 O56:X138 D125:I138 Y124:Y138 D11:H31 Y56:Y98 AA11:AA138 I11:I124 O11:Y55 D32:D108 E32:H124" xr:uid="{8FCCCF8D-A982-4ECC-8B53-E3BEBA112740}">
-      <formula1>AND(ISNUMBER(D11),(NOT(OR(NOT(ISERROR(DATEVALUE(D11))), AND(ISNUMBER(D11), LEFT(CELL("format", D11))="D")))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="Y102:Y103 Y106:Y118 D125 O57:X139 D126:I139 Y125:Y139 D12:H32 Y57:Y99 AA12:AA139 I12:I125 O12:Y56 D33:D109 E33:H125" xr:uid="{8FCCCF8D-A982-4ECC-8B53-E3BEBA112740}">
+      <formula1>AND(ISNUMBER(D12),(NOT(OR(NOT(ISERROR(DATEVALUE(D12))), AND(ISNUMBER(D12), LEFT(CELL("format", D12))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -24270,7 +24412,7 @@
       </c>
       <c r="F1" s="36">
         <f>SUMIF(E1:E1000, "&lt;&gt;", D1:D1000)</f>
-        <v>3461855</v>
+        <v>3791855</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -25886,21 +26028,21 @@
     </row>
     <row r="52" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
-        <v>46280</v>
+        <v>46292</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>339</v>
+        <v>410</v>
       </c>
       <c r="D52" s="9">
-        <v>65160</v>
+        <v>50000</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F52" s="11"/>
+        <v>414</v>
+      </c>
+      <c r="F52" s="7"/>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
@@ -25931,10 +26073,10 @@
         <v>339</v>
       </c>
       <c r="D53" s="9">
-        <v>35890</v>
+        <v>65160</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F53" s="11"/>
       <c r="G53" s="11"/>
@@ -25964,15 +26106,15 @@
         <v>250</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D54" s="9">
-        <v>50000</v>
+        <v>35890</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="F54" s="7"/>
+        <v>341</v>
+      </c>
+      <c r="F54" s="11"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -25994,19 +26136,19 @@
     </row>
     <row r="55" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="D55" s="9">
-        <v>116000</v>
+        <v>50000</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -26030,19 +26172,19 @@
     </row>
     <row r="56" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
-        <v>46287</v>
+        <v>46279</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>393</v>
+        <v>308</v>
       </c>
       <c r="D56" s="9">
-        <v>22000</v>
+        <v>116000</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
@@ -26066,19 +26208,19 @@
     </row>
     <row r="57" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="D57" s="9">
-        <v>50000</v>
+        <v>22000</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
@@ -26102,7 +26244,7 @@
     </row>
     <row r="58" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>250</v>
@@ -26138,19 +26280,19 @@
     </row>
     <row r="59" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D59" s="9">
         <v>50000</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
@@ -26174,19 +26316,19 @@
     </row>
     <row r="60" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
-        <v>46277</v>
+        <v>46286</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>292</v>
+        <v>372</v>
       </c>
       <c r="D60" s="9">
-        <v>95000</v>
+        <v>90000</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>293</v>
+        <v>408</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -26210,19 +26352,19 @@
     </row>
     <row r="61" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>322</v>
+        <v>375</v>
       </c>
       <c r="D61" s="9">
-        <v>27900</v>
+        <v>50000</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -26246,19 +26388,19 @@
     </row>
     <row r="62" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D62" s="9">
-        <v>24700</v>
+        <v>95000</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -26282,19 +26424,19 @@
     </row>
     <row r="63" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>286</v>
+        <v>412</v>
       </c>
       <c r="D63" s="9">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -26318,19 +26460,19 @@
     </row>
     <row r="64" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>397</v>
+        <v>322</v>
       </c>
       <c r="D64" s="9">
-        <v>124270</v>
+        <v>27900</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
@@ -26353,20 +26495,20 @@
       <c r="X64" s="7"/>
     </row>
     <row r="65" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
+      <c r="A65" s="8">
         <v>46275</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C65" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="D65" s="12">
-        <v>33140</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>284</v>
+      <c r="C65" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D65" s="9">
+        <v>24700</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -26390,19 +26532,19 @@
     </row>
     <row r="66" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>374</v>
+        <v>286</v>
       </c>
       <c r="D66" s="9">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>401</v>
+        <v>287</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
@@ -26426,19 +26568,19 @@
     </row>
     <row r="67" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>404</v>
+        <v>295</v>
       </c>
       <c r="D67" s="9">
-        <v>54240</v>
+        <v>30000</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
@@ -26462,19 +26604,19 @@
     </row>
     <row r="68" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
-        <v>46270</v>
+        <v>46288</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>272</v>
+        <v>397</v>
       </c>
       <c r="D68" s="9">
-        <v>50000</v>
+        <v>124270</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>273</v>
+        <v>398</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -26497,20 +26639,20 @@
       <c r="X68" s="7"/>
     </row>
     <row r="69" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B69" s="7" t="s">
+      <c r="A69" s="10">
+        <v>46275</v>
+      </c>
+      <c r="B69" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="D69" s="9">
-        <v>100000</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>329</v>
+      <c r="C69" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" s="12">
+        <v>33140</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>284</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
@@ -26534,19 +26676,19 @@
     </row>
     <row r="70" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D70" s="9">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
@@ -26570,19 +26712,19 @@
     </row>
     <row r="71" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <v>46277</v>
+        <v>46292</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>294</v>
+        <v>409</v>
       </c>
       <c r="D71" s="9">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>297</v>
+        <v>413</v>
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
@@ -26606,19 +26748,19 @@
     </row>
     <row r="72" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="D72" s="9">
-        <v>44140</v>
+        <v>54240</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
@@ -26642,19 +26784,19 @@
     </row>
     <row r="73" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D73" s="9">
         <v>50000</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
@@ -26678,19 +26820,19 @@
     </row>
     <row r="74" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="D74" s="9">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -26714,19 +26856,19 @@
     </row>
     <row r="75" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="D75" s="9">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
@@ -26750,19 +26892,19 @@
     </row>
     <row r="76" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
-        <v>46290</v>
+        <v>46277</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="D76" s="9">
-        <v>16880</v>
+        <v>10000</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
@@ -26786,18 +26928,20 @@
     </row>
     <row r="77" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D77" s="9">
-        <v>36050</v>
-      </c>
-      <c r="E77" s="7"/>
+        <v>44140</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>348</v>
+      </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
@@ -26820,18 +26964,20 @@
     </row>
     <row r="78" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>310</v>
+        <v>411</v>
       </c>
       <c r="D78" s="9">
-        <v>100000</v>
-      </c>
-      <c r="E78" s="7"/>
+        <v>50000</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>417</v>
+      </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -26854,18 +27000,20 @@
     </row>
     <row r="79" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="D79" s="9">
-        <v>20180</v>
-      </c>
-      <c r="E79" s="7"/>
+        <v>50000</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
@@ -26888,18 +27036,20 @@
     </row>
     <row r="80" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="D80" s="12">
-        <v>10000</v>
-      </c>
-      <c r="E80" s="11"/>
+      <c r="C80" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D80" s="9">
+        <v>20000</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -26922,18 +27072,20 @@
     </row>
     <row r="81" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="D81" s="9">
         <v>10000</v>
       </c>
-      <c r="E81" s="7"/>
+      <c r="E81" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
@@ -26956,18 +27108,20 @@
     </row>
     <row r="82" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
-        <v>46282</v>
+        <v>46290</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="D82" s="9">
-        <v>40000</v>
-      </c>
-      <c r="E82" s="7"/>
+        <v>16880</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
@@ -26990,16 +27144,16 @@
     </row>
     <row r="83" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>372</v>
+        <v>309</v>
       </c>
       <c r="D83" s="9">
-        <v>90000</v>
+        <v>36050</v>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7"/>
@@ -27024,16 +27178,16 @@
     </row>
     <row r="84" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
-        <v>46288</v>
+        <v>46279</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>395</v>
+        <v>310</v>
       </c>
       <c r="D84" s="9">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
@@ -27057,9 +27211,18 @@
       <c r="X84" s="7"/>
     </row>
     <row r="85" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="9"/>
+      <c r="A85" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D85" s="9">
+        <v>20180</v>
+      </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
@@ -27082,10 +27245,19 @@
       <c r="X85" s="7"/>
     </row>
     <row r="86" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="7"/>
+      <c r="A86" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D86" s="12">
+        <v>10000</v>
+      </c>
+      <c r="E86" s="11"/>
       <c r="F86" s="7"/>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -27107,9 +27279,18 @@
       <c r="X86" s="7"/>
     </row>
     <row r="87" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="9"/>
+      <c r="A87" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D87" s="9">
+        <v>10000</v>
+      </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -27132,9 +27313,18 @@
       <c r="X87" s="7"/>
     </row>
     <row r="88" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="9"/>
+      <c r="A88" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D88" s="9">
+        <v>40000</v>
+      </c>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -27157,9 +27347,18 @@
       <c r="X88" s="7"/>
     </row>
     <row r="89" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="9"/>
+      <c r="A89" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D89" s="9">
+        <v>40000</v>
+      </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -39681,8 +39880,8 @@
       <c r="X589" s="7"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F84">
-    <sortCondition ref="E2:E84"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F89">
+    <sortCondition ref="E2:E89"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -39727,7 +39926,7 @@
         <v>227</v>
       </c>
       <c r="B2" s="15">
-        <f>'1ST TERM ACCOUNT'!AC139</f>
+        <f>'1ST TERM ACCOUNT'!AC140</f>
         <v>42000</v>
       </c>
       <c r="C2" s="15">
@@ -39746,8 +39945,8 @@
         <v>229</v>
       </c>
       <c r="B3" s="15">
-        <f>SUMIF('1ST TERM ACCOUNT'!T11:T138,6000)</f>
-        <v>198000</v>
+        <f>SUMIF('1ST TERM ACCOUNT'!T12:T139,6000)</f>
+        <v>192000</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
@@ -39763,7 +39962,7 @@
       </c>
       <c r="B4" s="15">
         <f>B3-B2</f>
-        <v>156000</v>
+        <v>150000</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -39812,7 +40011,7 @@
         <v>227</v>
       </c>
       <c r="B8" s="15">
-        <f>'1ST TERM ACCOUNT'!AD139</f>
+        <f>'1ST TERM ACCOUNT'!AD140</f>
         <v>0</v>
       </c>
       <c r="C8" s="15">
@@ -39831,7 +40030,7 @@
         <v>229</v>
       </c>
       <c r="B9" s="15">
-        <f>SUMIF('1ST TERM ACCOUNT'!T11:T138,8000)</f>
+        <f>SUMIF('1ST TERM ACCOUNT'!T12:T139,8000)</f>
         <v>48000</v>
       </c>
       <c r="C9" s="15"/>
@@ -39896,7 +40095,7 @@
         <v>227</v>
       </c>
       <c r="B14" s="15">
-        <f>'1ST TERM ACCOUNT'!AE139</f>
+        <f>'1ST TERM ACCOUNT'!AE140</f>
         <v>0</v>
       </c>
       <c r="C14" s="15">
@@ -39915,7 +40114,7 @@
         <v>229</v>
       </c>
       <c r="B15" s="15">
-        <f>SUM('1ST TERM ACCOUNT'!W11:W138)</f>
+        <f>SUM('1ST TERM ACCOUNT'!W12:W139)</f>
         <v>0</v>
       </c>
       <c r="C15" s="15"/>

--- a/source/2026 - 2027 FEE.xlsx
+++ b/source/2026 - 2027 FEE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A628DB9E-7ACB-4A21-936E-68C36AF4654A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF3EC81-5496-4243-92AE-9084A62E2CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="432">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -1221,9 +1221,6 @@
     <t>NIP:MOSES NOAH OLUWASEYI</t>
   </si>
   <si>
-    <t>NIP:ODUNAYO IRETIOLUWA AKINDUN-ALADESAYE AFOLAHANMI VINCENT SCHOOL FE</t>
-  </si>
-  <si>
     <t>NIP:OLADOSU TOSIN ELIZABETH</t>
   </si>
   <si>
@@ -1321,6 +1318,21 @@
   </si>
   <si>
     <t>OLATUNJI FAMILY</t>
+  </si>
+  <si>
+    <t>NIP:ANUOLUWAPO DEBORAH OLADELE-oluwashola Elizabeth and Esther</t>
+  </si>
+  <si>
+    <t>PATIENCE DANIEL</t>
+  </si>
+  <si>
+    <t>OLUWASHOLA FAMILY</t>
+  </si>
+  <si>
+    <t>ISSAH IMOLE</t>
+  </si>
+  <si>
+    <t>NIP:ODUNAYO IRETIOLUWA AKINDUN</t>
   </si>
 </sst>
 </file>
@@ -4192,23 +4204,23 @@
         <v>76770</v>
       </c>
       <c r="AA22" s="24">
-        <v>37535</v>
+        <v>85535</v>
       </c>
       <c r="AB22" s="20">
         <f t="shared" si="6"/>
-        <v>39235</v>
-      </c>
-      <c r="AC22" s="24" t="str">
+        <v>-8765</v>
+      </c>
+      <c r="AC22" s="24">
         <f t="shared" si="7"/>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="AD22" s="24" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AE22" s="24" t="str">
+      <c r="AE22" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF22" s="25" t="s">
         <v>325</v>
@@ -9679,11 +9691,11 @@
         <v>79830</v>
       </c>
       <c r="AA73" s="24">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AB73" s="20">
         <f t="shared" si="29"/>
-        <v>79830</v>
+        <v>39830</v>
       </c>
       <c r="AC73" s="24" t="str">
         <f t="shared" si="20"/>
@@ -11643,10 +11655,10 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="B92" s="22" t="s">
         <v>406</v>
-      </c>
-      <c r="B92" s="22" t="s">
-        <v>407</v>
       </c>
       <c r="C92" s="22" t="s">
         <v>332</v>
@@ -14097,11 +14109,11 @@
         <v>45930</v>
       </c>
       <c r="AA114" s="24">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AB114" s="20">
         <f t="shared" si="39"/>
-        <v>45930</v>
+        <v>25930</v>
       </c>
       <c r="AC114" s="24" t="str">
         <f t="shared" si="30"/>
@@ -14205,11 +14217,11 @@
         <v>57980</v>
       </c>
       <c r="AA115" s="24">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="AB115" s="20">
         <f t="shared" si="39"/>
-        <v>57980</v>
+        <v>32980</v>
       </c>
       <c r="AC115" s="24" t="str">
         <f t="shared" si="30"/>
@@ -15819,14 +15831,14 @@
         <v>1250</v>
       </c>
       <c r="Z130" s="24">
-        <f t="shared" ref="Z130:Z161" si="48">SUM(J130:Y130)</f>
+        <f t="shared" ref="Z130:Z139" si="48">SUM(J130:Y130)</f>
         <v>51530</v>
       </c>
       <c r="AA130" s="24">
         <v>10000</v>
       </c>
       <c r="AB130" s="20">
-        <f t="shared" ref="AB130:AB161" si="49">Z130-AA130</f>
+        <f t="shared" ref="AB130:AB139" si="49">Z130-AA130</f>
         <v>41530</v>
       </c>
       <c r="AC130" s="24" t="str">
@@ -16897,15 +16909,15 @@
       </c>
       <c r="AA140" s="28">
         <f t="shared" si="50"/>
-        <v>4272905</v>
+        <v>4405905</v>
       </c>
       <c r="AB140" s="28">
         <f t="shared" si="50"/>
-        <v>4721065</v>
+        <v>4588065</v>
       </c>
       <c r="AC140" s="28">
         <f t="shared" si="50"/>
-        <v>48000</v>
+        <v>54000</v>
       </c>
       <c r="AD140" s="28">
         <f t="shared" si="50"/>
@@ -24415,7 +24427,7 @@
   <cols>
     <col min="1" max="1" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="107.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="7" bestFit="1" customWidth="1"/>
@@ -24442,7 +24454,7 @@
       </c>
       <c r="F1" s="36">
         <f>SUMIF(E1:E1000, "&lt;&gt;", D1:D1000)</f>
-        <v>4272905</v>
+        <v>4405905</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -24870,19 +24882,19 @@
     </row>
     <row r="19" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>46278</v>
+        <v>46295</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D19" s="9">
-        <v>62230</v>
+        <v>48000</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -24906,19 +24918,19 @@
     </row>
     <row r="20" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D20" s="9">
-        <v>60000</v>
+        <v>62230</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -24942,19 +24954,19 @@
     </row>
     <row r="21" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
-        <v>46286</v>
+        <v>46271</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>376</v>
+        <v>267</v>
       </c>
       <c r="D21" s="9">
-        <v>27000</v>
+        <v>60000</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>379</v>
+        <v>268</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -24981,13 +24993,13 @@
         <v>46286</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D22" s="9">
-        <v>16140</v>
+        <v>27000</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>379</v>
@@ -25014,19 +25026,19 @@
     </row>
     <row r="23" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="D23" s="9">
-        <v>40000</v>
+        <v>16140</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>327</v>
+        <v>379</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -25050,19 +25062,19 @@
     </row>
     <row r="24" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="D24" s="9">
-        <v>43140</v>
+        <v>40000</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -25086,19 +25098,19 @@
     </row>
     <row r="25" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="D25" s="9">
-        <v>60000</v>
+        <v>43140</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -25122,19 +25134,19 @@
     </row>
     <row r="26" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="D26" s="9">
-        <v>50430</v>
+        <v>60000</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>262</v>
+        <v>333</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -25158,19 +25170,19 @@
     </row>
     <row r="27" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
-        <v>46276</v>
+        <v>46265</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="D27" s="9">
-        <v>28000</v>
+        <v>50430</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -25194,7 +25206,7 @@
     </row>
     <row r="28" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>250</v>
@@ -25203,7 +25215,7 @@
         <v>291</v>
       </c>
       <c r="D28" s="9">
-        <v>15140</v>
+        <v>28000</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>298</v>
@@ -25230,19 +25242,19 @@
     </row>
     <row r="29" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>365</v>
+        <v>291</v>
       </c>
       <c r="D29" s="9">
-        <v>50000</v>
+        <v>15140</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>402</v>
+        <v>298</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -25266,19 +25278,19 @@
     </row>
     <row r="30" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="D30" s="9">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -25302,19 +25314,19 @@
     </row>
     <row r="31" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>46278</v>
+        <v>46287</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>299</v>
+        <v>431</v>
       </c>
       <c r="D31" s="9">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -25338,19 +25350,19 @@
     </row>
     <row r="32" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>46270</v>
+        <v>46278</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D32" s="9">
-        <v>79020</v>
+        <v>50000</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -25374,19 +25386,19 @@
     </row>
     <row r="33" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
-        <v>46238</v>
+        <v>46270</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="D33" s="9">
-        <v>48000</v>
+        <v>79020</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -25410,7 +25422,7 @@
     </row>
     <row r="34" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
-        <v>46282</v>
+        <v>46238</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>250</v>
@@ -25419,7 +25431,7 @@
         <v>249</v>
       </c>
       <c r="D34" s="9">
-        <v>35180</v>
+        <v>48000</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>251</v>
@@ -25446,19 +25458,19 @@
     </row>
     <row r="35" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
-        <v>46270</v>
+        <v>46282</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="D35" s="9">
-        <v>42350</v>
+        <v>35180</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
@@ -25482,7 +25494,7 @@
     </row>
     <row r="36" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>46282</v>
+        <v>46270</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>270</v>
@@ -25491,7 +25503,7 @@
         <v>271</v>
       </c>
       <c r="D36" s="9">
-        <v>40000</v>
+        <v>42350</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>274</v>
@@ -25518,19 +25530,19 @@
     </row>
     <row r="37" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="D37" s="9">
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>419</v>
+        <v>274</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -25554,19 +25566,19 @@
     </row>
     <row r="38" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="D38" s="12">
-        <v>40000</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>328</v>
+      <c r="C38" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D38" s="9">
+        <v>100000</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>418</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -25590,18 +25602,18 @@
     </row>
     <row r="39" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="D39" s="9">
-        <v>88000</v>
-      </c>
-      <c r="E39" s="7" t="s">
+      <c r="D39" s="12">
+        <v>40000</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>328</v>
       </c>
       <c r="F39" s="7"/>
@@ -25626,19 +25638,19 @@
     </row>
     <row r="40" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>46273</v>
+        <v>46289</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="D40" s="9">
-        <v>33000</v>
+        <v>88000</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -25665,13 +25677,13 @@
         <v>46273</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D41" s="9">
-        <v>6840</v>
+        <v>33000</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>282</v>
@@ -25698,7 +25710,7 @@
     </row>
     <row r="42" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>46281</v>
+        <v>46273</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>270</v>
@@ -25707,12 +25719,12 @@
         <v>278</v>
       </c>
       <c r="D42" s="9">
-        <v>5300</v>
+        <v>6840</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="F42" s="11"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -25748,7 +25760,7 @@
       <c r="E43" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="F43" s="7"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
@@ -25770,19 +25782,19 @@
     </row>
     <row r="44" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>270</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D44" s="9">
-        <v>200000</v>
+        <v>5300</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -25806,19 +25818,19 @@
     </row>
     <row r="45" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>270</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>378</v>
+        <v>279</v>
       </c>
       <c r="D45" s="9">
-        <v>56930</v>
+        <v>200000</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>384</v>
+        <v>281</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
@@ -25842,19 +25854,19 @@
     </row>
     <row r="46" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
-        <v>46264</v>
+        <v>46286</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>256</v>
+        <v>378</v>
       </c>
       <c r="D46" s="9">
-        <v>51930</v>
+        <v>56930</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>257</v>
+        <v>384</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -25878,19 +25890,19 @@
     </row>
     <row r="47" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
-        <v>46279</v>
+        <v>46264</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="D47" s="9">
-        <v>25000</v>
+        <v>51930</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -25914,19 +25926,19 @@
     </row>
     <row r="48" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="D48" s="9">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -25950,19 +25962,19 @@
     </row>
     <row r="49" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="D49" s="9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>399</v>
+        <v>343</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="11"/>
@@ -25986,19 +25998,19 @@
     </row>
     <row r="50" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>314</v>
+        <v>395</v>
       </c>
       <c r="D50" s="9">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="11"/>
@@ -26027,14 +26039,14 @@
       <c r="B51" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="D51" s="12">
-        <v>10000</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>420</v>
+      <c r="C51" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D51" s="9">
+        <v>30000</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="11"/>
@@ -26058,19 +26070,19 @@
     </row>
     <row r="52" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>316</v>
+        <v>422</v>
       </c>
       <c r="D52" s="9">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="11"/>
@@ -26093,20 +26105,20 @@
       <c r="X52" s="11"/>
     </row>
     <row r="53" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
-        <v>46271</v>
-      </c>
-      <c r="B53" s="11" t="s">
+      <c r="A53" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="D53" s="12">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>283</v>
+        <v>419</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="11"/>
@@ -26130,19 +26142,19 @@
     </row>
     <row r="54" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="D54" s="9">
-        <v>9640</v>
+        <v>10000</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>283</v>
+        <v>419</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -26166,19 +26178,19 @@
     </row>
     <row r="55" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D55" s="9">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -26201,22 +26213,22 @@
       <c r="X55" s="7"/>
     </row>
     <row r="56" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B56" s="7" t="s">
+      <c r="A56" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B56" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D56" s="9">
-        <v>65160</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F56" s="11"/>
+      <c r="C56" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D56" s="12">
+        <v>20000</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
@@ -26238,21 +26250,21 @@
     </row>
     <row r="57" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>339</v>
+        <v>276</v>
       </c>
       <c r="D57" s="9">
-        <v>35890</v>
+        <v>9640</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F57" s="11"/>
+        <v>283</v>
+      </c>
+      <c r="F57" s="7"/>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
@@ -26274,19 +26286,19 @@
     </row>
     <row r="58" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
-        <v>46280</v>
+        <v>46292</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>344</v>
+        <v>409</v>
       </c>
       <c r="D58" s="9">
         <v>50000</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>347</v>
+        <v>413</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -26310,21 +26322,21 @@
     </row>
     <row r="59" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="D59" s="9">
-        <v>116000</v>
+        <v>65160</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F59" s="7"/>
+        <v>340</v>
+      </c>
+      <c r="F59" s="11"/>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
@@ -26346,21 +26358,21 @@
     </row>
     <row r="60" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
       <c r="D60" s="9">
-        <v>22000</v>
+        <v>35890</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F60" s="7"/>
+        <v>341</v>
+      </c>
+      <c r="F60" s="11"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
@@ -26382,19 +26394,19 @@
     </row>
     <row r="61" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
-        <v>46284</v>
+        <v>46280</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="D61" s="9">
         <v>50000</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -26418,19 +26430,19 @@
     </row>
     <row r="62" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
-        <v>46285</v>
+        <v>46279</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="D62" s="9">
-        <v>50000</v>
+        <v>116000</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -26454,19 +26466,19 @@
     </row>
     <row r="63" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="D63" s="9">
-        <v>90000</v>
+        <v>22000</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -26490,19 +26502,19 @@
     </row>
     <row r="64" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>375</v>
+        <v>421</v>
       </c>
       <c r="D64" s="9">
-        <v>50000</v>
+        <v>65000</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
@@ -26526,19 +26538,19 @@
     </row>
     <row r="65" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>292</v>
+        <v>370</v>
       </c>
       <c r="D65" s="9">
-        <v>95000</v>
+        <v>50000</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>293</v>
+        <v>382</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -26562,19 +26574,19 @@
     </row>
     <row r="66" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
-        <v>46293</v>
+        <v>46285</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>412</v>
+        <v>370</v>
       </c>
       <c r="D66" s="9">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
@@ -26598,19 +26610,19 @@
     </row>
     <row r="67" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="D67" s="9">
-        <v>27900</v>
+        <v>90000</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>324</v>
+        <v>407</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
@@ -26634,19 +26646,19 @@
     </row>
     <row r="68" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="D68" s="9">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -26670,19 +26682,19 @@
     </row>
     <row r="69" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D69" s="9">
-        <v>24700</v>
+        <v>95000</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
@@ -26706,19 +26718,19 @@
     </row>
     <row r="70" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>286</v>
+        <v>411</v>
       </c>
       <c r="D70" s="9">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>287</v>
+        <v>415</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
@@ -26742,19 +26754,19 @@
     </row>
     <row r="71" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="D71" s="9">
-        <v>30000</v>
+        <v>27900</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>415</v>
+        <v>324</v>
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
@@ -26784,13 +26796,13 @@
         <v>250</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D72" s="9">
-        <v>124270</v>
+        <v>40000</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
@@ -26813,20 +26825,20 @@
       <c r="X72" s="7"/>
     </row>
     <row r="73" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
+      <c r="A73" s="8">
         <v>46275</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C73" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="D73" s="12">
-        <v>33140</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>284</v>
+      <c r="C73" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D73" s="9">
+        <v>24700</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
@@ -26850,19 +26862,19 @@
     </row>
     <row r="74" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>374</v>
+        <v>286</v>
       </c>
       <c r="D74" s="9">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>401</v>
+        <v>287</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -26886,19 +26898,19 @@
     </row>
     <row r="75" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="D75" s="9">
-        <v>30000</v>
+        <v>140000</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
@@ -26922,19 +26934,19 @@
     </row>
     <row r="76" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>404</v>
+        <v>295</v>
       </c>
       <c r="D76" s="9">
-        <v>54240</v>
+        <v>30000</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
@@ -26958,19 +26970,19 @@
     </row>
     <row r="77" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
-        <v>46279</v>
+        <v>46288</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>309</v>
+        <v>396</v>
       </c>
       <c r="D77" s="9">
-        <v>36050</v>
+        <v>124270</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
@@ -26993,20 +27005,20 @@
       <c r="X77" s="7"/>
     </row>
     <row r="78" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="D78" s="9">
-        <v>50000</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>273</v>
+      <c r="A78" s="10">
+        <v>46275</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D78" s="12">
+        <v>33140</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>284</v>
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
@@ -27030,19 +27042,19 @@
     </row>
     <row r="79" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>315</v>
+        <v>427</v>
       </c>
       <c r="D79" s="9">
-        <v>100000</v>
+        <v>45000</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>329</v>
+        <v>429</v>
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
@@ -27066,19 +27078,19 @@
     </row>
     <row r="80" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D80" s="9">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
@@ -27102,19 +27114,19 @@
     </row>
     <row r="81" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
-        <v>46277</v>
+        <v>46292</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>294</v>
+        <v>408</v>
       </c>
       <c r="D81" s="9">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
@@ -27138,19 +27150,19 @@
     </row>
     <row r="82" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>317</v>
+        <v>403</v>
       </c>
       <c r="D82" s="9">
-        <v>44140</v>
+        <v>54240</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>348</v>
+        <v>404</v>
       </c>
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
@@ -27174,16 +27186,16 @@
     </row>
     <row r="83" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>411</v>
+        <v>309</v>
       </c>
       <c r="D83" s="9">
-        <v>50000</v>
+        <v>36050</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>417</v>
@@ -27210,19 +27222,19 @@
     </row>
     <row r="84" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D84" s="9">
         <v>50000</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
@@ -27246,19 +27258,19 @@
     </row>
     <row r="85" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="D85" s="9">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
@@ -27282,19 +27294,19 @@
     </row>
     <row r="86" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="D86" s="9">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="F86" s="7"/>
       <c r="G86" s="7"/>
@@ -27318,19 +27330,19 @@
     </row>
     <row r="87" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
-        <v>46290</v>
+        <v>46277</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="D87" s="9">
-        <v>16880</v>
+        <v>10000</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -27354,18 +27366,20 @@
     </row>
     <row r="88" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D88" s="9">
-        <v>20180</v>
-      </c>
-      <c r="E88" s="7"/>
+        <v>44140</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>348</v>
+      </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -27388,18 +27402,20 @@
     </row>
     <row r="89" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
-        <v>46282</v>
+        <v>46294</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="D89" s="9">
         <v>40000</v>
       </c>
-      <c r="E89" s="7"/>
+      <c r="E89" s="7" t="s">
+        <v>425</v>
+      </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -27422,19 +27438,19 @@
     </row>
     <row r="90" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D90" s="9">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
@@ -27458,19 +27474,19 @@
     </row>
     <row r="91" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
-        <v>46294</v>
+        <v>46266</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>423</v>
+        <v>263</v>
       </c>
       <c r="D91" s="9">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>369</v>
+        <v>264</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
@@ -27494,19 +27510,19 @@
     </row>
     <row r="92" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
-        <v>46294</v>
+        <v>46281</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>424</v>
+        <v>345</v>
       </c>
       <c r="D92" s="9">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>426</v>
+        <v>346</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="7"/>
@@ -27530,19 +27546,19 @@
     </row>
     <row r="93" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>250</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>425</v>
+        <v>345</v>
       </c>
       <c r="D93" s="9">
-        <v>140000</v>
+        <v>10000</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>427</v>
+        <v>346</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -27565,10 +27581,21 @@
       <c r="X93" s="7"/>
     </row>
     <row r="94" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="7"/>
+      <c r="A94" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D94" s="9">
+        <v>16880</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>346</v>
+      </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -27590,9 +27617,18 @@
       <c r="X94" s="7"/>
     </row>
     <row r="95" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="9"/>
+      <c r="A95" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D95" s="9">
+        <v>20180</v>
+      </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -27615,9 +27651,18 @@
       <c r="X95" s="7"/>
     </row>
     <row r="96" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="9"/>
+      <c r="A96" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D96" s="9">
+        <v>40000</v>
+      </c>
       <c r="E96" s="7"/>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -39964,8 +40009,8 @@
       <c r="X589" s="7"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F93">
-    <sortCondition ref="E2:E93"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F96">
+    <sortCondition ref="E2:E96"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -40011,17 +40056,17 @@
       </c>
       <c r="B2" s="15">
         <f>'1ST TERM ACCOUNT'!AC140</f>
-        <v>48000</v>
+        <v>54000</v>
       </c>
       <c r="C2" s="15">
         <f>B2*0.7</f>
-        <v>33600</v>
+        <v>37800</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
       <c r="F2" s="15">
         <f>$C$2-D2</f>
-        <v>33600</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -40037,7 +40082,7 @@
       <c r="E3" s="16"/>
       <c r="F3" s="15">
         <f>$C$2-(D2+D3)</f>
-        <v>33600</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -40046,14 +40091,14 @@
       </c>
       <c r="B4" s="15">
         <f>B3-B2</f>
-        <v>144000</v>
+        <v>138000</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
       <c r="F4" s="15">
         <f>$C$2-(D2+D3+D4)</f>
-        <v>33600</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -40063,7 +40108,7 @@
       <c r="E5" s="16"/>
       <c r="F5" s="15">
         <f>$C$2-(D2+D3+D4+D5)</f>
-        <v>33600</v>
+        <v>37800</v>
       </c>
       <c r="H5" s="17"/>
     </row>
